--- a/jogos_2025-08-11.xlsx
+++ b/jogos_2025-08-11.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL31"/>
+  <dimension ref="A1:AL38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -806,13 +806,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -854,10 +854,10 @@
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Renofa Yamaguchi</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -986,10 +986,10 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Renofa Yamaguchi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.68</v>
+        <v>2.35</v>
       </c>
       <c r="M5" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="N5" t="n">
-        <v>5.2</v>
+        <v>2.96</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1112,16 +1112,16 @@
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.21</v>
+        <v>2.28</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="M10" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="N10" t="n">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1821,27 +1821,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="AL11" s="3" t="n">
-        <v>45880.58333333334</v>
+        <v>45880.54166666666</v>
       </c>
     </row>
     <row r="12">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="AL16" s="3" t="n">
-        <v>45880.625</v>
+        <v>45880.58333333334</v>
       </c>
     </row>
     <row r="17">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="AL17" s="3" t="n">
-        <v>45880.625</v>
+        <v>45880.58333333334</v>
       </c>
     </row>
     <row r="18">
@@ -2745,27 +2745,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="AL18" s="3" t="n">
-        <v>45880.625</v>
+        <v>45880.58333333334</v>
       </c>
     </row>
     <row r="19">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3000,7 +3000,7 @@
         </is>
       </c>
       <c r="AL19" s="3" t="n">
-        <v>45880.64583333334</v>
+        <v>45880.625</v>
       </c>
     </row>
     <row r="20">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="AL20" s="3" t="n">
-        <v>45880.64583333334</v>
+        <v>45880.625</v>
       </c>
     </row>
     <row r="21">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3264,7 +3264,7 @@
         </is>
       </c>
       <c r="AL21" s="3" t="n">
-        <v>45880.64583333334</v>
+        <v>45880.625</v>
       </c>
     </row>
     <row r="22">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.4</v>
+        <v>1.73</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>3.29</v>
       </c>
       <c r="N22" t="n">
-        <v>1.74</v>
+        <v>4.2</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="AL22" s="3" t="n">
-        <v>45880.65625</v>
+        <v>45880.63541666666</v>
       </c>
     </row>
     <row r="23">
@@ -3405,12 +3405,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="AL23" s="3" t="n">
-        <v>45880.67708333334</v>
+        <v>45880.64583333334</v>
       </c>
     </row>
     <row r="24">
@@ -3537,27 +3537,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3660,7 +3660,7 @@
         </is>
       </c>
       <c r="AL24" s="3" t="n">
-        <v>45880.67708333334</v>
+        <v>45880.64583333334</v>
       </c>
     </row>
     <row r="25">
@@ -3669,27 +3669,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="AL25" s="3" t="n">
-        <v>45880.67708333334</v>
+        <v>45880.64583333334</v>
       </c>
     </row>
     <row r="26">
@@ -3801,27 +3801,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="AL26" s="3" t="n">
-        <v>45880.83333333334</v>
+        <v>45880.65625</v>
       </c>
     </row>
     <row r="27">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4056,7 +4056,7 @@
         </is>
       </c>
       <c r="AL27" s="3" t="n">
-        <v>45880.83333333334</v>
+        <v>45880.67708333334</v>
       </c>
     </row>
     <row r="28">
@@ -4065,27 +4065,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4188,7 +4188,7 @@
         </is>
       </c>
       <c r="AL28" s="3" t="n">
-        <v>45880.83333333334</v>
+        <v>45880.67708333334</v>
       </c>
     </row>
     <row r="29">
@@ -4197,12 +4197,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.85</v>
+        <v>1.62</v>
       </c>
       <c r="M29" t="n">
-        <v>3.05</v>
+        <v>3.9</v>
       </c>
       <c r="N29" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4286,10 +4286,10 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -4320,7 +4320,7 @@
         </is>
       </c>
       <c r="AL29" s="3" t="n">
-        <v>45880.83333333334</v>
+        <v>45880.67708333334</v>
       </c>
     </row>
     <row r="30">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="AL30" s="3" t="n">
-        <v>45880.85416666666</v>
+        <v>45880.75</v>
       </c>
     </row>
     <row r="31">
@@ -4461,12 +4461,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4508,7 +4508,7 @@
         <v>3.15</v>
       </c>
       <c r="N31" t="n">
-        <v>3.15</v>
+        <v>3.29</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4544,46 +4544,970 @@
         <v>0</v>
       </c>
       <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL31" s="3" t="n">
+        <v>45880.8125</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>45880</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Itabaiana</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>CSA</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL32" s="3" t="n">
+        <v>45880.8125</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>45880</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Deportes Limache</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Audax Italiano</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL33" s="3" t="n">
+        <v>45880.83333333334</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>45880</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>New York RB II</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Philadelphia Union II</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL34" s="3" t="n">
+        <v>45880.83333333334</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>45880</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="M35" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
         <v>1.47</v>
       </c>
-      <c r="AA31" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL31" s="3" t="n">
+      <c r="AA35" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL35" s="3" t="n">
+        <v>45880.83333333334</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>45880</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>FC Cincinnati II</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Crown Legacy</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL36" s="3" t="n">
+        <v>45880.85416666666</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>45880</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Racing Córdoba</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Quilmes</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="M37" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N37" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL37" s="3" t="n">
+        <v>45880.88194444445</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>45880</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Paysandu</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N38" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL38" s="3" t="n">
         <v>45880.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-08-11.xlsx
+++ b/jogos_2025-08-11.xlsx
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Renofa Yamaguchi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.59</v>
+        <v>2.35</v>
       </c>
       <c r="M4" t="n">
-        <v>3.82</v>
+        <v>2.8</v>
       </c>
       <c r="N4" t="n">
-        <v>4.4</v>
+        <v>2.96</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -980,16 +980,16 @@
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.76</v>
+        <v>2.28</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.94</v>
+        <v>1.55</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Renofa Yamaguchi</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.35</v>
+        <v>1.59</v>
       </c>
       <c r="M5" t="n">
-        <v>2.8</v>
+        <v>3.82</v>
       </c>
       <c r="N5" t="n">
-        <v>2.96</v>
+        <v>4.4</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1112,16 +1112,16 @@
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.28</v>
+        <v>1.76</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.55</v>
+        <v>1.94</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Kudrivka</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kudrivka</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="N13" t="n">
-        <v>2.91</v>
+        <v>3.23</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.98</v>
+        <v>5.2</v>
       </c>
       <c r="M14" t="n">
-        <v>3.28</v>
+        <v>3.65</v>
       </c>
       <c r="N14" t="n">
-        <v>3.23</v>
+        <v>1.63</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.2</v>
+        <v>2.72</v>
       </c>
       <c r="M16" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="N16" t="n">
-        <v>1.63</v>
+        <v>2.16</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.72</v>
+        <v>1.39</v>
       </c>
       <c r="M17" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="N17" t="n">
-        <v>2.16</v>
+        <v>5.7</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.39</v>
+        <v>2.04</v>
       </c>
       <c r="M18" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>5.7</v>
+        <v>2.91</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.38</v>
+        <v>1.62</v>
       </c>
       <c r="M27" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="N27" t="n">
-        <v>2.55</v>
+        <v>4.5</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4070,22 +4070,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4202,22 +4202,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2025-08-11.xlsx
+++ b/jogos_2025-08-11.xlsx
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.45</v>
+        <v>1.39</v>
       </c>
       <c r="M12" t="n">
-        <v>3.31</v>
+        <v>4.5</v>
       </c>
       <c r="N12" t="n">
-        <v>1.9</v>
+        <v>5.7</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.98</v>
+        <v>2.72</v>
       </c>
       <c r="M13" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>3.23</v>
+        <v>2.16</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.2</v>
+        <v>2.08</v>
       </c>
       <c r="M14" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>1.63</v>
+        <v>3.2</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.08</v>
+        <v>4.2</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="N15" t="n">
-        <v>3.2</v>
+        <v>1.69</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.72</v>
+        <v>2.04</v>
       </c>
       <c r="M16" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>2.16</v>
+        <v>2.91</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.39</v>
+        <v>1.98</v>
       </c>
       <c r="M17" t="n">
-        <v>4.5</v>
+        <v>3.28</v>
       </c>
       <c r="N17" t="n">
-        <v>5.7</v>
+        <v>3.23</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.18</v>
+        <v>1.9</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.04</v>
+        <v>3.45</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>3.31</v>
       </c>
       <c r="N18" t="n">
-        <v>2.91</v>
+        <v>1.9</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2025-08-11.xlsx
+++ b/jogos_2025-08-11.xlsx
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.39</v>
+        <v>2.72</v>
       </c>
       <c r="M12" t="n">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>5.7</v>
+        <v>2.16</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.72</v>
+        <v>2.04</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>2.16</v>
+        <v>2.91</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="N14" t="n">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.2</v>
+        <v>1.39</v>
       </c>
       <c r="M15" t="n">
-        <v>3.47</v>
+        <v>4.5</v>
       </c>
       <c r="N15" t="n">
-        <v>1.69</v>
+        <v>5.7</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.75</v>
+        <v>2.18</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="M16" t="n">
         <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.98</v>
+        <v>3.45</v>
       </c>
       <c r="M17" t="n">
-        <v>3.28</v>
+        <v>3.31</v>
       </c>
       <c r="N17" t="n">
-        <v>3.23</v>
+        <v>1.9</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="M18" t="n">
-        <v>3.31</v>
+        <v>3.47</v>
       </c>
       <c r="N18" t="n">
-        <v>1.9</v>
+        <v>1.69</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.62</v>
+        <v>2.5</v>
       </c>
       <c r="M27" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="N27" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4022,10 +4022,10 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.38</v>
+        <v>1.65</v>
       </c>
       <c r="M28" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="N28" t="n">
-        <v>2.55</v>
+        <v>4.6</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4160,10 +4160,10 @@
         <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4946,10 +4946,10 @@
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5072,16 +5072,16 @@
         <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5121,12 +5121,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5204,16 +5204,16 @@
         <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="AL36" s="3" t="n">
-        <v>45880.85416666666</v>
+        <v>45880.83333333334</v>
       </c>
     </row>
     <row r="37">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5342,10 +5342,10 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="AL37" s="3" t="n">
-        <v>45880.88194444445</v>
+        <v>45880.85416666666</v>
       </c>
     </row>
     <row r="38">

--- a/jogos_2025-08-11.xlsx
+++ b/jogos_2025-08-11.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL38"/>
+  <dimension ref="A1:AL39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Renofa Yamaguchi</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.35</v>
+        <v>1.59</v>
       </c>
       <c r="M4" t="n">
-        <v>2.8</v>
+        <v>3.82</v>
       </c>
       <c r="N4" t="n">
-        <v>2.96</v>
+        <v>4.4</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -980,16 +980,16 @@
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.28</v>
+        <v>1.76</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.55</v>
+        <v>1.94</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Renofa Yamaguchi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.59</v>
+        <v>2.35</v>
       </c>
       <c r="M5" t="n">
-        <v>3.82</v>
+        <v>2.8</v>
       </c>
       <c r="N5" t="n">
-        <v>4.4</v>
+        <v>2.96</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1112,16 +1112,16 @@
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.76</v>
+        <v>2.28</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.94</v>
+        <v>1.55</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.72</v>
+        <v>2.08</v>
       </c>
       <c r="M12" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>2.16</v>
+        <v>3.2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.04</v>
+        <v>4.2</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="N13" t="n">
-        <v>2.91</v>
+        <v>1.69</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.98</v>
+        <v>2.72</v>
       </c>
       <c r="M14" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>3.23</v>
+        <v>2.16</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.39</v>
+        <v>1.98</v>
       </c>
       <c r="M15" t="n">
-        <v>4.5</v>
+        <v>3.28</v>
       </c>
       <c r="N15" t="n">
-        <v>5.7</v>
+        <v>3.23</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.18</v>
+        <v>1.9</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.08</v>
+        <v>3.45</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>3.31</v>
       </c>
       <c r="N16" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.45</v>
+        <v>2.04</v>
       </c>
       <c r="M17" t="n">
-        <v>3.31</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>1.9</v>
+        <v>2.91</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4.2</v>
+        <v>1.39</v>
       </c>
       <c r="M18" t="n">
-        <v>3.47</v>
+        <v>4.5</v>
       </c>
       <c r="N18" t="n">
-        <v>1.69</v>
+        <v>5.7</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,16 +2834,16 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.75</v>
+        <v>2.18</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -2877,12 +2877,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3000,7 +3000,7 @@
         </is>
       </c>
       <c r="AL19" s="3" t="n">
-        <v>45880.625</v>
+        <v>45880.61458333334</v>
       </c>
     </row>
     <row r="20">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="AL22" s="3" t="n">
-        <v>45880.63541666666</v>
+        <v>45880.625</v>
       </c>
     </row>
     <row r="23">
@@ -3405,12 +3405,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="AL23" s="3" t="n">
-        <v>45880.64583333334</v>
+        <v>45880.63541666666</v>
       </c>
     </row>
     <row r="24">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4</v>
+        <v>3.12</v>
       </c>
       <c r="M26" t="n">
-        <v>3.31</v>
+        <v>2.91</v>
       </c>
       <c r="N26" t="n">
-        <v>1.76</v>
+        <v>2.19</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="AL26" s="3" t="n">
-        <v>45880.65625</v>
+        <v>45880.64583333334</v>
       </c>
     </row>
     <row r="27">
@@ -3933,27 +3933,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="M27" t="n">
-        <v>3.75</v>
+        <v>3.31</v>
       </c>
       <c r="N27" t="n">
-        <v>2.6</v>
+        <v>1.76</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4022,10 +4022,10 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.15</v>
+        <v>1.72</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -4056,7 +4056,7 @@
         </is>
       </c>
       <c r="AL27" s="3" t="n">
-        <v>45880.67708333334</v>
+        <v>45880.65625</v>
       </c>
     </row>
     <row r="28">
@@ -4202,22 +4202,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4286,10 +4286,10 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -4329,27 +4329,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="AL30" s="3" t="n">
-        <v>45880.75</v>
+        <v>45880.69791666666</v>
       </c>
     </row>
     <row r="31">
@@ -4461,12 +4461,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
@@ -4584,7 +4584,7 @@
         </is>
       </c>
       <c r="AL31" s="3" t="n">
-        <v>45880.8125</v>
+        <v>45880.75</v>
       </c>
     </row>
     <row r="32">
@@ -4725,12 +4725,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -4848,7 +4848,7 @@
         </is>
       </c>
       <c r="AL33" s="3" t="n">
-        <v>45880.83333333334</v>
+        <v>45880.8125</v>
       </c>
     </row>
     <row r="34">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4946,10 +4946,10 @@
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5078,10 +5078,10 @@
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5204,16 +5204,16 @@
         <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5253,12 +5253,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5336,16 +5336,16 @@
         <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="AL37" s="3" t="n">
-        <v>45880.85416666666</v>
+        <v>45880.83333333334</v>
       </c>
     </row>
     <row r="38">
@@ -5385,129 +5385,261 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>FC Cincinnati II</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Crown Legacy</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL38" s="3" t="n">
+        <v>45880.85416666666</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>45880</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Paysandu</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>Vila Nova</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="inlineStr">
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L38" t="n">
+      <c r="L39" t="n">
         <v>2.17</v>
       </c>
-      <c r="M38" t="n">
+      <c r="M39" t="n">
         <v>3.2</v>
       </c>
-      <c r="N38" t="n">
+      <c r="N39" t="n">
         <v>3.25</v>
       </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z38" t="n">
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
         <v>1.5</v>
       </c>
-      <c r="AA38" t="n">
+      <c r="AA39" t="n">
         <v>2.4</v>
       </c>
-      <c r="AB38" t="n">
+      <c r="AB39" t="n">
         <v>2.37</v>
       </c>
-      <c r="AC38" t="n">
+      <c r="AC39" t="n">
         <v>1.48</v>
       </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL38" s="3" t="n">
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL39" s="3" t="n">
         <v>45880.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-08-11.xlsx
+++ b/jogos_2025-08-11.xlsx
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kudrivka</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Kudrivka</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.08</v>
+        <v>3.45</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>3.31</v>
       </c>
       <c r="N12" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.2</v>
+        <v>2.72</v>
       </c>
       <c r="M13" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>1.69</v>
+        <v>2.16</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.72</v>
+        <v>1.98</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="N14" t="n">
-        <v>2.16</v>
+        <v>3.23</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.98</v>
+        <v>4.2</v>
       </c>
       <c r="M15" t="n">
-        <v>3.28</v>
+        <v>3.47</v>
       </c>
       <c r="N15" t="n">
-        <v>3.23</v>
+        <v>1.69</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.45</v>
+        <v>2.08</v>
       </c>
       <c r="M16" t="n">
-        <v>3.31</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="M28" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="N28" t="n">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4154,16 +4154,16 @@
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="M29" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="N29" t="n">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4286,16 +4286,16 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF29" t="n">
         <v>0</v>
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="M30" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="N30" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O30" t="n">
         <v>1.5</v>
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4682,10 +4682,10 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5072,10 +5072,10 @@
         <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB35" t="n">
         <v>2.4</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5204,16 +5204,16 @@
         <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5336,16 +5336,16 @@
         <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="M39" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="N39" t="n">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>

--- a/jogos_2025-08-11.xlsx
+++ b/jogos_2025-08-11.xlsx
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.45</v>
+        <v>2.04</v>
       </c>
       <c r="M12" t="n">
-        <v>3.31</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>1.9</v>
+        <v>2.91</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.72</v>
+        <v>1.39</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="N13" t="n">
-        <v>2.16</v>
+        <v>5.7</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,16 +2174,16 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.04</v>
+        <v>2.72</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N17" t="n">
-        <v>2.91</v>
+        <v>2.16</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.39</v>
+        <v>3.45</v>
       </c>
       <c r="M18" t="n">
-        <v>4.5</v>
+        <v>3.31</v>
       </c>
       <c r="N18" t="n">
-        <v>5.7</v>
+        <v>1.9</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,16 +2834,16 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="M28" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="N28" t="n">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4154,16 +4154,16 @@
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="M29" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="N29" t="n">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4286,16 +4286,16 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
         <v>0</v>
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4682,10 +4682,10 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5072,16 +5072,16 @@
         <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5336,16 +5336,16 @@
         <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>

--- a/jogos_2025-08-11.xlsx
+++ b/jogos_2025-08-11.xlsx
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="M12" t="n">
         <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.39</v>
+        <v>4.2</v>
       </c>
       <c r="M13" t="n">
-        <v>4.5</v>
+        <v>3.47</v>
       </c>
       <c r="N13" t="n">
-        <v>5.7</v>
+        <v>1.69</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,16 +2174,16 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.18</v>
+        <v>1.75</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="M14" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>3.23</v>
+        <v>2.91</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.2</v>
+        <v>2.72</v>
       </c>
       <c r="M15" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>1.69</v>
+        <v>2.16</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="N16" t="n">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.72</v>
+        <v>3.45</v>
       </c>
       <c r="M17" t="n">
-        <v>3.45</v>
+        <v>3.31</v>
       </c>
       <c r="N17" t="n">
-        <v>2.16</v>
+        <v>1.9</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.45</v>
+        <v>1.39</v>
       </c>
       <c r="M18" t="n">
-        <v>3.31</v>
+        <v>4.5</v>
       </c>
       <c r="N18" t="n">
-        <v>1.9</v>
+        <v>5.7</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,16 +2834,16 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="M28" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="N28" t="n">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4154,16 +4154,16 @@
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="M29" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="N29" t="n">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4286,16 +4286,16 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF29" t="n">
         <v>0</v>
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4682,10 +4682,10 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4940,16 +4940,16 @@
         <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5072,16 +5072,16 @@
         <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5204,16 +5204,16 @@
         <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5336,16 +5336,16 @@
         <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>

--- a/jogos_2025-08-11.xlsx
+++ b/jogos_2025-08-11.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL39"/>
+  <dimension ref="A1:AL44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -806,52 +806,52 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.11</v>
+        <v>1.52</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>3.79</v>
       </c>
       <c r="N3" t="n">
-        <v>3.3</v>
+        <v>5.1</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>11.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB3" t="n">
         <v>1.82</v>
@@ -860,22 +860,22 @@
         <v>1.94</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -947,43 +947,43 @@
         <v>4.4</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB4" t="n">
         <v>1.76</v>
@@ -992,22 +992,22 @@
         <v>1.94</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1079,67 +1079,67 @@
         <v>2.96</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="Z5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC5" t="n">
         <v>1.48</v>
       </c>
-      <c r="AA5" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Kudrivka</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,40 +1334,40 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1394,10 +1394,10 @@
         <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH7" t="n">
         <v>0</v>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kudrivka</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1557,27 +1557,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>45880.54166666666</v>
+        <v>45880.52083333334</v>
       </c>
     </row>
     <row r="10">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="M10" t="n">
-        <v>3.12</v>
+        <v>3.5</v>
       </c>
       <c r="N10" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1953,27 +1953,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="AL12" s="3" t="n">
-        <v>45880.58333333334</v>
+        <v>45880.54166666666</v>
       </c>
     </row>
     <row r="13">
@@ -2085,12 +2085,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,40 +2126,40 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.2</v>
+        <v>1.75</v>
       </c>
       <c r="M13" t="n">
-        <v>3.47</v>
+        <v>3.12</v>
       </c>
       <c r="N13" t="n">
-        <v>1.69</v>
+        <v>4.33</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2186,10 +2186,10 @@
         <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH13" t="n">
         <v>0</v>
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="AL13" s="3" t="n">
-        <v>45880.58333333334</v>
+        <v>45880.54166666666</v>
       </c>
     </row>
     <row r="14">
@@ -2217,27 +2217,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N14" t="n">
-        <v>2.91</v>
+        <v>2.5</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>17.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="AL14" s="3" t="n">
-        <v>45880.58333333334</v>
+        <v>45880.54166666666</v>
       </c>
     </row>
     <row r="15">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.72</v>
+        <v>4.2</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="N15" t="n">
-        <v>2.16</v>
+        <v>1.69</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.57</v>
+        <v>1.94</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.15</v>
+        <v>1.76</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.98</v>
+        <v>3.57</v>
       </c>
       <c r="M16" t="n">
-        <v>3.28</v>
+        <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>3.23</v>
+        <v>2.1</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.9</v>
+        <v>1.42</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="M17" t="n">
         <v>3.45</v>
       </c>
-      <c r="M17" t="n">
-        <v>3.31</v>
-      </c>
       <c r="N17" t="n">
-        <v>1.9</v>
+        <v>2.16</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.39</v>
+        <v>2.07</v>
       </c>
       <c r="M18" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>5.7</v>
+        <v>3.05</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.25</v>
+        <v>2.94</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2877,27 +2877,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         </is>
       </c>
       <c r="AL19" s="3" t="n">
-        <v>45880.61458333334</v>
+        <v>45880.58333333334</v>
       </c>
     </row>
     <row r="20">
@@ -3009,27 +3009,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="AL20" s="3" t="n">
-        <v>45880.625</v>
+        <v>45880.58333333334</v>
       </c>
     </row>
     <row r="21">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,76 +3182,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         </is>
       </c>
       <c r="AL21" s="3" t="n">
-        <v>45880.625</v>
+        <v>45880.58333333334</v>
       </c>
     </row>
     <row r="22">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="AL22" s="3" t="n">
-        <v>45880.625</v>
+        <v>45880.58333333334</v>
       </c>
     </row>
     <row r="23">
@@ -3405,12 +3405,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="M23" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
         <v>4.2</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="AL23" s="3" t="n">
-        <v>45880.63541666666</v>
+        <v>45880.61458333334</v>
       </c>
     </row>
     <row r="24">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,76 +3578,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         </is>
       </c>
       <c r="AL24" s="3" t="n">
-        <v>45880.64583333334</v>
+        <v>45880.625</v>
       </c>
     </row>
     <row r="25">
@@ -3669,12 +3669,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,76 +3710,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="M25" t="n">
-        <v>2.91</v>
+        <v>3.7</v>
       </c>
       <c r="N25" t="n">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC25" t="n">
         <v>2.4</v>
       </c>
-      <c r="AC25" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="AL25" s="3" t="n">
-        <v>45880.64583333334</v>
+        <v>45880.625</v>
       </c>
     </row>
     <row r="26">
@@ -3801,12 +3801,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="AL26" s="3" t="n">
-        <v>45880.64583333334</v>
+        <v>45880.625</v>
       </c>
     </row>
     <row r="27">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4022,10 +4022,10 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -4056,7 +4056,7 @@
         </is>
       </c>
       <c r="AL27" s="3" t="n">
-        <v>45880.65625</v>
+        <v>45880.625</v>
       </c>
     </row>
     <row r="28">
@@ -4065,27 +4065,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.5</v>
+        <v>1.78</v>
       </c>
       <c r="M28" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="N28" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         </is>
       </c>
       <c r="AL28" s="3" t="n">
-        <v>45880.67708333334</v>
+        <v>45880.63541666666</v>
       </c>
     </row>
     <row r="29">
@@ -4197,27 +4197,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,76 +4238,76 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.65</v>
+        <v>3.12</v>
       </c>
       <c r="M29" t="n">
-        <v>4.3</v>
+        <v>2.91</v>
       </c>
       <c r="N29" t="n">
-        <v>4.6</v>
+        <v>2.19</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.25</v>
+        <v>3.52</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.63</v>
+        <v>1.22</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         </is>
       </c>
       <c r="AL29" s="3" t="n">
-        <v>45880.67708333334</v>
+        <v>45880.64583333334</v>
       </c>
     </row>
     <row r="30">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.59</v>
+        <v>1.19</v>
       </c>
       <c r="M30" t="n">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="N30" t="n">
-        <v>5.6</v>
+        <v>12.25</v>
       </c>
       <c r="O30" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="P30" t="n">
-        <v>10</v>
+        <v>15.25</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.75</v>
+        <v>4.65</v>
       </c>
       <c r="R30" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="S30" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="T30" t="n">
-        <v>2.63</v>
+        <v>2.19</v>
       </c>
       <c r="U30" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="V30" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="W30" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X30" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y30" t="n">
-        <v>9.5</v>
+        <v>19</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.65</v>
+        <v>5</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.83</v>
+        <v>1.42</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.97</v>
+        <v>2.49</v>
       </c>
       <c r="AD30" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.38</v>
+        <v>1.66</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.95</v>
+        <v>1.64</v>
       </c>
       <c r="AH30" t="n">
-        <v>5.75</v>
+        <v>3.28</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="AL30" s="3" t="n">
-        <v>45880.69791666666</v>
+        <v>45880.64583333334</v>
       </c>
     </row>
     <row r="31">
@@ -4461,27 +4461,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         </is>
       </c>
       <c r="AL31" s="3" t="n">
-        <v>45880.75</v>
+        <v>45880.64583333334</v>
       </c>
     </row>
     <row r="32">
@@ -4593,27 +4593,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,76 +4634,76 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.15</v>
+        <v>4</v>
       </c>
       <c r="M32" t="n">
-        <v>3.15</v>
+        <v>3.31</v>
       </c>
       <c r="N32" t="n">
-        <v>3.29</v>
+        <v>1.76</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AB32" t="n">
         <v>2.12</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="AL32" s="3" t="n">
-        <v>45880.8125</v>
+        <v>45880.65625</v>
       </c>
     </row>
     <row r="33">
@@ -4725,12 +4725,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         </is>
       </c>
       <c r="AL33" s="3" t="n">
-        <v>45880.8125</v>
+        <v>45880.67708333334</v>
       </c>
     </row>
     <row r="34">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="M34" t="n">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="N34" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4916,58 +4916,58 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.53</v>
+        <v>1.11</v>
       </c>
       <c r="AA34" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD34" t="n">
         <v>2.25</v>
       </c>
-      <c r="AB34" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="AL34" s="3" t="n">
-        <v>45880.83333333334</v>
+        <v>45880.67708333334</v>
       </c>
     </row>
     <row r="35">
@@ -4989,27 +4989,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.29</v>
+        <v>1.65</v>
       </c>
       <c r="M35" t="n">
-        <v>2.94</v>
+        <v>3.85</v>
       </c>
       <c r="N35" t="n">
-        <v>2.1</v>
+        <v>5.5</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.6</v>
+        <v>3.65</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.55</v>
+        <v>1.97</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="AL35" s="3" t="n">
-        <v>45880.83333333334</v>
+        <v>45880.69791666666</v>
       </c>
     </row>
     <row r="36">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,40 +5162,40 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5222,10 +5222,10 @@
         <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH36" t="n">
         <v>0</v>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="AL36" s="3" t="n">
-        <v>45880.83333333334</v>
+        <v>45880.75</v>
       </c>
     </row>
     <row r="37">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,76 +5294,76 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="AL37" s="3" t="n">
-        <v>45880.83333333334</v>
+        <v>45880.8125</v>
       </c>
     </row>
     <row r="38">
@@ -5385,12 +5385,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,76 +5426,76 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="AL38" s="3" t="n">
-        <v>45880.85416666666</v>
+        <v>45880.8125</v>
       </c>
     </row>
     <row r="39">
@@ -5517,129 +5517,789 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="M39" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P39" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V39" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL39" s="3" t="n">
+        <v>45880.83333333334</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>45880</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Deportes Limache</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Audax Italiano</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="M40" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O40" t="n">
+        <v>2</v>
+      </c>
+      <c r="P40" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V40" t="n">
+        <v>7</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL40" s="3" t="n">
+        <v>45880.83333333334</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>45880</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>New York RB II</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Philadelphia Union II</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL41" s="3" t="n">
+        <v>45880.83333333334</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>45880</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>FC Cincinnati II</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Crown Legacy</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL42" s="3" t="n">
+        <v>45880.85416666666</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>45880</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Racing Córdoba</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Quilmes</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="M43" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N43" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V43" t="n">
+        <v>13</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL43" s="3" t="n">
+        <v>45880.88194444445</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>45880</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>Paysandu</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Vila Nova</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="inlineStr">
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L39" t="n">
+      <c r="L44" t="n">
         <v>2.22</v>
       </c>
-      <c r="M39" t="n">
+      <c r="M44" t="n">
         <v>2.83</v>
       </c>
-      <c r="N39" t="n">
+      <c r="N44" t="n">
         <v>3.16</v>
       </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z39" t="n">
+      <c r="O44" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P44" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R44" t="n">
         <v>1.5</v>
       </c>
-      <c r="AA39" t="n">
+      <c r="S44" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V44" t="n">
+        <v>11</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X44" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA44" t="n">
         <v>2.4</v>
       </c>
-      <c r="AB39" t="n">
+      <c r="AB44" t="n">
         <v>2.37</v>
       </c>
-      <c r="AC39" t="n">
+      <c r="AC44" t="n">
         <v>1.48</v>
       </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL39" s="3" t="n">
+      <c r="AD44" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL44" s="3" t="n">
         <v>45880.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-08-11.xlsx
+++ b/jogos_2025-08-11.xlsx
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Renofa Yamaguchi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.59</v>
+        <v>2.35</v>
       </c>
       <c r="M4" t="n">
-        <v>3.82</v>
+        <v>2.8</v>
       </c>
       <c r="N4" t="n">
-        <v>4.4</v>
+        <v>2.96</v>
       </c>
       <c r="O4" t="n">
-        <v>1.5</v>
+        <v>1.98</v>
       </c>
       <c r="P4" t="n">
-        <v>9.5</v>
+        <v>6.55</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>2.18</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="S4" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="T4" t="n">
-        <v>2.65</v>
+        <v>3.6</v>
       </c>
       <c r="U4" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="V4" t="n">
-        <v>6.5</v>
+        <v>11</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X4" t="n">
         <v>1.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.5</v>
+        <v>6.55</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.76</v>
+        <v>2.45</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.94</v>
+        <v>1.48</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.1</v>
+        <v>4.95</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AH4" t="n">
-        <v>5.75</v>
+        <v>9</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Renofa Yamaguchi</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.35</v>
+        <v>1.59</v>
       </c>
       <c r="M5" t="n">
-        <v>2.8</v>
+        <v>3.82</v>
       </c>
       <c r="N5" t="n">
-        <v>2.96</v>
+        <v>4.4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.98</v>
+        <v>1.5</v>
       </c>
       <c r="P5" t="n">
-        <v>6.55</v>
+        <v>9.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.18</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="T5" t="n">
-        <v>3.6</v>
+        <v>2.65</v>
       </c>
       <c r="U5" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="V5" t="n">
-        <v>11</v>
+        <v>6.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X5" t="n">
         <v>1.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.55</v>
+        <v>9.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.45</v>
+        <v>1.76</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.48</v>
+        <v>1.94</v>
       </c>
       <c r="AD5" t="n">
-        <v>4.95</v>
+        <v>3.1</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AH5" t="n">
-        <v>9</v>
+        <v>5.75</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P10" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V10" t="n">
         <v>5</v>
       </c>
-      <c r="O10" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="P10" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V10" t="n">
-        <v>7.4</v>
-      </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>8.699999999999999</v>
+        <v>12</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.04</v>
+        <v>5.3</v>
       </c>
       <c r="AB10" t="n">
-        <v>2</v>
+        <v>1.46</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.72</v>
+        <v>2.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.44</v>
+        <v>2.2</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.23</v>
+        <v>1.6</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.87</v>
+        <v>1.43</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>6.8</v>
+        <v>3.7</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>17.75</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.2</v>
+        <v>3.64</v>
       </c>
       <c r="M15" t="n">
-        <v>3.47</v>
+        <v>3.26</v>
       </c>
       <c r="N15" t="n">
-        <v>1.69</v>
+        <v>1.89</v>
       </c>
       <c r="O15" t="n">
         <v>2.5</v>
@@ -2408,22 +2408,22 @@
         <v>1.67</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="T15" t="n">
         <v>3.1</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V15" t="n">
         <v>8.4</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
         <v>1.06</v>
@@ -2432,28 +2432,28 @@
         <v>8</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AD15" t="n">
         <v>3.8</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AF15" t="n">
         <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH15" t="n">
         <v>6.5</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.57</v>
+        <v>1.96</v>
       </c>
       <c r="M16" t="n">
-        <v>3.15</v>
+        <v>3.42</v>
       </c>
       <c r="N16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="P16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V16" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AG16" t="n">
         <v>2.1</v>
       </c>
-      <c r="O16" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="P16" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V16" t="n">
-        <v>10</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AH16" t="n">
-        <v>11</v>
+        <v>4.9</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.72</v>
+        <v>3.45</v>
       </c>
       <c r="M17" t="n">
-        <v>3.45</v>
+        <v>3.31</v>
       </c>
       <c r="N17" t="n">
-        <v>2.16</v>
+        <v>1.9</v>
       </c>
       <c r="O17" t="n">
         <v>2</v>
       </c>
       <c r="P17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="R17" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S17" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="T17" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="U17" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="V17" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="W17" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>13</v>
+        <v>8.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.6</v>
+        <v>3.88</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AH17" t="n">
-        <v>4.41</v>
+        <v>5.25</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.07</v>
+        <v>2.72</v>
       </c>
       <c r="M18" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N18" t="n">
-        <v>3.05</v>
+        <v>2.16</v>
       </c>
       <c r="O18" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="P18" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="R18" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="S18" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="T18" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="U18" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="V18" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="W18" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>9.1</v>
+        <v>13</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.94</v>
+        <v>2.4</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.9</v>
+        <v>4.41</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.98</v>
+        <v>3.53</v>
       </c>
       <c r="M20" t="n">
-        <v>3.28</v>
+        <v>3.18</v>
       </c>
       <c r="N20" t="n">
-        <v>3.23</v>
+        <v>2.16</v>
       </c>
       <c r="O20" t="n">
-        <v>1.73</v>
+        <v>2.53</v>
       </c>
       <c r="P20" t="n">
-        <v>9</v>
+        <v>6.55</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="R20" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>2.36</v>
       </c>
       <c r="T20" t="n">
-        <v>2.63</v>
+        <v>3.66</v>
       </c>
       <c r="U20" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="V20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W20" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AE20" t="n">
         <v>1.1</v>
       </c>
-      <c r="X20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AF20" t="n">
-        <v>1.7</v>
+        <v>2.17</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.05</v>
+        <v>1.61</v>
       </c>
       <c r="AH20" t="n">
-        <v>6.25</v>
+        <v>11</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3146,22 +3146,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,76 +3182,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.45</v>
+        <v>1.98</v>
       </c>
       <c r="M21" t="n">
-        <v>3.31</v>
+        <v>3.28</v>
       </c>
       <c r="N21" t="n">
-        <v>1.9</v>
+        <v>3.23</v>
       </c>
       <c r="O21" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U21" t="n">
         <v>1.44</v>
       </c>
       <c r="V21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W21" t="n">
         <v>1.1</v>
       </c>
       <c r="X21" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y21" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.88</v>
+        <v>3.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="AH21" t="n">
-        <v>5.25</v>
+        <v>6.25</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,76 +3578,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,76 +3710,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="M25" t="n">
-        <v>3.7</v>
+        <v>3.77</v>
       </c>
       <c r="N25" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O25" t="n">
         <v>2.1</v>
       </c>
       <c r="P25" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Q25" t="n">
         <v>1.73</v>
       </c>
       <c r="R25" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S25" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T25" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="U25" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="V25" t="n">
-        <v>5.05</v>
+        <v>4.8</v>
       </c>
       <c r="W25" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AA25" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.63</v>
+        <v>2.49</v>
       </c>
       <c r="AH25" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,76 +3842,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,76 +4238,76 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.12</v>
+        <v>1.53</v>
       </c>
       <c r="M29" t="n">
-        <v>2.91</v>
+        <v>3.9</v>
       </c>
       <c r="N29" t="n">
-        <v>2.19</v>
+        <v>4.75</v>
       </c>
       <c r="O29" t="n">
-        <v>2.38</v>
+        <v>1.5</v>
       </c>
       <c r="P29" t="n">
-        <v>7.3</v>
+        <v>10.5</v>
       </c>
       <c r="Q29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V29" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF29" t="n">
         <v>1.83</v>
       </c>
-      <c r="R29" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V29" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AG29" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH29" t="n">
-        <v>6.85</v>
+        <v>5.5</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.53</v>
+        <v>3.12</v>
       </c>
       <c r="M31" t="n">
-        <v>3.9</v>
+        <v>2.91</v>
       </c>
       <c r="N31" t="n">
-        <v>4.75</v>
+        <v>2.19</v>
       </c>
       <c r="O31" t="n">
-        <v>1.5</v>
+        <v>2.38</v>
       </c>
       <c r="P31" t="n">
-        <v>10.5</v>
+        <v>7.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="R31" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U31" t="n">
         <v>1.33</v>
       </c>
-      <c r="S31" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.44</v>
-      </c>
       <c r="V31" t="n">
-        <v>6.5</v>
+        <v>7.4</v>
       </c>
       <c r="W31" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X31" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y31" t="n">
-        <v>9.5</v>
+        <v>7.3</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.8</v>
+        <v>2.84</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.05</v>
+        <v>1.55</v>
       </c>
       <c r="AD31" t="n">
-        <v>3</v>
+        <v>3.52</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH31" t="n">
-        <v>5.5</v>
+        <v>6.85</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,76 +5294,76 @@
         </is>
       </c>
       <c r="L37" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M37" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N37" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="P37" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Q37" t="n">
         <v>2.4</v>
       </c>
-      <c r="M37" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N37" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O37" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="P37" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>2.2</v>
-      </c>
       <c r="R37" t="n">
-        <v>1.61</v>
+        <v>1.46</v>
       </c>
       <c r="S37" t="n">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="T37" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="U37" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="V37" t="n">
-        <v>10</v>
+        <v>8.25</v>
       </c>
       <c r="W37" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X37" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y37" t="n">
-        <v>5.7</v>
+        <v>7.7</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="AA37" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AB37" t="n">
         <v>2.25</v>
       </c>
-      <c r="AB37" t="n">
-        <v>2.62</v>
-      </c>
       <c r="AC37" t="n">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="AD37" t="n">
-        <v>4.75</v>
+        <v>3.9</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AH37" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,76 +5426,76 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="M38" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="N38" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="O38" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="P38" t="n">
-        <v>7.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="R38" t="n">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="S38" t="n">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="T38" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="U38" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="V38" t="n">
-        <v>8.25</v>
+        <v>10</v>
       </c>
       <c r="W38" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X38" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y38" t="n">
-        <v>7.7</v>
+        <v>5.7</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.93</v>
+        <v>2.25</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="AD38" t="n">
-        <v>3.9</v>
+        <v>4.75</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AH38" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,76 +5558,76 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.66</v>
+        <v>3.29</v>
       </c>
       <c r="M40" t="n">
-        <v>3.63</v>
+        <v>2.94</v>
       </c>
       <c r="N40" t="n">
-        <v>2.47</v>
+        <v>2.1</v>
       </c>
       <c r="O40" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="P40" t="n">
-        <v>12</v>
+        <v>6.5</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="R40" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="T40" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="U40" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="V40" t="n">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W40" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X40" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="Y40" t="n">
-        <v>9.199999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.24</v>
+        <v>1.47</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.36</v>
+        <v>2.6</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.94</v>
+        <v>2.35</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.88</v>
+        <v>1.52</v>
       </c>
       <c r="AD40" t="n">
-        <v>3.08</v>
+        <v>5.2</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AH40" t="n">
-        <v>5.85</v>
+        <v>8.4</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,76 +5822,76 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>

--- a/jogos_2025-08-11.xlsx
+++ b/jogos_2025-08-11.xlsx
@@ -809,10 +809,10 @@
         <v>1.52</v>
       </c>
       <c r="M3" t="n">
-        <v>3.79</v>
+        <v>4.1</v>
       </c>
       <c r="N3" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="O3" t="n">
         <v>1.44</v>
@@ -830,10 +830,10 @@
         <v>2.8</v>
       </c>
       <c r="T3" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="U3" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="V3" t="n">
         <v>6.35</v>
@@ -851,31 +851,31 @@
         <v>1.25</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.6</v>
+        <v>4.02</v>
       </c>
       <c r="AB3" t="n">
         <v>1.82</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AD3" t="n">
         <v>2.88</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AH3" t="n">
         <v>5.1</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
       <c r="M10" t="n">
-        <v>3.75</v>
+        <v>3.23</v>
       </c>
       <c r="N10" t="n">
-        <v>2.5</v>
+        <v>3.68</v>
       </c>
       <c r="O10" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="P10" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.83</v>
       </c>
-      <c r="P10" t="n">
-        <v>17.75</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V10" t="n">
-        <v>5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AH10" t="n">
-        <v>3.7</v>
+        <v>6.8</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="M12" t="n">
-        <v>3.23</v>
+        <v>3.12</v>
       </c>
       <c r="N12" t="n">
-        <v>3.68</v>
+        <v>4.33</v>
       </c>
       <c r="O12" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="P12" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.66</v>
+        <v>2.38</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="T12" t="n">
-        <v>2.94</v>
+        <v>3.5</v>
       </c>
       <c r="U12" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="V12" t="n">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AH12" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>3.12</v>
+        <v>3.65</v>
       </c>
       <c r="N13" t="n">
-        <v>4.33</v>
+        <v>2.5</v>
       </c>
       <c r="O13" t="n">
         <v>1.83</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>17.75</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="S13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V13" t="n">
+        <v>5</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG13" t="n">
         <v>2.5</v>
       </c>
-      <c r="T13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V13" t="n">
-        <v>11</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.64</v>
+        <v>2.69</v>
       </c>
       <c r="M15" t="n">
-        <v>3.26</v>
+        <v>3.56</v>
       </c>
       <c r="N15" t="n">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="O15" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="P15" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="T15" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="U15" t="n">
-        <v>1.32</v>
+        <v>1.55</v>
       </c>
       <c r="V15" t="n">
-        <v>8.4</v>
+        <v>5.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.89</v>
+        <v>4.69</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>1.47</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="AH15" t="n">
-        <v>6.5</v>
+        <v>4.25</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.45</v>
+        <v>1.98</v>
       </c>
       <c r="M17" t="n">
-        <v>3.31</v>
+        <v>3.28</v>
       </c>
       <c r="N17" t="n">
-        <v>1.9</v>
+        <v>3.23</v>
       </c>
       <c r="O17" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U17" t="n">
         <v>1.44</v>
       </c>
       <c r="V17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W17" t="n">
         <v>1.1</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.88</v>
+        <v>3.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="AH17" t="n">
-        <v>5.25</v>
+        <v>6.25</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.72</v>
+        <v>1.39</v>
       </c>
       <c r="M18" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="N18" t="n">
-        <v>2.16</v>
+        <v>5.7</v>
       </c>
       <c r="O18" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="P18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.8</v>
+        <v>2.88</v>
       </c>
       <c r="R18" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="T18" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="U18" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="V18" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="X18" t="n">
         <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.6</v>
+        <v>5.25</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AC18" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AD18" t="n">
         <v>2.15</v>
       </c>
-      <c r="AD18" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AE18" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.41</v>
+        <v>3.9</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.39</v>
+        <v>3.45</v>
       </c>
       <c r="M19" t="n">
-        <v>4.5</v>
+        <v>3.31</v>
       </c>
       <c r="N19" t="n">
-        <v>5.7</v>
+        <v>1.9</v>
       </c>
       <c r="O19" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="P19" t="n">
-        <v>12</v>
+        <v>8.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.88</v>
+        <v>1.91</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="S19" t="n">
-        <v>3.75</v>
+        <v>3.19</v>
       </c>
       <c r="T19" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="U19" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="V19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W19" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AA19" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AH19" t="n">
         <v>5.25</v>
       </c>
-      <c r="AB19" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AI19" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,73 +3050,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.53</v>
+        <v>3.64</v>
       </c>
       <c r="M20" t="n">
-        <v>3.18</v>
+        <v>3.26</v>
       </c>
       <c r="N20" t="n">
-        <v>2.16</v>
+        <v>1.89</v>
       </c>
       <c r="O20" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="P20" t="n">
-        <v>6.55</v>
+        <v>8.5</v>
       </c>
       <c r="Q20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.8</v>
       </c>
-      <c r="R20" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V20" t="n">
-        <v>10</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AH20" t="n">
-        <v>11</v>
+        <v>6.5</v>
       </c>
       <c r="AI20" t="n">
         <v>1.02</v>
@@ -3146,22 +3146,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,76 +3182,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.98</v>
+        <v>3.53</v>
       </c>
       <c r="M21" t="n">
-        <v>3.28</v>
+        <v>3.18</v>
       </c>
       <c r="N21" t="n">
-        <v>3.23</v>
+        <v>2.16</v>
       </c>
       <c r="O21" t="n">
-        <v>1.73</v>
+        <v>2.53</v>
       </c>
       <c r="P21" t="n">
-        <v>9</v>
+        <v>6.55</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>2.36</v>
       </c>
       <c r="T21" t="n">
-        <v>2.63</v>
+        <v>3.66</v>
       </c>
       <c r="U21" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="V21" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W21" t="n">
+        <v>1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AE21" t="n">
         <v>1.1</v>
       </c>
-      <c r="X21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AF21" t="n">
-        <v>1.7</v>
+        <v>2.17</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.05</v>
+        <v>1.61</v>
       </c>
       <c r="AH21" t="n">
-        <v>6.25</v>
+        <v>11</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="M22" t="n">
         <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="O22" t="n">
         <v>1.75</v>
@@ -3332,28 +3332,28 @@
         <v>2.3</v>
       </c>
       <c r="R22" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S22" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="T22" t="n">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="U22" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="V22" t="n">
         <v>5.25</v>
       </c>
       <c r="W22" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Z22" t="n">
         <v>1.22</v>
@@ -3362,10 +3362,10 @@
         <v>4.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AD22" t="n">
         <v>2.5</v>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,76 +3710,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.77</v>
+        <v>3.6</v>
       </c>
       <c r="N25" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="O25" t="n">
         <v>2.1</v>
       </c>
       <c r="P25" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Q25" t="n">
         <v>1.73</v>
       </c>
       <c r="R25" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="T25" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="U25" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="V25" t="n">
-        <v>4.8</v>
+        <v>5.05</v>
       </c>
       <c r="W25" t="n">
         <v>1.15</v>
       </c>
       <c r="X25" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Z25" t="n">
         <v>1.15</v>
       </c>
       <c r="AA25" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.35</v>
+        <v>2.44</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.49</v>
+        <v>2.65</v>
       </c>
       <c r="AH25" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3845,73 +3845,73 @@
         <v>3.25</v>
       </c>
       <c r="M26" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="N26" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O26" t="n">
         <v>2.1</v>
       </c>
       <c r="P26" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Q26" t="n">
         <v>1.73</v>
       </c>
       <c r="R26" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S26" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T26" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="U26" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="V26" t="n">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AA26" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AF26" t="n">
         <v>1.44</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.63</v>
+        <v>2.49</v>
       </c>
       <c r="AH26" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="M28" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N28" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="O28" t="n">
         <v>1.73</v>
@@ -4124,19 +4124,19 @@
         <v>2.63</v>
       </c>
       <c r="R28" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="S28" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="T28" t="n">
         <v>3.07</v>
       </c>
       <c r="U28" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="V28" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="W28" t="n">
         <v>1</v>
@@ -4145,7 +4145,7 @@
         <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>6.5</v>
+        <v>7.3</v>
       </c>
       <c r="Z28" t="n">
         <v>1.42</v>
@@ -4154,10 +4154,10 @@
         <v>2.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.3</v>
+        <v>2.59</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AD28" t="n">
         <v>4.94</v>
@@ -4166,10 +4166,10 @@
         <v>1.15</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AH28" t="n">
         <v>8.800000000000001</v>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,76 +4238,76 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.53</v>
+        <v>1.19</v>
       </c>
       <c r="M29" t="n">
-        <v>3.9</v>
+        <v>6</v>
       </c>
       <c r="N29" t="n">
-        <v>4.75</v>
+        <v>12.25</v>
       </c>
       <c r="O29" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="P29" t="n">
-        <v>10.5</v>
+        <v>15.25</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.75</v>
+        <v>4.65</v>
       </c>
       <c r="R29" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="S29" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="T29" t="n">
-        <v>2.63</v>
+        <v>2.19</v>
       </c>
       <c r="U29" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="V29" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="W29" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X29" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>9.5</v>
+        <v>19</v>
       </c>
       <c r="Z29" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AI29" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1.14</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.19</v>
+        <v>1.53</v>
       </c>
       <c r="M30" t="n">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="N30" t="n">
-        <v>12.25</v>
+        <v>4.75</v>
       </c>
       <c r="O30" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="P30" t="n">
-        <v>15.25</v>
+        <v>10.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.65</v>
+        <v>2.75</v>
       </c>
       <c r="R30" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="S30" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="T30" t="n">
-        <v>2.19</v>
+        <v>2.63</v>
       </c>
       <c r="U30" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="V30" t="n">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="W30" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AI30" t="n">
         <v>1.14</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>1.25</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.5</v>
+        <v>1.49</v>
       </c>
       <c r="M33" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="N33" t="n">
-        <v>2.6</v>
+        <v>5.23</v>
       </c>
       <c r="O33" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S33" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="T33" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U33" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="V33" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="W33" t="n">
         <v>1.2</v>
       </c>
       <c r="X33" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y33" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AA33" t="n">
         <v>5.5</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.7</v>
+        <v>1.37</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.15</v>
+        <v>2.67</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.69</v>
+        <v>2.45</v>
       </c>
       <c r="AH33" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="M34" t="n">
-        <v>4.3</v>
+        <v>4.14</v>
       </c>
       <c r="N34" t="n">
-        <v>4.6</v>
+        <v>3.38</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R34" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S34" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="T34" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U34" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="V34" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="W34" t="n">
         <v>1.2</v>
       </c>
       <c r="X34" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>17.5</v>
+        <v>10</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AA34" t="n">
         <v>5.5</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="AH34" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="M37" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N37" t="n">
-        <v>3.4</v>
+        <v>3.16</v>
       </c>
       <c r="O37" t="n">
         <v>1.73</v>
@@ -5312,22 +5312,22 @@
         <v>2.4</v>
       </c>
       <c r="R37" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="S37" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="T37" t="n">
         <v>3</v>
       </c>
       <c r="U37" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="V37" t="n">
         <v>8.25</v>
       </c>
       <c r="W37" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X37" t="n">
         <v>1.05</v>
@@ -5336,22 +5336,22 @@
         <v>7.7</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AA37" t="n">
         <v>2.93</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AD37" t="n">
         <v>3.9</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AF37" t="n">
         <v>1.88</v>
@@ -5363,7 +5363,7 @@
         <v>8.4</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -5447,10 +5447,10 @@
         <v>1.61</v>
       </c>
       <c r="S38" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="T38" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="U38" t="n">
         <v>1.24</v>
@@ -5459,7 +5459,7 @@
         <v>10</v>
       </c>
       <c r="W38" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X38" t="n">
         <v>1.1</v>
@@ -5468,16 +5468,16 @@
         <v>5.7</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AB38" t="n">
         <v>2.62</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AD38" t="n">
         <v>4.75</v>
@@ -5489,7 +5489,7 @@
         <v>2.1</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AH38" t="n">
         <v>10</v>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,76 +5558,76 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.29</v>
+        <v>2.66</v>
       </c>
       <c r="M40" t="n">
-        <v>2.94</v>
+        <v>3.63</v>
       </c>
       <c r="N40" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O40" t="n">
+        <v>2</v>
+      </c>
+      <c r="P40" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V40" t="n">
+        <v>7</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG40" t="n">
         <v>2.1</v>
       </c>
-      <c r="O40" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P40" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S40" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T40" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V40" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X40" t="n">
+      <c r="AH40" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="AI40" t="n">
         <v>1.07</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>1.05</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,76 +5822,76 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="M43" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="N43" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="O43" t="n">
         <v>1.8</v>
@@ -6107,7 +6107,7 @@
         <v>1.6</v>
       </c>
       <c r="S43" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="T43" t="n">
         <v>3.86</v>
@@ -6116,10 +6116,10 @@
         <v>1.2</v>
       </c>
       <c r="V43" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="W43" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X43" t="n">
         <v>1.13</v>
@@ -6128,19 +6128,19 @@
         <v>5.5</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AD43" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="AE43" t="n">
         <v>1.11</v>
@@ -6152,7 +6152,7 @@
         <v>1.53</v>
       </c>
       <c r="AH43" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AI43" t="n">
         <v>1.03</v>
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="M44" t="n">
-        <v>2.83</v>
+        <v>2.98</v>
       </c>
       <c r="N44" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="O44" t="n">
         <v>1.91</v>
@@ -6242,16 +6242,16 @@
         <v>2.35</v>
       </c>
       <c r="T44" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="U44" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="V44" t="n">
         <v>11</v>
       </c>
       <c r="W44" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X44" t="n">
         <v>1.1</v>
@@ -6260,25 +6260,25 @@
         <v>7</v>
       </c>
       <c r="Z44" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AC44" t="n">
         <v>1.5</v>
       </c>
-      <c r="AA44" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AD44" t="n">
-        <v>4.9</v>
+        <v>4.75</v>
       </c>
       <c r="AE44" t="n">
         <v>1.15</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AG44" t="n">
         <v>1.7</v>

--- a/jogos_2025-08-11.xlsx
+++ b/jogos_2025-08-11.xlsx
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Renofa Yamaguchi</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.35</v>
+        <v>1.59</v>
       </c>
       <c r="M4" t="n">
-        <v>2.8</v>
+        <v>3.82</v>
       </c>
       <c r="N4" t="n">
-        <v>2.96</v>
+        <v>4.4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.98</v>
+        <v>1.5</v>
       </c>
       <c r="P4" t="n">
-        <v>6.55</v>
+        <v>9.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.18</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="T4" t="n">
-        <v>3.6</v>
+        <v>2.65</v>
       </c>
       <c r="U4" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="V4" t="n">
-        <v>11</v>
+        <v>6.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X4" t="n">
         <v>1.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.55</v>
+        <v>9.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.45</v>
+        <v>1.76</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.48</v>
+        <v>1.94</v>
       </c>
       <c r="AD4" t="n">
-        <v>4.95</v>
+        <v>3.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AH4" t="n">
-        <v>9</v>
+        <v>5.75</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Renofa Yamaguchi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.59</v>
+        <v>2.35</v>
       </c>
       <c r="M5" t="n">
-        <v>3.82</v>
+        <v>2.8</v>
       </c>
       <c r="N5" t="n">
-        <v>4.4</v>
+        <v>2.96</v>
       </c>
       <c r="O5" t="n">
-        <v>1.5</v>
+        <v>1.98</v>
       </c>
       <c r="P5" t="n">
-        <v>9.5</v>
+        <v>6.55</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>2.18</v>
       </c>
       <c r="R5" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="S5" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="T5" t="n">
-        <v>2.65</v>
+        <v>3.6</v>
       </c>
       <c r="U5" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="V5" t="n">
-        <v>6.5</v>
+        <v>11</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X5" t="n">
         <v>1.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.5</v>
+        <v>6.55</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.76</v>
+        <v>2.45</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.94</v>
+        <v>1.48</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.1</v>
+        <v>4.95</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AH5" t="n">
-        <v>5.75</v>
+        <v>9</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kudrivka</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,40 +1334,40 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1394,10 +1394,10 @@
         <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
         <v>0</v>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Kudrivka</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,40 +1466,40 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1526,10 +1526,10 @@
         <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH8" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="M10" t="n">
-        <v>3.23</v>
+        <v>3.12</v>
       </c>
       <c r="N10" t="n">
-        <v>3.68</v>
+        <v>4.33</v>
       </c>
       <c r="O10" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="P10" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.66</v>
+        <v>2.38</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="T10" t="n">
-        <v>2.94</v>
+        <v>3.5</v>
       </c>
       <c r="U10" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="V10" t="n">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AH10" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>17.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,40 +1994,40 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2054,10 +2054,10 @@
         <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>17.75</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.69</v>
+        <v>3.64</v>
       </c>
       <c r="M15" t="n">
-        <v>3.56</v>
+        <v>3.26</v>
       </c>
       <c r="N15" t="n">
-        <v>2.3</v>
+        <v>1.89</v>
       </c>
       <c r="O15" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="P15" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="Q15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.8</v>
       </c>
-      <c r="R15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AH15" t="n">
-        <v>4.25</v>
+        <v>6.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.98</v>
+        <v>1.39</v>
       </c>
       <c r="M17" t="n">
-        <v>3.28</v>
+        <v>4.5</v>
       </c>
       <c r="N17" t="n">
-        <v>3.23</v>
+        <v>5.7</v>
       </c>
       <c r="O17" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="P17" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="T17" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="V17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.5</v>
+        <v>5.25</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.25</v>
+        <v>2.15</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.35</v>
+        <v>1.62</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="n">
-        <v>6.25</v>
+        <v>3.9</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.39</v>
+        <v>2.1</v>
       </c>
       <c r="M18" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>5.7</v>
+        <v>3.2</v>
       </c>
       <c r="O18" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="P18" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="R18" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S18" t="n">
-        <v>3.75</v>
+        <v>3.28</v>
       </c>
       <c r="T18" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="U18" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="V18" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="W18" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.25</v>
+        <v>4.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.62</v>
+        <v>1.42</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.45</v>
+        <v>3.57</v>
       </c>
       <c r="M19" t="n">
-        <v>3.31</v>
+        <v>3.15</v>
       </c>
       <c r="N19" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="O19" t="n">
-        <v>2</v>
+        <v>2.53</v>
       </c>
       <c r="P19" t="n">
-        <v>8.5</v>
+        <v>6.55</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="R19" t="n">
-        <v>1.32</v>
+        <v>1.55</v>
       </c>
       <c r="S19" t="n">
-        <v>3.19</v>
+        <v>2.36</v>
       </c>
       <c r="T19" t="n">
-        <v>2.62</v>
+        <v>3.66</v>
       </c>
       <c r="U19" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="V19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
         <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.5</v>
+        <v>6.55</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.58</v>
+        <v>2.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.02</v>
+        <v>1.42</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.9</v>
+        <v>5.05</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.38</v>
+        <v>1.1</v>
       </c>
       <c r="AF19" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AG19" t="n">
         <v>1.61</v>
       </c>
-      <c r="AG19" t="n">
-        <v>2.16</v>
-      </c>
       <c r="AH19" t="n">
-        <v>5.25</v>
+        <v>11</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.64</v>
+        <v>3.45</v>
       </c>
       <c r="M20" t="n">
-        <v>3.26</v>
+        <v>3.31</v>
       </c>
       <c r="N20" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="O20" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="P20" t="n">
         <v>8.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="R20" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="S20" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="T20" t="n">
         <v>2.62</v>
       </c>
-      <c r="T20" t="n">
-        <v>3.1</v>
-      </c>
       <c r="U20" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="V20" t="n">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="W20" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="X20" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.89</v>
+        <v>3.58</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.65</v>
+        <v>2.02</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.8</v>
+        <v>2.16</v>
       </c>
       <c r="AH20" t="n">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,76 +3182,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.53</v>
+        <v>2.69</v>
       </c>
       <c r="M21" t="n">
-        <v>3.18</v>
+        <v>3.56</v>
       </c>
       <c r="N21" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="O21" t="n">
-        <v>2.53</v>
+        <v>2</v>
       </c>
       <c r="P21" t="n">
-        <v>6.55</v>
+        <v>10</v>
       </c>
       <c r="Q21" t="n">
         <v>1.8</v>
       </c>
       <c r="R21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U21" t="n">
         <v>1.55</v>
       </c>
-      <c r="S21" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.22</v>
-      </c>
       <c r="V21" t="n">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="X21" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>6.55</v>
+        <v>12.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.53</v>
+        <v>1.15</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.44</v>
+        <v>4.69</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.5</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.42</v>
+        <v>2.25</v>
       </c>
       <c r="AD21" t="n">
-        <v>5.05</v>
+        <v>2.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.1</v>
+        <v>1.47</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.17</v>
+        <v>1.47</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.61</v>
+        <v>2.4</v>
       </c>
       <c r="AH21" t="n">
-        <v>11</v>
+        <v>4.25</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3278,22 +3278,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="M22" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="N22" t="n">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="O22" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="P22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q22" t="n">
         <v>2.3</v>
       </c>
       <c r="R22" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="S22" t="n">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="T22" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="U22" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="V22" t="n">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="W22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AI22" t="n">
         <v>1.12</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1.19</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,76 +3578,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,76 +3842,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,73 +5294,73 @@
         </is>
       </c>
       <c r="L37" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M37" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O37" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P37" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V37" t="n">
+        <v>10</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF37" t="n">
         <v>2.1</v>
       </c>
-      <c r="M37" t="n">
-        <v>3</v>
-      </c>
-      <c r="N37" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="O37" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="P37" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T37" t="n">
-        <v>3</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V37" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AG37" t="n">
-        <v>1.77</v>
+        <v>1.59</v>
       </c>
       <c r="AH37" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AI37" t="n">
         <v>1.04</v>
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,73 +5426,73 @@
         </is>
       </c>
       <c r="L38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3</v>
+      </c>
+      <c r="N38" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="P38" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Q38" t="n">
         <v>2.4</v>
       </c>
-      <c r="M38" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N38" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O38" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="P38" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2.2</v>
-      </c>
       <c r="R38" t="n">
-        <v>1.61</v>
+        <v>1.42</v>
       </c>
       <c r="S38" t="n">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="T38" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="U38" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="V38" t="n">
-        <v>10</v>
+        <v>8.25</v>
       </c>
       <c r="W38" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X38" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y38" t="n">
-        <v>5.7</v>
+        <v>7.7</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.54</v>
+        <v>1.34</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.3</v>
+        <v>2.93</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="AD38" t="n">
-        <v>4.75</v>
+        <v>3.9</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.59</v>
+        <v>1.77</v>
       </c>
       <c r="AH38" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AI38" t="n">
         <v>1.04</v>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,76 +5558,76 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.66</v>
+        <v>3.5</v>
       </c>
       <c r="M40" t="n">
-        <v>3.63</v>
+        <v>3.16</v>
       </c>
       <c r="N40" t="n">
-        <v>2.47</v>
+        <v>2.12</v>
       </c>
       <c r="O40" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="P40" t="n">
-        <v>12</v>
+        <v>6.5</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="R40" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="T40" t="n">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="U40" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="V40" t="n">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W40" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X40" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="Y40" t="n">
-        <v>9.199999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.24</v>
+        <v>1.49</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.36</v>
+        <v>2.5</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.94</v>
+        <v>2.45</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="AD40" t="n">
-        <v>3.08</v>
+        <v>5.1</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.67</v>
+        <v>2.08</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="AH40" t="n">
-        <v>5.85</v>
+        <v>8.4</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,76 +5822,76 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>

--- a/jogos_2025-08-11.xlsx
+++ b/jogos_2025-08-11.xlsx
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.64</v>
+        <v>4.2</v>
       </c>
       <c r="M15" t="n">
-        <v>3.26</v>
+        <v>3.47</v>
       </c>
       <c r="N15" t="n">
-        <v>1.89</v>
+        <v>1.69</v>
       </c>
       <c r="O15" t="n">
         <v>2.5</v>
@@ -2408,22 +2408,22 @@
         <v>1.67</v>
       </c>
       <c r="R15" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="T15" t="n">
         <v>3.1</v>
       </c>
       <c r="U15" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
         <v>1.06</v>
@@ -2432,25 +2432,25 @@
         <v>8</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AG15" t="n">
         <v>1.8</v>
@@ -2459,7 +2459,7 @@
         <v>6.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.96</v>
+        <v>3.57</v>
       </c>
       <c r="M16" t="n">
-        <v>3.42</v>
+        <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="O16" t="n">
-        <v>1.73</v>
+        <v>2.53</v>
       </c>
       <c r="P16" t="n">
-        <v>12.5</v>
+        <v>6.55</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="S16" t="n">
-        <v>3.05</v>
+        <v>2.36</v>
       </c>
       <c r="T16" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V16" t="n">
+        <v>10</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB16" t="n">
         <v>2.5</v>
       </c>
-      <c r="U16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V16" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AC16" t="n">
-        <v>1.97</v>
+        <v>1.42</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.94</v>
+        <v>5.05</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.37</v>
+        <v>1.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.63</v>
+        <v>2.17</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.1</v>
+        <v>1.61</v>
       </c>
       <c r="AH16" t="n">
-        <v>4.9</v>
+        <v>11</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.39</v>
+        <v>3.45</v>
       </c>
       <c r="M17" t="n">
-        <v>4.5</v>
+        <v>3.31</v>
       </c>
       <c r="N17" t="n">
-        <v>5.7</v>
+        <v>1.9</v>
       </c>
       <c r="O17" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="P17" t="n">
-        <v>12</v>
+        <v>8.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.88</v>
+        <v>1.91</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="U17" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="V17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W17" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AA17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AH17" t="n">
         <v>5.25</v>
       </c>
-      <c r="AB17" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AI17" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="M18" t="n">
         <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>3.2</v>
+        <v>2.91</v>
       </c>
       <c r="O18" t="n">
         <v>1.75</v>
@@ -2804,22 +2804,22 @@
         <v>2.3</v>
       </c>
       <c r="R18" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="T18" t="n">
         <v>2.3</v>
       </c>
       <c r="U18" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="V18" t="n">
         <v>5.25</v>
       </c>
       <c r="W18" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
         <v>1.03</v>
@@ -2834,10 +2834,10 @@
         <v>4.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AD18" t="n">
         <v>2.5</v>
@@ -2846,7 +2846,7 @@
         <v>1.42</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG18" t="n">
         <v>2.3</v>
@@ -2855,7 +2855,7 @@
         <v>4</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.57</v>
+        <v>2.07</v>
       </c>
       <c r="M19" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="P19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG19" t="n">
         <v>2.1</v>
       </c>
-      <c r="O19" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="P19" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V19" t="n">
-        <v>10</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AH19" t="n">
-        <v>11</v>
+        <v>5.2</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.45</v>
+        <v>1.98</v>
       </c>
       <c r="M20" t="n">
-        <v>3.31</v>
+        <v>3.28</v>
       </c>
       <c r="N20" t="n">
-        <v>1.9</v>
+        <v>3.23</v>
       </c>
       <c r="O20" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="P20" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S20" t="n">
-        <v>3.19</v>
+        <v>3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="U20" t="n">
         <v>1.44</v>
       </c>
       <c r="V20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W20" t="n">
         <v>1.1</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y20" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AB20" t="n">
         <v>1.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="AH20" t="n">
-        <v>5.25</v>
+        <v>6.25</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.98</v>
+        <v>1.39</v>
       </c>
       <c r="M22" t="n">
-        <v>3.28</v>
+        <v>4.5</v>
       </c>
       <c r="N22" t="n">
-        <v>3.23</v>
+        <v>5.7</v>
       </c>
       <c r="O22" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="P22" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="R22" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="T22" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="U22" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="V22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X22" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.5</v>
+        <v>5.25</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.25</v>
+        <v>2.15</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.35</v>
+        <v>1.62</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH22" t="n">
-        <v>6.25</v>
+        <v>3.9</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,76 +3578,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,76 +3710,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="M25" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="N25" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="O25" t="n">
         <v>2.1</v>
       </c>
       <c r="P25" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Q25" t="n">
         <v>1.73</v>
       </c>
       <c r="R25" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S25" t="n">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="T25" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="U25" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="V25" t="n">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Z25" t="n">
         <v>1.15</v>
       </c>
       <c r="AA25" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.65</v>
+        <v>2.49</v>
       </c>
       <c r="AH25" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,76 +3842,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.53</v>
+        <v>3.12</v>
       </c>
       <c r="M30" t="n">
-        <v>3.9</v>
+        <v>2.91</v>
       </c>
       <c r="N30" t="n">
-        <v>4.75</v>
+        <v>2.19</v>
       </c>
       <c r="O30" t="n">
-        <v>1.5</v>
+        <v>2.38</v>
       </c>
       <c r="P30" t="n">
-        <v>10.5</v>
+        <v>7.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="R30" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U30" t="n">
         <v>1.33</v>
       </c>
-      <c r="S30" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.44</v>
-      </c>
       <c r="V30" t="n">
-        <v>6.5</v>
+        <v>7.4</v>
       </c>
       <c r="W30" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X30" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y30" t="n">
-        <v>9.5</v>
+        <v>7.3</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.8</v>
+        <v>2.84</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.05</v>
+        <v>1.55</v>
       </c>
       <c r="AD30" t="n">
-        <v>3</v>
+        <v>3.52</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH30" t="n">
-        <v>5.5</v>
+        <v>6.85</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.12</v>
+        <v>1.53</v>
       </c>
       <c r="M31" t="n">
-        <v>2.91</v>
+        <v>3.9</v>
       </c>
       <c r="N31" t="n">
-        <v>2.19</v>
+        <v>4.75</v>
       </c>
       <c r="O31" t="n">
-        <v>2.38</v>
+        <v>1.5</v>
       </c>
       <c r="P31" t="n">
-        <v>7.3</v>
+        <v>10.5</v>
       </c>
       <c r="Q31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V31" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF31" t="n">
         <v>1.83</v>
       </c>
-      <c r="R31" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V31" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AG31" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH31" t="n">
-        <v>6.85</v>
+        <v>5.5</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.49</v>
+        <v>1.8</v>
       </c>
       <c r="M33" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V33" t="n">
         <v>4.33</v>
-      </c>
-      <c r="N33" t="n">
-        <v>5.23</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S33" t="n">
-        <v>4</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V33" t="n">
-        <v>4</v>
       </c>
       <c r="W33" t="n">
         <v>1.2</v>
       </c>
       <c r="X33" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y33" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AA33" t="n">
         <v>5.5</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.67</v>
+        <v>2.05</v>
       </c>
       <c r="AD33" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.45</v>
+        <v>2.69</v>
       </c>
       <c r="AH33" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.8</v>
+        <v>1.49</v>
       </c>
       <c r="M34" t="n">
-        <v>4.14</v>
+        <v>4.33</v>
       </c>
       <c r="N34" t="n">
-        <v>3.38</v>
+        <v>5.23</v>
       </c>
       <c r="O34" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S34" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="T34" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U34" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="V34" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="W34" t="n">
         <v>1.2</v>
       </c>
       <c r="X34" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y34" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AA34" t="n">
         <v>5.5</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.05</v>
+        <v>2.67</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.69</v>
+        <v>2.45</v>
       </c>
       <c r="AH34" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,76 +5294,76 @@
         </is>
       </c>
       <c r="L37" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M37" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N37" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="P37" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Q37" t="n">
         <v>2.4</v>
       </c>
-      <c r="M37" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N37" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O37" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="P37" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>2.2</v>
-      </c>
       <c r="R37" t="n">
-        <v>1.61</v>
+        <v>1.42</v>
       </c>
       <c r="S37" t="n">
-        <v>2.28</v>
+        <v>2.55</v>
       </c>
       <c r="T37" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="U37" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="V37" t="n">
-        <v>10</v>
+        <v>8.25</v>
       </c>
       <c r="W37" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AI37" t="n">
         <v>1.03</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>1.04</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,73 +5426,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="M38" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="N38" t="n">
-        <v>3.16</v>
+        <v>2.8</v>
       </c>
       <c r="O38" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="P38" t="n">
-        <v>7.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="R38" t="n">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="S38" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="T38" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="U38" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="V38" t="n">
-        <v>8.25</v>
+        <v>10</v>
       </c>
       <c r="W38" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X38" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y38" t="n">
-        <v>7.7</v>
+        <v>6.1</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.34</v>
+        <v>1.53</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.93</v>
+        <v>2.25</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.15</v>
+        <v>2.62</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="AD38" t="n">
-        <v>3.9</v>
+        <v>4.75</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.88</v>
+        <v>2.16</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.77</v>
+        <v>1.58</v>
       </c>
       <c r="AH38" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AI38" t="n">
         <v>1.04</v>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.5</v>
+        <v>2.66</v>
       </c>
       <c r="M40" t="n">
-        <v>3.16</v>
+        <v>3.63</v>
       </c>
       <c r="N40" t="n">
-        <v>2.12</v>
+        <v>2.47</v>
       </c>
       <c r="O40" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="P40" t="n">
-        <v>6.5</v>
+        <v>12</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="R40" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="S40" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="T40" t="n">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="U40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V40" t="n">
+        <v>7</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AE40" t="n">
         <v>1.28</v>
       </c>
-      <c r="V40" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X40" t="n">
+      <c r="AF40" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="AI40" t="n">
         <v>1.07</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>1.02</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,76 +5822,76 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.66</v>
+        <v>3.29</v>
       </c>
       <c r="M41" t="n">
-        <v>3.63</v>
+        <v>2.94</v>
       </c>
       <c r="N41" t="n">
-        <v>2.47</v>
+        <v>2.1</v>
       </c>
       <c r="O41" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="P41" t="n">
-        <v>12</v>
+        <v>6.5</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="R41" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="T41" t="n">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="U41" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="V41" t="n">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W41" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X41" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="Y41" t="n">
-        <v>9.199999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.24</v>
+        <v>1.47</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.36</v>
+        <v>2.6</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.94</v>
+        <v>2.35</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.88</v>
+        <v>1.52</v>
       </c>
       <c r="AD41" t="n">
-        <v>3.08</v>
+        <v>5.1</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.67</v>
+        <v>2.08</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.1</v>
+        <v>1.69</v>
       </c>
       <c r="AH41" t="n">
-        <v>5.85</v>
+        <v>8.4</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.34</v>
+        <v>2.22</v>
       </c>
       <c r="M44" t="n">
-        <v>2.98</v>
+        <v>2.83</v>
       </c>
       <c r="N44" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="O44" t="n">
         <v>1.91</v>
@@ -6245,49 +6245,49 @@
         <v>3.45</v>
       </c>
       <c r="U44" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="V44" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W44" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X44" t="n">
         <v>1.1</v>
       </c>
       <c r="Y44" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.59</v>
+        <v>2.4</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.55</v>
+        <v>2.37</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AD44" t="n">
-        <v>4.75</v>
+        <v>4.9</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AH44" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AI44" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>

--- a/jogos_2025-08-11.xlsx
+++ b/jogos_2025-08-11.xlsx
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="M10" t="n">
-        <v>3.12</v>
+        <v>3.65</v>
       </c>
       <c r="N10" t="n">
-        <v>4.33</v>
+        <v>2.5</v>
       </c>
       <c r="O10" t="n">
         <v>1.83</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>17.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V10" t="n">
+        <v>5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG10" t="n">
         <v>2.5</v>
       </c>
-      <c r="T10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V10" t="n">
-        <v>11</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="M11" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="P11" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.83</v>
       </c>
-      <c r="P11" t="n">
-        <v>17.75</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V11" t="n">
-        <v>5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AH11" t="n">
-        <v>3.7</v>
+        <v>6.8</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="M13" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T13" t="n">
         <v>3.5</v>
       </c>
-      <c r="N13" t="n">
-        <v>5</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="P13" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.94</v>
-      </c>
       <c r="U13" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="V13" t="n">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
         <v>2</v>
       </c>
-      <c r="AC13" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AG13" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AH13" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.57</v>
+        <v>2.04</v>
       </c>
       <c r="M16" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>2.1</v>
+        <v>2.91</v>
       </c>
       <c r="O16" t="n">
-        <v>2.53</v>
+        <v>1.75</v>
       </c>
       <c r="P16" t="n">
-        <v>6.55</v>
+        <v>10</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="R16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V16" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF16" t="n">
         <v>1.55</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V16" t="n">
-        <v>10</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.17</v>
-      </c>
       <c r="AG16" t="n">
-        <v>1.61</v>
+        <v>2.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.45</v>
+        <v>2.07</v>
       </c>
       <c r="M17" t="n">
-        <v>3.31</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>1.9</v>
+        <v>3.05</v>
       </c>
       <c r="O17" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="P17" t="n">
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="R17" t="n">
         <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="T17" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="U17" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="V17" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="W17" t="n">
         <v>1.1</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>8.5</v>
+        <v>9.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="n">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.04</v>
+        <v>3.57</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>2.91</v>
+        <v>2.1</v>
       </c>
       <c r="O18" t="n">
-        <v>1.75</v>
+        <v>2.53</v>
       </c>
       <c r="P18" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V18" t="n">
         <v>10</v>
       </c>
-      <c r="Q18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V18" t="n">
-        <v>5.25</v>
-      </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>15</v>
+        <v>6.55</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.62</v>
+        <v>2.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.3</v>
+        <v>1.42</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.5</v>
+        <v>5.05</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.42</v>
+        <v>1.1</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.55</v>
+        <v>2.17</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.3</v>
+        <v>1.61</v>
       </c>
       <c r="AH18" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.07</v>
+        <v>1.39</v>
       </c>
       <c r="M19" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="N19" t="n">
-        <v>3.05</v>
+        <v>5.7</v>
       </c>
       <c r="O19" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="P19" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="R19" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="T19" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="U19" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="V19" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>9.1</v>
+        <v>11</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.7</v>
+        <v>5.25</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.96</v>
+        <v>2.15</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.37</v>
+        <v>1.62</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG19" t="n">
         <v>2.1</v>
       </c>
       <c r="AH19" t="n">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.98</v>
+        <v>3.45</v>
       </c>
       <c r="M20" t="n">
-        <v>3.28</v>
+        <v>3.31</v>
       </c>
       <c r="N20" t="n">
-        <v>3.23</v>
+        <v>1.9</v>
       </c>
       <c r="O20" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="P20" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="R20" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T20" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="U20" t="n">
         <v>1.44</v>
       </c>
       <c r="V20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W20" t="n">
         <v>1.1</v>
       </c>
       <c r="X20" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="AH20" t="n">
-        <v>6.25</v>
+        <v>5.25</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.39</v>
+        <v>1.98</v>
       </c>
       <c r="M22" t="n">
-        <v>4.5</v>
+        <v>3.28</v>
       </c>
       <c r="N22" t="n">
-        <v>5.7</v>
+        <v>3.23</v>
       </c>
       <c r="O22" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="P22" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="S22" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="T22" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="U22" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="V22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W22" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y22" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>5.25</v>
+        <v>3.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.18</v>
+        <v>1.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.15</v>
+        <v>3.25</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH22" t="n">
-        <v>3.9</v>
+        <v>6.25</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="M25" t="n">
         <v>3.75</v>
       </c>
       <c r="N25" t="n">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="O25" t="n">
         <v>2.1</v>
@@ -3728,7 +3728,7 @@
         <v>1.73</v>
       </c>
       <c r="R25" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S25" t="n">
         <v>3.4</v>
@@ -3737,19 +3737,19 @@
         <v>2.25</v>
       </c>
       <c r="U25" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="V25" t="n">
-        <v>5</v>
+        <v>5.35</v>
       </c>
       <c r="W25" t="n">
         <v>1.1</v>
       </c>
       <c r="X25" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Z25" t="n">
         <v>1.15</v>
@@ -3761,13 +3761,13 @@
         <v>1.56</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.41</v>
+        <v>2.48</v>
       </c>
       <c r="AD25" t="n">
         <v>2.35</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AF25" t="n">
         <v>1.44</v>
@@ -3779,7 +3779,7 @@
         <v>4.2</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,76 +3842,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,76 +3974,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,76 +4238,76 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.19</v>
+        <v>1.53</v>
       </c>
       <c r="M29" t="n">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="N29" t="n">
-        <v>12.25</v>
+        <v>4.75</v>
       </c>
       <c r="O29" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="P29" t="n">
-        <v>15.25</v>
+        <v>10.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.65</v>
+        <v>2.75</v>
       </c>
       <c r="R29" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="S29" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="T29" t="n">
-        <v>2.19</v>
+        <v>2.63</v>
       </c>
       <c r="U29" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="V29" t="n">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="W29" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AI29" t="n">
         <v>1.14</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1.25</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.53</v>
+        <v>1.19</v>
       </c>
       <c r="M31" t="n">
-        <v>3.9</v>
+        <v>6</v>
       </c>
       <c r="N31" t="n">
-        <v>4.75</v>
+        <v>12.25</v>
       </c>
       <c r="O31" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="P31" t="n">
-        <v>10.5</v>
+        <v>15.25</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.75</v>
+        <v>4.65</v>
       </c>
       <c r="R31" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="S31" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="T31" t="n">
-        <v>2.63</v>
+        <v>2.19</v>
       </c>
       <c r="U31" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="V31" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="W31" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X31" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y31" t="n">
-        <v>9.5</v>
+        <v>19</v>
       </c>
       <c r="Z31" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AI31" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>1.14</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,34 +4766,34 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="M33" t="n">
-        <v>4.14</v>
+        <v>4.3</v>
       </c>
       <c r="N33" t="n">
-        <v>3.38</v>
+        <v>4.6</v>
       </c>
       <c r="O33" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S33" t="n">
-        <v>3.25</v>
+        <v>3.85</v>
       </c>
       <c r="T33" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U33" t="n">
-        <v>1.44</v>
+        <v>1.76</v>
       </c>
       <c r="V33" t="n">
         <v>4.33</v>
@@ -4802,40 +4802,40 @@
         <v>1.2</v>
       </c>
       <c r="X33" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y33" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AA33" t="n">
         <v>5.5</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.69</v>
+        <v>2.45</v>
       </c>
       <c r="AH33" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.49</v>
+        <v>2.5</v>
       </c>
       <c r="M34" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V34" t="n">
         <v>4.33</v>
-      </c>
-      <c r="N34" t="n">
-        <v>5.23</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S34" t="n">
-        <v>4</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V34" t="n">
-        <v>4</v>
       </c>
       <c r="W34" t="n">
         <v>1.2</v>
       </c>
       <c r="X34" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AA34" t="n">
         <v>5.5</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.37</v>
+        <v>1.7</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.67</v>
+        <v>2.15</v>
       </c>
       <c r="AD34" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.45</v>
+        <v>2.69</v>
       </c>
       <c r="AH34" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.66</v>
+        <v>3.29</v>
       </c>
       <c r="M40" t="n">
-        <v>3.63</v>
+        <v>2.94</v>
       </c>
       <c r="N40" t="n">
-        <v>2.47</v>
+        <v>2.1</v>
       </c>
       <c r="O40" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="P40" t="n">
-        <v>12</v>
+        <v>6.5</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="R40" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="T40" t="n">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="U40" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="V40" t="n">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W40" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X40" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="Y40" t="n">
-        <v>9.199999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.24</v>
+        <v>1.47</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.36</v>
+        <v>2.6</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.94</v>
+        <v>2.35</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.88</v>
+        <v>1.52</v>
       </c>
       <c r="AD40" t="n">
-        <v>3.08</v>
+        <v>5.1</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.67</v>
+        <v>2.08</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.1</v>
+        <v>1.69</v>
       </c>
       <c r="AH40" t="n">
-        <v>5.85</v>
+        <v>8.4</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,76 +5822,76 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.29</v>
+        <v>2.66</v>
       </c>
       <c r="M41" t="n">
-        <v>2.94</v>
+        <v>3.63</v>
       </c>
       <c r="N41" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O41" t="n">
+        <v>2</v>
+      </c>
+      <c r="P41" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V41" t="n">
+        <v>7</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG41" t="n">
         <v>2.1</v>
       </c>
-      <c r="O41" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P41" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S41" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T41" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V41" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X41" t="n">
+      <c r="AH41" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="AI41" t="n">
         <v>1.07</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>1.02</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="M43" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="N43" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="O43" t="n">
         <v>1.8</v>
@@ -6104,19 +6104,19 @@
         <v>2.5</v>
       </c>
       <c r="R43" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="S43" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="T43" t="n">
-        <v>3.86</v>
+        <v>3.5</v>
       </c>
       <c r="U43" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="V43" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="W43" t="n">
         <v>1.03</v>
@@ -6128,16 +6128,16 @@
         <v>5.5</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AD43" t="n">
         <v>5</v>
@@ -6146,16 +6146,16 @@
         <v>1.11</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AH43" t="n">
         <v>11</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>

--- a/jogos_2025-08-11.xlsx
+++ b/jogos_2025-08-11.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL44"/>
+  <dimension ref="A1:AL45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -806,13 +806,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="M3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="N3" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="O3" t="n">
         <v>1.44</v>
@@ -830,10 +830,10 @@
         <v>2.8</v>
       </c>
       <c r="T3" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="U3" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="V3" t="n">
         <v>6.35</v>
@@ -842,19 +842,19 @@
         <v>1.06</v>
       </c>
       <c r="X3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>12</v>
+        <v>11.4</v>
       </c>
       <c r="Z3" t="n">
         <v>1.25</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.02</v>
+        <v>3.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AC3" t="n">
         <v>2</v>
@@ -866,16 +866,16 @@
         <v>1.35</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AH3" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Renofa Yamaguchi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.59</v>
+        <v>2.35</v>
       </c>
       <c r="M4" t="n">
-        <v>3.82</v>
+        <v>2.8</v>
       </c>
       <c r="N4" t="n">
-        <v>4.4</v>
+        <v>2.96</v>
       </c>
       <c r="O4" t="n">
-        <v>1.5</v>
+        <v>1.98</v>
       </c>
       <c r="P4" t="n">
-        <v>9.5</v>
+        <v>6.55</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>2.18</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="S4" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="T4" t="n">
-        <v>2.65</v>
+        <v>3.6</v>
       </c>
       <c r="U4" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="V4" t="n">
-        <v>6.5</v>
+        <v>11</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X4" t="n">
         <v>1.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.5</v>
+        <v>6.55</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.76</v>
+        <v>2.45</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.94</v>
+        <v>1.48</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.1</v>
+        <v>4.95</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AH4" t="n">
-        <v>5.75</v>
+        <v>9</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Renofa Yamaguchi</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.35</v>
+        <v>1.59</v>
       </c>
       <c r="M5" t="n">
-        <v>2.8</v>
+        <v>3.82</v>
       </c>
       <c r="N5" t="n">
-        <v>2.96</v>
+        <v>4.4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.98</v>
+        <v>1.5</v>
       </c>
       <c r="P5" t="n">
-        <v>6.55</v>
+        <v>9.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.18</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="T5" t="n">
-        <v>3.6</v>
+        <v>2.65</v>
       </c>
       <c r="U5" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="V5" t="n">
-        <v>11</v>
+        <v>6.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X5" t="n">
         <v>1.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.55</v>
+        <v>9.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.45</v>
+        <v>1.76</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.48</v>
+        <v>1.94</v>
       </c>
       <c r="AD5" t="n">
-        <v>4.95</v>
+        <v>3.1</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AH5" t="n">
-        <v>9</v>
+        <v>5.75</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>17.75</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="N11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P11" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V11" t="n">
         <v>5</v>
       </c>
-      <c r="O11" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="P11" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V11" t="n">
-        <v>7.4</v>
-      </c>
       <c r="W11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X11" t="n">
         <v>1.03</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y11" t="n">
-        <v>8.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.04</v>
+        <v>5.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>1.46</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.72</v>
+        <v>2.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.44</v>
+        <v>2.2</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.23</v>
+        <v>1.6</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.87</v>
+        <v>1.44</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>6.8</v>
+        <v>3.7</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,40 +2126,40 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2186,10 +2186,10 @@
         <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
         <v>0</v>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,40 +2258,40 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2318,10 +2318,10 @@
         <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="M15" t="n">
-        <v>3.47</v>
+        <v>3.31</v>
       </c>
       <c r="N15" t="n">
-        <v>1.69</v>
+        <v>1.9</v>
       </c>
       <c r="O15" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="P15" t="n">
         <v>8.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S15" t="n">
-        <v>2.64</v>
+        <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="U15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE15" t="n">
         <v>1.33</v>
       </c>
-      <c r="V15" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AF15" t="n">
-        <v>1.91</v>
+        <v>1.61</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="AH15" t="n">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.04</v>
+        <v>1.39</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N16" t="n">
-        <v>2.91</v>
+        <v>5.7</v>
       </c>
       <c r="O16" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="P16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="T16" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="U16" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="V16" t="n">
+        <v>5</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AA16" t="n">
         <v>5.25</v>
       </c>
-      <c r="W16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AB16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE16" t="n">
         <v>1.62</v>
       </c>
-      <c r="AC16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AF16" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AH16" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="N17" t="n">
-        <v>3.05</v>
+        <v>3.23</v>
       </c>
       <c r="O17" t="n">
         <v>1.73</v>
       </c>
       <c r="P17" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="R17" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U17" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="V17" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="W17" t="n">
         <v>1.1</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH17" t="n">
-        <v>5.2</v>
+        <v>6.25</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.57</v>
+        <v>4</v>
       </c>
       <c r="M18" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="O18" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="P18" t="n">
-        <v>6.55</v>
+        <v>8.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="R18" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="S18" t="n">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="T18" t="n">
-        <v>3.66</v>
+        <v>3.01</v>
       </c>
       <c r="U18" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
-        <v>10</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W18" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>6.55</v>
+        <v>8</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.4</v>
+        <v>2.95</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.5</v>
+        <v>2.09</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="AD18" t="n">
-        <v>5.05</v>
+        <v>3.75</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.17</v>
+        <v>1.91</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AH18" t="n">
-        <v>11</v>
+        <v>6.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.39</v>
+        <v>3.53</v>
       </c>
       <c r="M19" t="n">
-        <v>4.5</v>
+        <v>3.18</v>
       </c>
       <c r="N19" t="n">
-        <v>5.7</v>
+        <v>2.16</v>
       </c>
       <c r="O19" t="n">
-        <v>1.4</v>
+        <v>2.53</v>
       </c>
       <c r="P19" t="n">
-        <v>12</v>
+        <v>6.55</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.88</v>
+        <v>1.8</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="S19" t="n">
-        <v>3.75</v>
+        <v>2.36</v>
       </c>
       <c r="T19" t="n">
-        <v>2.2</v>
+        <v>3.66</v>
       </c>
       <c r="U19" t="n">
-        <v>1.62</v>
+        <v>1.22</v>
       </c>
       <c r="V19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="W19" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AH19" t="n">
         <v>11</v>
       </c>
-      <c r="Z19" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AI19" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.45</v>
+        <v>2.04</v>
       </c>
       <c r="M20" t="n">
-        <v>3.31</v>
+        <v>3.67</v>
       </c>
       <c r="N20" t="n">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="O20" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="P20" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S20" t="n">
         <v>3.1</v>
       </c>
       <c r="T20" t="n">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="U20" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="V20" t="n">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>8.5</v>
+        <v>15</v>
       </c>
       <c r="Z20" t="n">
         <v>1.22</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>5.25</v>
+        <v>4.75</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,76 +3182,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.69</v>
+        <v>2.09</v>
       </c>
       <c r="M21" t="n">
-        <v>3.56</v>
+        <v>3.45</v>
       </c>
       <c r="N21" t="n">
-        <v>2.3</v>
+        <v>2.97</v>
       </c>
       <c r="O21" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="P21" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="R21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="Z21" t="n">
         <v>1.25</v>
       </c>
-      <c r="S21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V21" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AA21" t="n">
-        <v>4.69</v>
+        <v>3.7</v>
       </c>
       <c r="AB21" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF21" t="n">
         <v>1.62</v>
       </c>
-      <c r="AC21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AG21" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AH21" t="n">
-        <v>4.25</v>
+        <v>5.2</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3278,22 +3278,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.98</v>
+        <v>2.7</v>
       </c>
       <c r="M22" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>3.23</v>
+        <v>2.2</v>
       </c>
       <c r="O22" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="P22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T22" t="n">
         <v>2.3</v>
       </c>
-      <c r="R22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.63</v>
-      </c>
       <c r="U22" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="V22" t="n">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X22" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.25</v>
+        <v>2.41</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.05</v>
+        <v>2.41</v>
       </c>
       <c r="AH22" t="n">
-        <v>6.25</v>
+        <v>4.33</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="M25" t="n">
         <v>3.75</v>
@@ -3728,7 +3728,7 @@
         <v>1.73</v>
       </c>
       <c r="R25" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S25" t="n">
         <v>3.4</v>
@@ -3740,16 +3740,16 @@
         <v>1.6</v>
       </c>
       <c r="V25" t="n">
-        <v>5.35</v>
+        <v>4.8</v>
       </c>
       <c r="W25" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X25" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Z25" t="n">
         <v>1.15</v>
@@ -3761,25 +3761,25 @@
         <v>1.56</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="AD25" t="n">
         <v>2.35</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="AH25" t="n">
         <v>4.2</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="M27" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="N27" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="O27" t="n">
         <v>2.1</v>
@@ -3998,7 +3998,7 @@
         <v>3.64</v>
       </c>
       <c r="T27" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="U27" t="n">
         <v>1.62</v>
@@ -4007,13 +4007,13 @@
         <v>5.05</v>
       </c>
       <c r="W27" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X27" t="n">
         <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>17</v>
+        <v>14.2</v>
       </c>
       <c r="Z27" t="n">
         <v>1.15</v>
@@ -4022,22 +4022,22 @@
         <v>5.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="AD27" t="n">
         <v>2.25</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="AH27" t="n">
         <v>3.9</v>
@@ -4106,7 +4106,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="M28" t="n">
         <v>3.05</v>
@@ -4124,13 +4124,13 @@
         <v>2.63</v>
       </c>
       <c r="R28" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="S28" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="T28" t="n">
-        <v>3.07</v>
+        <v>3.48</v>
       </c>
       <c r="U28" t="n">
         <v>1.28</v>
@@ -4139,22 +4139,22 @@
         <v>9</v>
       </c>
       <c r="W28" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X28" t="n">
         <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AA28" t="n">
         <v>2.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="AC28" t="n">
         <v>1.5</v>
@@ -4166,10 +4166,10 @@
         <v>1.15</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AH28" t="n">
         <v>8.800000000000001</v>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,76 +4238,76 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.53</v>
+        <v>3.12</v>
       </c>
       <c r="M29" t="n">
-        <v>3.9</v>
+        <v>2.91</v>
       </c>
       <c r="N29" t="n">
-        <v>4.75</v>
+        <v>2.19</v>
       </c>
       <c r="O29" t="n">
-        <v>1.5</v>
+        <v>2.38</v>
       </c>
       <c r="P29" t="n">
-        <v>10.5</v>
+        <v>7.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="R29" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U29" t="n">
         <v>1.33</v>
       </c>
-      <c r="S29" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.44</v>
-      </c>
       <c r="V29" t="n">
-        <v>6.5</v>
+        <v>7.4</v>
       </c>
       <c r="W29" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X29" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>9.5</v>
+        <v>7.3</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.8</v>
+        <v>2.84</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.05</v>
+        <v>1.55</v>
       </c>
       <c r="AD29" t="n">
-        <v>3</v>
+        <v>3.52</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH29" t="n">
-        <v>5.5</v>
+        <v>6.85</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.12</v>
+        <v>1.19</v>
       </c>
       <c r="M30" t="n">
-        <v>2.91</v>
+        <v>6</v>
       </c>
       <c r="N30" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P30" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T30" t="n">
         <v>2.19</v>
       </c>
-      <c r="O30" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="P30" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T30" t="n">
-        <v>3.04</v>
-      </c>
       <c r="U30" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="V30" t="n">
-        <v>7.4</v>
+        <v>4.6</v>
       </c>
       <c r="W30" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="X30" t="n">
         <v>1.03</v>
       </c>
       <c r="Y30" t="n">
-        <v>7.3</v>
+        <v>19</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.84</v>
+        <v>5</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.4</v>
+        <v>1.42</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.55</v>
+        <v>2.49</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.52</v>
+        <v>2.1</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.22</v>
+        <v>1.66</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="AH30" t="n">
-        <v>6.85</v>
+        <v>3.28</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.19</v>
+        <v>1.53</v>
       </c>
       <c r="M31" t="n">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="N31" t="n">
-        <v>12.25</v>
+        <v>4.75</v>
       </c>
       <c r="O31" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="P31" t="n">
-        <v>15.25</v>
+        <v>10.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.65</v>
+        <v>2.75</v>
       </c>
       <c r="R31" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="S31" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="T31" t="n">
-        <v>2.19</v>
+        <v>2.63</v>
       </c>
       <c r="U31" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="V31" t="n">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="W31" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AI31" t="n">
         <v>1.14</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>1.25</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -5253,12 +5253,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,76 +5294,76 @@
         </is>
       </c>
       <c r="L37" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="M37" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O37" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V37" t="n">
+        <v>15</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA37" t="n">
         <v>2.15</v>
       </c>
-      <c r="M37" t="n">
+      <c r="AB37" t="n">
         <v>3.1</v>
       </c>
-      <c r="N37" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O37" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="P37" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T37" t="n">
-        <v>3</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V37" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AC37" t="n">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.87</v>
+        <v>2.38</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="AH37" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="AL37" s="3" t="n">
-        <v>45880.8125</v>
+        <v>45880.79861111111</v>
       </c>
     </row>
     <row r="38">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,76 +5558,76 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
@@ -5640,7 +5640,7 @@
         </is>
       </c>
       <c r="AL39" s="3" t="n">
-        <v>45880.83333333334</v>
+        <v>45880.8125</v>
       </c>
     </row>
     <row r="40">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,76 +5822,76 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
@@ -5913,12 +5913,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,76 +5954,76 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         </is>
       </c>
       <c r="AL42" s="3" t="n">
-        <v>45880.85416666666</v>
+        <v>45880.83333333334</v>
       </c>
     </row>
     <row r="43">
@@ -6045,12 +6045,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,76 +6086,76 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         </is>
       </c>
       <c r="AL43" s="3" t="n">
-        <v>45880.88194444445</v>
+        <v>45880.85416666666</v>
       </c>
     </row>
     <row r="44">
@@ -6177,12 +6177,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,88 +6218,220 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.22</v>
+        <v>1.95</v>
       </c>
       <c r="M44" t="n">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="N44" t="n">
-        <v>3.16</v>
+        <v>3.95</v>
       </c>
       <c r="O44" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="P44" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="R44" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="S44" t="n">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="T44" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="U44" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="V44" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="W44" t="n">
         <v>1.04</v>
       </c>
       <c r="X44" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL44" s="3" t="n">
+        <v>45880.88194444445</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>45880</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Paysandu</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="M45" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="N45" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P45" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S45" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V45" t="n">
+        <v>9</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X45" t="n">
         <v>1.1</v>
       </c>
-      <c r="Y44" t="n">
+      <c r="Y45" t="n">
         <v>6.6</v>
       </c>
-      <c r="Z44" t="n">
+      <c r="Z45" t="n">
         <v>1.5</v>
       </c>
-      <c r="AA44" t="n">
+      <c r="AA45" t="n">
         <v>2.4</v>
       </c>
-      <c r="AB44" t="n">
+      <c r="AB45" t="n">
         <v>2.37</v>
       </c>
-      <c r="AC44" t="n">
+      <c r="AC45" t="n">
         <v>1.48</v>
       </c>
-      <c r="AD44" t="n">
+      <c r="AD45" t="n">
         <v>4.9</v>
       </c>
-      <c r="AE44" t="n">
+      <c r="AE45" t="n">
         <v>1.17</v>
       </c>
-      <c r="AF44" t="n">
+      <c r="AF45" t="n">
         <v>2.1</v>
       </c>
-      <c r="AG44" t="n">
+      <c r="AG45" t="n">
         <v>1.63</v>
       </c>
-      <c r="AH44" t="n">
+      <c r="AH45" t="n">
         <v>10</v>
       </c>
-      <c r="AI44" t="n">
+      <c r="AI45" t="n">
         <v>1.05</v>
       </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL44" s="3" t="n">
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL45" s="3" t="n">
         <v>45880.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-08-11.xlsx
+++ b/jogos_2025-08-11.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL45"/>
+  <dimension ref="A1:AL47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,57 +657,57 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -716,43 +716,43 @@
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['23', '36', '64', '89']</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['9', '16']</t>
         </is>
       </c>
       <c r="AL2" s="3" t="n">
@@ -789,102 +789,102 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="M3" t="n">
-        <v>4</v>
+        <v>3.79</v>
       </c>
       <c r="N3" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="O3" t="n">
-        <v>1.44</v>
+        <v>2.05</v>
       </c>
       <c r="P3" t="n">
-        <v>11.25</v>
+        <v>2.35</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.88</v>
+        <v>4.46</v>
       </c>
       <c r="R3" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="T3" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="U3" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="V3" t="n">
-        <v>6.35</v>
+        <v>6.2</v>
       </c>
       <c r="W3" t="n">
         <v>1.06</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>11.4</v>
+        <v>12</v>
       </c>
       <c r="Z3" t="n">
         <v>1.25</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AB3" t="n">
         <v>1.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AD3" t="n">
         <v>2.88</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AH3" t="n">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['15', '62', '68', '80']</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+6']</t>
         </is>
       </c>
       <c r="AL3" s="3" t="n">
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,111 +912,111 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Renofa Yamaguchi</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.35</v>
+        <v>1.59</v>
       </c>
       <c r="M4" t="n">
-        <v>2.8</v>
+        <v>3.82</v>
       </c>
       <c r="N4" t="n">
-        <v>2.96</v>
+        <v>4.4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="P4" t="n">
-        <v>6.55</v>
+        <v>2.15</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.18</v>
+        <v>5.25</v>
       </c>
       <c r="R4" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="T4" t="n">
-        <v>3.6</v>
+        <v>2.65</v>
       </c>
       <c r="U4" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="V4" t="n">
-        <v>11</v>
+        <v>6.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X4" t="n">
         <v>1.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.55</v>
+        <v>9.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.45</v>
+        <v>1.76</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.48</v>
+        <v>1.94</v>
       </c>
       <c r="AD4" t="n">
-        <v>4.95</v>
+        <v>3.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AH4" t="n">
-        <v>9</v>
+        <v>5.75</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13', '54', '81']</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2']</t>
         </is>
       </c>
       <c r="AL4" s="3" t="n">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,102 +1044,102 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Renofa Yamaguchi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.59</v>
+        <v>2.35</v>
       </c>
       <c r="M5" t="n">
-        <v>3.82</v>
+        <v>2.8</v>
       </c>
       <c r="N5" t="n">
-        <v>4.4</v>
+        <v>2.96</v>
       </c>
       <c r="O5" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="P5" t="n">
-        <v>9.5</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="R5" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="S5" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="T5" t="n">
-        <v>2.65</v>
+        <v>3.6</v>
       </c>
       <c r="U5" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="V5" t="n">
-        <v>6.5</v>
+        <v>11</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X5" t="n">
         <v>1.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.5</v>
+        <v>6.55</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.76</v>
+        <v>2.45</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.94</v>
+        <v>1.48</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.1</v>
+        <v>4.95</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AH5" t="n">
-        <v>5.75</v>
+        <v>9</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['40']</t>
         </is>
       </c>
       <c r="AL5" s="3" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1475,13 +1475,13 @@
         <v>4.8</v>
       </c>
       <c r="O8" t="n">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.6</v>
+        <v>5.47</v>
       </c>
       <c r="R8" t="n">
         <v>1.46</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="M11" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.5</v>
+        <v>3.35</v>
       </c>
       <c r="O11" t="n">
-        <v>1.83</v>
+        <v>3.07</v>
       </c>
       <c r="P11" t="n">
-        <v>17.75</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.91</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="T11" t="n">
-        <v>2.17</v>
+        <v>3.1</v>
       </c>
       <c r="U11" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W11" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
         <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.11</v>
+        <v>1.37</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.3</v>
+        <v>2.88</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.46</v>
+        <v>2.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.4</v>
+        <v>1.66</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.2</v>
+        <v>3.99</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.6</v>
+        <v>1.18</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.7</v>
+        <v>7.8</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="M12" t="n">
-        <v>3.58</v>
+        <v>3.12</v>
       </c>
       <c r="N12" t="n">
-        <v>4.21</v>
+        <v>4.33</v>
       </c>
       <c r="O12" t="n">
-        <v>1.63</v>
+        <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>8.699999999999999</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.66</v>
+        <v>4</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="T12" t="n">
-        <v>2.94</v>
+        <v>3.5</v>
       </c>
       <c r="U12" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="V12" t="n">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.29</v>
+        <v>1.47</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.04</v>
+        <v>2.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AH12" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>6.34</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>5.79</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.75</v>
+        <v>3.02</v>
       </c>
       <c r="M14" t="n">
-        <v>3.12</v>
+        <v>3.35</v>
       </c>
       <c r="N14" t="n">
-        <v>4.33</v>
+        <v>2.05</v>
       </c>
       <c r="O14" t="n">
-        <v>1.83</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5</v>
+        <v>3.14</v>
       </c>
       <c r="T14" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="U14" t="n">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="V14" t="n">
-        <v>11</v>
+        <v>4.8</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.68</v>
+        <v>2.25</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.73</v>
+        <v>2.45</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2349,27 +2349,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.45</v>
+        <v>2.44</v>
       </c>
       <c r="M15" t="n">
-        <v>3.31</v>
+        <v>3.6</v>
       </c>
       <c r="N15" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="O15" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T15" t="n">
         <v>2</v>
       </c>
-      <c r="P15" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.62</v>
-      </c>
       <c r="U15" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="V15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>8.5</v>
+        <v>12</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.6</v>
+        <v>7.28</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.91</v>
+        <v>3</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.61</v>
+        <v>1.42</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.04</v>
+        <v>2.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>5.25</v>
+        <v>3.2</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         </is>
       </c>
       <c r="AL15" s="3" t="n">
-        <v>45880.58333333334</v>
+        <v>45880.54166666666</v>
       </c>
     </row>
     <row r="16">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.39</v>
+        <v>2.01</v>
       </c>
       <c r="M16" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>5.7</v>
+        <v>2.91</v>
       </c>
       <c r="O16" t="n">
-        <v>1.4</v>
+        <v>2.85</v>
       </c>
       <c r="P16" t="n">
-        <v>12</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="R16" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="T16" t="n">
-        <v>2.2</v>
+        <v>2.41</v>
       </c>
       <c r="U16" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="V16" t="n">
-        <v>5</v>
+        <v>5.35</v>
       </c>
       <c r="W16" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z16" t="n">
         <v>1.17</v>
       </c>
       <c r="AA16" t="n">
-        <v>5.25</v>
+        <v>4.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.15</v>
+        <v>2.57</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AG16" t="n">
         <v>2.1</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.9</v>
+        <v>4.45</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="O17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V17" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF17" t="n">
         <v>1.98</v>
       </c>
-      <c r="M17" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="P17" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V17" t="n">
-        <v>7</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X17" t="n">
+      <c r="AG17" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI17" t="n">
         <v>1.06</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.12</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q18" t="n">
         <v>4</v>
       </c>
-      <c r="M18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="O18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P18" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.67</v>
-      </c>
       <c r="R18" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>3.01</v>
+        <v>2.63</v>
       </c>
       <c r="U18" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="V18" t="n">
-        <v>8.300000000000001</v>
+        <v>7</v>
       </c>
       <c r="W18" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X18" t="n">
         <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.09</v>
+        <v>1.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AH18" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.53</v>
+        <v>1.39</v>
       </c>
       <c r="M19" t="n">
-        <v>3.18</v>
+        <v>4.5</v>
       </c>
       <c r="N19" t="n">
-        <v>2.16</v>
+        <v>5.7</v>
       </c>
       <c r="O19" t="n">
-        <v>2.53</v>
+        <v>1.83</v>
       </c>
       <c r="P19" t="n">
-        <v>6.55</v>
+        <v>2.63</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="R19" t="n">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>2.36</v>
+        <v>3.75</v>
       </c>
       <c r="T19" t="n">
-        <v>3.66</v>
+        <v>2.2</v>
       </c>
       <c r="U19" t="n">
-        <v>1.22</v>
+        <v>1.62</v>
       </c>
       <c r="V19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>6.55</v>
+        <v>11</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.44</v>
+        <v>5.25</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.5</v>
+        <v>1.58</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.42</v>
+        <v>2.18</v>
       </c>
       <c r="AD19" t="n">
-        <v>5.05</v>
+        <v>2.15</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.1</v>
+        <v>1.62</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.17</v>
+        <v>1.67</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.61</v>
+        <v>2.1</v>
       </c>
       <c r="AH19" t="n">
-        <v>11</v>
+        <v>3.9</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.04</v>
+        <v>2.75</v>
       </c>
       <c r="M20" t="n">
-        <v>3.67</v>
+        <v>3.75</v>
       </c>
       <c r="N20" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O20" t="n">
         <v>3.2</v>
       </c>
-      <c r="O20" t="n">
-        <v>1.75</v>
-      </c>
       <c r="P20" t="n">
-        <v>10</v>
+        <v>2.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="R20" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S20" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="T20" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="U20" t="n">
         <v>1.55</v>
       </c>
       <c r="V20" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AA20" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC20" t="n">
         <v>2.15</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AH20" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,73 +3182,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.09</v>
+        <v>2.6</v>
       </c>
       <c r="M21" t="n">
-        <v>3.45</v>
+        <v>3.64</v>
       </c>
       <c r="N21" t="n">
-        <v>2.97</v>
+        <v>2.46</v>
       </c>
       <c r="O21" t="n">
-        <v>1.73</v>
+        <v>3.25</v>
       </c>
       <c r="P21" t="n">
-        <v>12.5</v>
+        <v>2.15</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="R21" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="U21" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="V21" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>9.1</v>
+        <v>10.9</v>
       </c>
       <c r="Z21" t="n">
         <v>1.25</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AH21" t="n">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="AI21" t="n">
         <v>1.13</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,70 +3314,70 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.7</v>
+        <v>2.29</v>
       </c>
       <c r="M22" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N22" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="O22" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="P22" t="n">
-        <v>10</v>
+        <v>2.19</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.8</v>
+        <v>3.35</v>
       </c>
       <c r="R22" t="n">
         <v>1.3</v>
       </c>
       <c r="S22" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T22" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="U22" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="V22" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="W22" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="AB22" t="n">
         <v>1.62</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.41</v>
+        <v>2.65</v>
       </c>
       <c r="AE22" t="n">
         <v>1.5</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="AH22" t="n">
         <v>4.33</v>
@@ -3405,12 +3405,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O23" t="n">
+        <v>4</v>
+      </c>
+      <c r="P23" t="n">
         <v>1.85</v>
       </c>
-      <c r="M23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="P23" t="n">
-        <v>8.25</v>
-      </c>
       <c r="Q23" t="n">
-        <v>2.5</v>
+        <v>3.12</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="S23" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="T23" t="n">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="U23" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="V23" t="n">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="W23" t="n">
+        <v>1</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AE23" t="n">
         <v>1.08</v>
       </c>
-      <c r="X23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AF23" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AH23" t="n">
-        <v>7.5</v>
+        <v>13</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="AL23" s="3" t="n">
-        <v>45880.61458333334</v>
+        <v>45880.58333333334</v>
       </c>
     </row>
     <row r="24">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,76 +3578,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         </is>
       </c>
       <c r="AL24" s="3" t="n">
-        <v>45880.625</v>
+        <v>45880.61458333334</v>
       </c>
     </row>
     <row r="25">
@@ -3710,76 +3710,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="M25" t="n">
-        <v>3.75</v>
+        <v>4.01</v>
       </c>
       <c r="N25" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="O25" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="P25" t="n">
-        <v>11</v>
+        <v>2.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.73</v>
+        <v>2.57</v>
       </c>
       <c r="R25" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="S25" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="T25" t="n">
         <v>2.25</v>
       </c>
       <c r="U25" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="V25" t="n">
-        <v>4.8</v>
+        <v>5.15</v>
       </c>
       <c r="W25" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X25" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z25" t="n">
         <v>1.15</v>
       </c>
       <c r="AA25" t="n">
-        <v>4.9</v>
+        <v>5.73</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AH25" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3842,76 +3842,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,76 +3974,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="M27" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="N27" t="n">
-        <v>2</v>
+        <v>5.75</v>
       </c>
       <c r="O27" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="P27" t="n">
-        <v>15</v>
+        <v>2.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.73</v>
+        <v>6</v>
       </c>
       <c r="R27" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S27" t="n">
-        <v>3.64</v>
+        <v>3.22</v>
       </c>
       <c r="T27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V27" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC27" t="n">
         <v>2.15</v>
       </c>
-      <c r="U27" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V27" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.48</v>
-      </c>
       <c r="AD27" t="n">
-        <v>2.25</v>
+        <v>2.46</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.58</v>
+        <v>1.91</v>
       </c>
       <c r="AH27" t="n">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4065,12 +4065,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.78</v>
+        <v>2.62</v>
       </c>
       <c r="M28" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="N28" t="n">
-        <v>3.6</v>
+        <v>2.34</v>
       </c>
       <c r="O28" t="n">
-        <v>1.73</v>
+        <v>3.1</v>
       </c>
       <c r="P28" t="n">
-        <v>7.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="R28" t="n">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="S28" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="T28" t="n">
-        <v>3.48</v>
+        <v>2.25</v>
       </c>
       <c r="U28" t="n">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="V28" t="n">
-        <v>9</v>
+        <v>4.6</v>
       </c>
       <c r="W28" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="X28" t="n">
         <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>6.5</v>
+        <v>12</v>
       </c>
       <c r="Z28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF28" t="n">
         <v>1.5</v>
       </c>
-      <c r="AA28" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>4.94</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AG28" t="n">
-        <v>1.67</v>
+        <v>2.55</v>
       </c>
       <c r="AH28" t="n">
-        <v>8.800000000000001</v>
+        <v>3.85</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         </is>
       </c>
       <c r="AL28" s="3" t="n">
-        <v>45880.63541666666</v>
+        <v>45880.625</v>
       </c>
     </row>
     <row r="29">
@@ -4197,12 +4197,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,76 +4238,76 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.12</v>
+        <v>2.05</v>
       </c>
       <c r="M29" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="N29" t="n">
-        <v>2.19</v>
+        <v>3.7</v>
       </c>
       <c r="O29" t="n">
-        <v>2.38</v>
+        <v>2.95</v>
       </c>
       <c r="P29" t="n">
-        <v>7.3</v>
+        <v>1.93</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.83</v>
+        <v>4.27</v>
       </c>
       <c r="R29" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="S29" t="n">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="T29" t="n">
-        <v>3.04</v>
+        <v>3.4</v>
       </c>
       <c r="U29" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="V29" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="W29" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X29" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="Y29" t="n">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.84</v>
+        <v>2.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.52</v>
+        <v>4.95</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AH29" t="n">
-        <v>6.85</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         </is>
       </c>
       <c r="AL29" s="3" t="n">
-        <v>45880.64583333334</v>
+        <v>45880.63541666666</v>
       </c>
     </row>
     <row r="30">
@@ -4379,13 +4379,13 @@
         <v>12.25</v>
       </c>
       <c r="O30" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="P30" t="n">
-        <v>15.25</v>
+        <v>2.61</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.65</v>
+        <v>9.1</v>
       </c>
       <c r="R30" t="n">
         <v>1.26</v>
@@ -4511,13 +4511,13 @@
         <v>4.75</v>
       </c>
       <c r="O31" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="P31" t="n">
-        <v>10.5</v>
+        <v>2.38</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.75</v>
+        <v>5.5</v>
       </c>
       <c r="R31" t="n">
         <v>1.33</v>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,73 +4634,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4</v>
+        <v>3.12</v>
       </c>
       <c r="M32" t="n">
-        <v>3.31</v>
+        <v>2.91</v>
       </c>
       <c r="N32" t="n">
-        <v>1.76</v>
+        <v>2.19</v>
       </c>
       <c r="O32" t="n">
-        <v>2.75</v>
+        <v>4.05</v>
       </c>
       <c r="P32" t="n">
-        <v>8</v>
+        <v>1.98</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.57</v>
+        <v>2.84</v>
       </c>
       <c r="R32" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S32" t="n">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="T32" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="U32" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V32" t="n">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="W32" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X32" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y32" t="n">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.12</v>
+        <v>2.84</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.77</v>
+        <v>3.52</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AF32" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AH32" t="n">
-        <v>6.75</v>
+        <v>6.85</v>
       </c>
       <c r="AI32" t="n">
         <v>1.04</v>
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="AL32" s="3" t="n">
-        <v>45880.65625</v>
+        <v>45880.64583333334</v>
       </c>
     </row>
     <row r="33">
@@ -4725,27 +4725,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.65</v>
+        <v>4</v>
       </c>
       <c r="M33" t="n">
-        <v>4.3</v>
+        <v>3.31</v>
       </c>
       <c r="N33" t="n">
-        <v>4.6</v>
+        <v>1.76</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R33" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="S33" t="n">
-        <v>3.85</v>
+        <v>2.63</v>
       </c>
       <c r="T33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U33" t="n">
-        <v>1.76</v>
+        <v>1.36</v>
       </c>
       <c r="V33" t="n">
-        <v>4.33</v>
+        <v>9</v>
       </c>
       <c r="W33" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="X33" t="n">
         <v>1.02</v>
       </c>
       <c r="Y33" t="n">
-        <v>21</v>
+        <v>7.8</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="AA33" t="n">
-        <v>5.5</v>
+        <v>3.12</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.4</v>
+        <v>1.94</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.75</v>
+        <v>1.76</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.25</v>
+        <v>3.77</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.63</v>
+        <v>1.26</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.45</v>
+        <v>1.73</v>
       </c>
       <c r="AH33" t="n">
-        <v>3.22</v>
+        <v>6.75</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         </is>
       </c>
       <c r="AL33" s="3" t="n">
-        <v>45880.67708333334</v>
+        <v>45880.65625</v>
       </c>
     </row>
     <row r="34">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M34" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="N34" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O34" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="P34" t="n">
         <v>2.5</v>
       </c>
-      <c r="M34" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N34" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O34" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
       <c r="Q34" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="R34" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S34" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="T34" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="U34" t="n">
-        <v>1.44</v>
+        <v>1.76</v>
       </c>
       <c r="V34" t="n">
-        <v>4.33</v>
+        <v>4.7</v>
       </c>
       <c r="W34" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="X34" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y34" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AA34" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.15</v>
+        <v>2.47</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.69</v>
+        <v>2.33</v>
       </c>
       <c r="AH34" t="n">
         <v>3.2</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -4989,27 +4989,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="M35" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="N35" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O35" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V35" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AA35" t="n">
         <v>5.5</v>
       </c>
-      <c r="O35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P35" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S35" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V35" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>3.65</v>
-      </c>
       <c r="AB35" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.97</v>
+        <v>2.9</v>
       </c>
       <c r="AD35" t="n">
-        <v>3</v>
+        <v>1.85</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.38</v>
+        <v>1.75</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.8</v>
+        <v>1.42</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="AH35" t="n">
-        <v>5.75</v>
+        <v>3.2</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="AL35" s="3" t="n">
-        <v>45880.69791666666</v>
+        <v>45880.67708333334</v>
       </c>
     </row>
     <row r="36">
@@ -5121,27 +5121,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,76 +5162,76 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="M36" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="N36" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="O36" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="R36" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U36" t="n">
         <v>1.44</v>
       </c>
-      <c r="S36" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T36" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.33</v>
-      </c>
       <c r="V36" t="n">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="W36" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.65</v>
+        <v>1.97</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF36" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="AL36" s="3" t="n">
-        <v>45880.75</v>
+        <v>45880.69791666666</v>
       </c>
     </row>
     <row r="37">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,77 +5294,77 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.42</v>
+        <v>1.9</v>
       </c>
       <c r="M37" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="N37" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="O37" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.3</v>
+        <v>4.75</v>
       </c>
       <c r="R37" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="S37" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="T37" t="n">
-        <v>4.33</v>
+        <v>3.25</v>
       </c>
       <c r="U37" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="V37" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="W37" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AI37" t="n">
         <v>1.03</v>
       </c>
-      <c r="X37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ37" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="AL37" s="3" t="n">
-        <v>45880.79861111111</v>
+        <v>45880.75</v>
       </c>
     </row>
     <row r="38">
@@ -5385,12 +5385,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,76 +5426,76 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="M38" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="N38" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="O38" t="n">
-        <v>2.05</v>
+        <v>3.39</v>
       </c>
       <c r="P38" t="n">
-        <v>5.25</v>
+        <v>1.84</v>
       </c>
       <c r="Q38" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S38" t="n">
         <v>2.2</v>
       </c>
-      <c r="R38" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.15</v>
-      </c>
       <c r="T38" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="U38" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="V38" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W38" t="n">
         <v>1.03</v>
       </c>
       <c r="X38" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y38" t="n">
-        <v>6.1</v>
+        <v>5.5</v>
       </c>
       <c r="Z38" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC38" t="n">
         <v>1.53</v>
       </c>
-      <c r="AA38" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AD38" t="n">
-        <v>4.75</v>
+        <v>5.7</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AH38" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="AL38" s="3" t="n">
-        <v>45880.8125</v>
+        <v>45880.79166666666</v>
       </c>
     </row>
     <row r="39">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,73 +5558,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="M39" t="n">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="N39" t="n">
         <v>3.4</v>
       </c>
       <c r="O39" t="n">
-        <v>1.73</v>
+        <v>3.14</v>
       </c>
       <c r="P39" t="n">
-        <v>7.5</v>
+        <v>1.75</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.4</v>
+        <v>4.6</v>
       </c>
       <c r="R39" t="n">
-        <v>1.42</v>
+        <v>1.68</v>
       </c>
       <c r="S39" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="T39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U39" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="V39" t="n">
-        <v>8.25</v>
+        <v>11.5</v>
       </c>
       <c r="W39" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X39" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="Y39" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.34</v>
+        <v>1.66</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.87</v>
+        <v>2.1</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.25</v>
+        <v>3.23</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.58</v>
+        <v>1.33</v>
       </c>
       <c r="AD39" t="n">
-        <v>3.85</v>
+        <v>6.25</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.87</v>
+        <v>2.38</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="AH39" t="n">
-        <v>7.4</v>
+        <v>19</v>
       </c>
       <c r="AI39" t="n">
         <v>1.03</v>
@@ -5640,7 +5640,7 @@
         </is>
       </c>
       <c r="AL39" s="3" t="n">
-        <v>45880.8125</v>
+        <v>45880.79861111111</v>
       </c>
     </row>
     <row r="40">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,77 +5690,77 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.29</v>
+        <v>2.2</v>
       </c>
       <c r="M40" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="N40" t="n">
-        <v>2.1</v>
+        <v>2.97</v>
       </c>
       <c r="O40" t="n">
         <v>2.4</v>
       </c>
       <c r="P40" t="n">
-        <v>6.5</v>
+        <v>1.95</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="R40" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S40" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="T40" t="n">
-        <v>3.3</v>
+        <v>3.17</v>
       </c>
       <c r="U40" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="V40" t="n">
-        <v>9.800000000000001</v>
+        <v>8.25</v>
       </c>
       <c r="W40" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AI40" t="n">
         <v>1.03</v>
       </c>
-      <c r="X40" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AJ40" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5772,7 +5772,7 @@
         </is>
       </c>
       <c r="AL40" s="3" t="n">
-        <v>45880.83333333334</v>
+        <v>45880.8125</v>
       </c>
     </row>
     <row r="41">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,76 +5822,76 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         </is>
       </c>
       <c r="AL41" s="3" t="n">
-        <v>45880.83333333334</v>
+        <v>45880.8125</v>
       </c>
     </row>
     <row r="42">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,76 +5954,76 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.66</v>
+        <v>3.29</v>
       </c>
       <c r="M42" t="n">
-        <v>3.63</v>
+        <v>2.94</v>
       </c>
       <c r="N42" t="n">
-        <v>2.47</v>
+        <v>2.1</v>
       </c>
       <c r="O42" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="P42" t="n">
-        <v>12</v>
+        <v>1.77</v>
       </c>
       <c r="Q42" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V42" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF42" t="n">
         <v>1.95</v>
       </c>
-      <c r="R42" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S42" t="n">
-        <v>3</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V42" t="n">
-        <v>7</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X42" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AG42" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AH42" t="n">
-        <v>5.85</v>
+        <v>9</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,40 +6086,40 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X43" t="n">
         <v>0</v>
@@ -6128,34 +6128,34 @@
         <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         </is>
       </c>
       <c r="AL43" s="3" t="n">
-        <v>45880.85416666666</v>
+        <v>45880.83333333334</v>
       </c>
     </row>
     <row r="44">
@@ -6177,12 +6177,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,76 +6218,76 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.95</v>
+        <v>2.66</v>
       </c>
       <c r="M44" t="n">
-        <v>2.95</v>
+        <v>3.63</v>
       </c>
       <c r="N44" t="n">
-        <v>3.95</v>
+        <v>2.47</v>
       </c>
       <c r="O44" t="n">
-        <v>1.8</v>
+        <v>3.25</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="R44" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="S44" t="n">
-        <v>1.97</v>
+        <v>3</v>
       </c>
       <c r="T44" t="n">
-        <v>3.7</v>
+        <v>2.75</v>
       </c>
       <c r="U44" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="V44" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="W44" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X44" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="Y44" t="n">
-        <v>5.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.6</v>
+        <v>1.24</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.2</v>
+        <v>3.36</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.81</v>
+        <v>1.94</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.36</v>
+        <v>1.88</v>
       </c>
       <c r="AD44" t="n">
-        <v>5.3</v>
+        <v>3.08</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.38</v>
+        <v>1.67</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="AH44" t="n">
-        <v>11</v>
+        <v>5.85</v>
       </c>
       <c r="AI44" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="AL44" s="3" t="n">
-        <v>45880.88194444445</v>
+        <v>45880.83333333334</v>
       </c>
     </row>
     <row r="45">
@@ -6309,129 +6309,393 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>FC Cincinnati II</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Crown Legacy</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="M45" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="N45" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="O45" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V45" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL45" s="3" t="n">
+        <v>45880.85416666666</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45880</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Racing Córdoba</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Quilmes</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>2</v>
+      </c>
+      <c r="M46" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="N46" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O46" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S46" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T46" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V46" t="n">
+        <v>13</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL46" s="3" t="n">
+        <v>45880.88194444445</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>45880</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Paysandu</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Vila Nova</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="inlineStr">
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L45" t="n">
+      <c r="L47" t="n">
         <v>2.22</v>
       </c>
-      <c r="M45" t="n">
+      <c r="M47" t="n">
         <v>2.83</v>
       </c>
-      <c r="N45" t="n">
+      <c r="N47" t="n">
         <v>3.16</v>
       </c>
-      <c r="O45" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P45" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="Q45" t="n">
+      <c r="O47" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S47" t="n">
         <v>2.3</v>
       </c>
-      <c r="R45" t="n">
+      <c r="T47" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V47" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X47" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Z47" t="n">
         <v>1.5</v>
       </c>
-      <c r="S45" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="T45" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V45" t="n">
-        <v>9</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X45" t="n">
+      <c r="AA47" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AE47" t="n">
         <v>1.1</v>
       </c>
-      <c r="Y45" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL45" s="3" t="n">
+      <c r="AF47" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL47" s="3" t="n">
         <v>45880.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-08-11.xlsx
+++ b/jogos_2025-08-11.xlsx
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,22 +912,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Renofa Yamaguchi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.59</v>
+        <v>2.35</v>
       </c>
       <c r="M4" t="n">
-        <v>3.82</v>
+        <v>2.8</v>
       </c>
       <c r="N4" t="n">
-        <v>4.4</v>
+        <v>2.96</v>
       </c>
       <c r="O4" t="n">
-        <v>2.15</v>
+        <v>3.2</v>
       </c>
       <c r="P4" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.25</v>
+        <v>3.6</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="S4" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="T4" t="n">
-        <v>2.65</v>
+        <v>3.6</v>
       </c>
       <c r="U4" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="V4" t="n">
-        <v>6.5</v>
+        <v>11</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X4" t="n">
         <v>1.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.5</v>
+        <v>6.55</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.76</v>
+        <v>2.45</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.94</v>
+        <v>1.48</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.1</v>
+        <v>4.95</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AH4" t="n">
-        <v>5.75</v>
+        <v>9</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>['13', '54', '81']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>['2']</t>
+          <t>['40']</t>
         </is>
       </c>
       <c r="AL4" s="3" t="n">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,22 +1044,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Renofa Yamaguchi</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -1070,85 +1070,85 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.35</v>
+        <v>1.59</v>
       </c>
       <c r="M5" t="n">
-        <v>2.8</v>
+        <v>3.82</v>
       </c>
       <c r="N5" t="n">
-        <v>2.96</v>
+        <v>4.4</v>
       </c>
       <c r="O5" t="n">
-        <v>3.2</v>
+        <v>2.15</v>
       </c>
       <c r="P5" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.6</v>
+        <v>5.25</v>
       </c>
       <c r="R5" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="T5" t="n">
-        <v>3.6</v>
+        <v>2.65</v>
       </c>
       <c r="U5" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="V5" t="n">
-        <v>11</v>
+        <v>6.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X5" t="n">
         <v>1.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.55</v>
+        <v>9.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.45</v>
+        <v>1.76</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.48</v>
+        <v>1.94</v>
       </c>
       <c r="AD5" t="n">
-        <v>4.95</v>
+        <v>3.1</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AH5" t="n">
-        <v>9</v>
+        <v>5.75</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13', '54', '81']</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>['40']</t>
+          <t>['2']</t>
         </is>
       </c>
       <c r="AL5" s="3" t="n">
@@ -1185,20 +1185,20 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['28']</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1298,121 +1298,121 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Kudrivka</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.35</v>
+        <v>1.69</v>
       </c>
       <c r="M7" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="N7" t="n">
-        <v>1.92</v>
+        <v>4.8</v>
       </c>
       <c r="O7" t="n">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
       <c r="P7" t="n">
         <v>2.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.5</v>
+        <v>5.47</v>
       </c>
       <c r="R7" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="S7" t="n">
-        <v>2.94</v>
+        <v>2.6</v>
       </c>
       <c r="T7" t="n">
-        <v>2.55</v>
+        <v>3.15</v>
       </c>
       <c r="U7" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="V7" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="W7" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.65</v>
+        <v>2.13</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.08</v>
+        <v>1.71</v>
       </c>
       <c r="AH7" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['22', '56']</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['50']</t>
         </is>
       </c>
       <c r="AL7" s="3" t="n">
@@ -1430,121 +1430,121 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kudrivka</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.69</v>
+        <v>3.35</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>4.8</v>
+        <v>1.92</v>
       </c>
       <c r="O8" t="n">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="P8" t="n">
         <v>2.15</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.47</v>
+        <v>2.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>2.6</v>
+        <v>2.94</v>
       </c>
       <c r="T8" t="n">
-        <v>3.15</v>
+        <v>2.55</v>
       </c>
       <c r="U8" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="V8" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AC8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF8" t="n">
         <v>1.65</v>
       </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.13</v>
-      </c>
       <c r="AG8" t="n">
-        <v>1.71</v>
+        <v>2.08</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['18']</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['84']</t>
         </is>
       </c>
       <c r="AL8" s="3" t="n">
@@ -1581,7 +1581,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['47', '53', '57', '87', '90']</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -1694,112 +1694,112 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.49</v>
+        <v>1.72</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="N10" t="n">
-        <v>2.85</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>2.42</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.5</v>
+        <v>6.34</v>
       </c>
       <c r="R10" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="S10" t="n">
-        <v>2.62</v>
+        <v>2.31</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>3.66</v>
       </c>
       <c r="U10" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="V10" t="n">
-        <v>7.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y10" t="n">
-        <v>8</v>
+        <v>5.79</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.74</v>
+        <v>2.33</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.1</v>
+        <v>2.61</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.98</v>
+        <v>5.04</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.91</v>
+        <v>2.36</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AH10" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['41']</t>
         </is>
       </c>
       <c r="AL10" s="3" t="n">
@@ -1826,29 +1826,29 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1858,89 +1858,89 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.2</v>
+        <v>3.02</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>3.35</v>
+        <v>2.05</v>
       </c>
       <c r="O11" t="n">
-        <v>3.07</v>
+        <v>3.4</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>2.6</v>
+        <v>3.14</v>
       </c>
       <c r="T11" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="U11" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="V11" t="n">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="W11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X11" t="n">
         <v>1.02</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y11" t="n">
-        <v>7.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.37</v>
+        <v>1.16</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.88</v>
+        <v>4.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.66</v>
+        <v>2.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.99</v>
+        <v>2.63</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.18</v>
+        <v>1.48</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.85</v>
+        <v>2.45</v>
       </c>
       <c r="AH11" t="n">
-        <v>7.8</v>
+        <v>4.7</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['-1', '-1']</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['-1', '-1']</t>
         </is>
       </c>
       <c r="AL11" s="3" t="n">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,16 +1994,16 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="M12" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="N12" t="n">
-        <v>4.33</v>
+        <v>3.35</v>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="P12" t="n">
         <v>2</v>
@@ -2012,58 +2012,58 @@
         <v>4</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="T12" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="U12" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF12" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2090,29 +2090,29 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -2122,89 +2122,89 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.72</v>
+        <v>2.44</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="O13" t="n">
-        <v>2.42</v>
+        <v>2.85</v>
       </c>
       <c r="P13" t="n">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.34</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>2.31</v>
+        <v>3.5</v>
       </c>
       <c r="T13" t="n">
-        <v>3.66</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>1.22</v>
+        <v>1.58</v>
       </c>
       <c r="V13" t="n">
-        <v>9.300000000000001</v>
+        <v>4</v>
       </c>
       <c r="W13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X13" t="n">
         <v>1.02</v>
       </c>
-      <c r="X13" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y13" t="n">
-        <v>5.79</v>
+        <v>12</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.56</v>
+        <v>1.11</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.33</v>
+        <v>7.28</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.61</v>
+        <v>1.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.68</v>
+        <v>3</v>
       </c>
       <c r="AD13" t="n">
-        <v>5.04</v>
+        <v>2.2</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.36</v>
+        <v>1.42</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.53</v>
+        <v>2.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>9.300000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['70', '72', '86', '89', '90+3']</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['65']</t>
         </is>
       </c>
       <c r="AL13" s="3" t="n">
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.02</v>
+        <v>1.75</v>
       </c>
       <c r="M14" t="n">
-        <v>3.35</v>
+        <v>3.12</v>
       </c>
       <c r="N14" t="n">
-        <v>2.05</v>
+        <v>4.33</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
+        <v>4</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V14" t="n">
+        <v>11</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AA14" t="n">
         <v>2.6</v>
       </c>
-      <c r="R14" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AB14" t="n">
-        <v>1.55</v>
+        <v>2.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.25</v>
+        <v>1.68</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.45</v>
+        <v>1.73</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
       <c r="M15" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="N15" t="n">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="O15" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T15" t="n">
         <v>3</v>
       </c>
-      <c r="R15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
       <c r="U15" t="n">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y15" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.11</v>
+        <v>1.35</v>
       </c>
       <c r="AA15" t="n">
-        <v>7.28</v>
+        <v>2.74</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.2</v>
+        <v>3.98</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.42</v>
+        <v>1.91</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="AH15" t="n">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.24</v>
+        <v>1.06</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="N16" t="n">
-        <v>2.91</v>
+        <v>3.23</v>
       </c>
       <c r="O16" t="n">
-        <v>2.85</v>
+        <v>2.6</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.41</v>
+        <v>2.63</v>
       </c>
       <c r="U16" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V16" t="n">
-        <v>5.35</v>
+        <v>7</v>
       </c>
       <c r="W16" t="n">
         <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.57</v>
+        <v>3.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH16" t="n">
-        <v>4.45</v>
+        <v>6.25</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="M17" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O17" t="n">
         <v>3.25</v>
       </c>
-      <c r="N17" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="O17" t="n">
-        <v>4.7</v>
-      </c>
       <c r="P17" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="R17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U17" t="n">
         <v>1.44</v>
       </c>
-      <c r="S17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.33</v>
-      </c>
       <c r="V17" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
         <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>7.5</v>
+        <v>10.9</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.95</v>
+        <v>2.9</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.77</v>
+        <v>2.17</v>
       </c>
       <c r="AH17" t="n">
-        <v>8</v>
+        <v>5.25</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="O18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V18" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF18" t="n">
         <v>1.98</v>
       </c>
-      <c r="M18" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="O18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>4</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V18" t="n">
-        <v>7</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X18" t="n">
+      <c r="AG18" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI18" t="n">
         <v>1.06</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1.12</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.39</v>
+        <v>2.29</v>
       </c>
       <c r="M19" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>5.7</v>
+        <v>2.8</v>
       </c>
       <c r="O19" t="n">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="P19" t="n">
-        <v>2.63</v>
+        <v>2.19</v>
       </c>
       <c r="Q19" t="n">
-        <v>6</v>
+        <v>3.35</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="U19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB19" t="n">
         <v>1.62</v>
       </c>
-      <c r="V19" t="n">
-        <v>5</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.58</v>
-      </c>
       <c r="AC19" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.15</v>
+        <v>2.65</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.75</v>
+        <v>1.39</v>
       </c>
       <c r="M20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N20" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>6</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S20" t="n">
         <v>3.75</v>
       </c>
-      <c r="N20" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="O20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P20" t="n">
+      <c r="T20" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.4</v>
-      </c>
       <c r="U20" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="V20" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z20" t="n">
         <v>1.17</v>
       </c>
       <c r="AA20" t="n">
-        <v>4.2</v>
+        <v>5.25</v>
       </c>
       <c r="AB20" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF20" t="n">
         <v>1.67</v>
       </c>
-      <c r="AC20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AG20" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AH20" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,73 +3182,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.6</v>
+        <v>2.01</v>
       </c>
       <c r="M21" t="n">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>2.46</v>
+        <v>2.91</v>
       </c>
       <c r="O21" t="n">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="P21" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T21" t="n">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="U21" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V21" t="n">
-        <v>6.5</v>
+        <v>5.35</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X21" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>10.9</v>
+        <v>10</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.9</v>
+        <v>2.57</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AH21" t="n">
-        <v>5.25</v>
+        <v>4.45</v>
       </c>
       <c r="AI21" t="n">
         <v>1.13</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.29</v>
+        <v>2.75</v>
       </c>
       <c r="M22" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="N22" t="n">
-        <v>2.8</v>
+        <v>2.44</v>
       </c>
       <c r="O22" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="P22" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="R22" t="n">
         <v>1.3</v>
       </c>
       <c r="S22" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="T22" t="n">
         <v>2.4</v>
       </c>
       <c r="U22" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="V22" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AA22" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AC22" t="n">
         <v>2.15</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG22" t="n">
         <v>2.4</v>
       </c>
       <c r="AH22" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,76 +3710,76 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>2</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>4</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T25" t="n">
         <v>3.15</v>
       </c>
-      <c r="M25" t="n">
-        <v>4.01</v>
-      </c>
-      <c r="N25" t="n">
-        <v>2</v>
-      </c>
-      <c r="O25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.25</v>
-      </c>
       <c r="U25" t="n">
-        <v>1.62</v>
+        <v>1.32</v>
       </c>
       <c r="V25" t="n">
-        <v>5.15</v>
+        <v>8.1</v>
       </c>
       <c r="W25" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="X25" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y25" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>5.73</v>
+        <v>2.9</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.5</v>
+        <v>2.16</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.45</v>
+        <v>1.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.65</v>
+        <v>1.18</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.46</v>
+        <v>1.83</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.6</v>
+        <v>1.77</v>
       </c>
       <c r="AH25" t="n">
-        <v>3.5</v>
+        <v>8.5</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,76 +3842,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="M26" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="N26" t="n">
-        <v>3.3</v>
+        <v>2.34</v>
       </c>
       <c r="O26" t="n">
-        <v>2.69</v>
+        <v>3.1</v>
       </c>
       <c r="P26" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="S26" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="T26" t="n">
-        <v>3.15</v>
+        <v>2.25</v>
       </c>
       <c r="U26" t="n">
-        <v>1.32</v>
+        <v>1.62</v>
       </c>
       <c r="V26" t="n">
-        <v>8.1</v>
+        <v>4.6</v>
       </c>
       <c r="W26" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="X26" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.35</v>
+        <v>1.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.16</v>
+        <v>1.47</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.7</v>
+        <v>2.35</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.77</v>
+        <v>2.55</v>
       </c>
       <c r="AH26" t="n">
-        <v>8.5</v>
+        <v>3.85</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,76 +3974,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.4</v>
+        <v>3.15</v>
       </c>
       <c r="M27" t="n">
-        <v>4.2</v>
+        <v>4.01</v>
       </c>
       <c r="N27" t="n">
-        <v>5.75</v>
+        <v>2</v>
       </c>
       <c r="O27" t="n">
-        <v>1.91</v>
+        <v>3.5</v>
       </c>
       <c r="P27" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q27" t="n">
-        <v>6</v>
+        <v>2.57</v>
       </c>
       <c r="R27" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="S27" t="n">
-        <v>3.22</v>
+        <v>3.85</v>
       </c>
       <c r="T27" t="n">
         <v>2.25</v>
       </c>
       <c r="U27" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="V27" t="n">
-        <v>5.8</v>
+        <v>5.15</v>
       </c>
       <c r="W27" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="X27" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y27" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.37</v>
+        <v>1.15</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.91</v>
+        <v>5.73</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.83</v>
+        <v>1.46</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.91</v>
+        <v>2.6</v>
       </c>
       <c r="AH27" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.62</v>
+        <v>1.4</v>
       </c>
       <c r="M28" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="N28" t="n">
-        <v>2.34</v>
+        <v>5.75</v>
       </c>
       <c r="O28" t="n">
-        <v>3.1</v>
+        <v>1.91</v>
       </c>
       <c r="P28" t="n">
         <v>2.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="R28" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S28" t="n">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="T28" t="n">
         <v>2.25</v>
       </c>
       <c r="U28" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="V28" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="W28" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X28" t="n">
         <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.1</v>
+        <v>1.37</v>
       </c>
       <c r="AA28" t="n">
-        <v>5.1</v>
+        <v>2.91</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.35</v>
+        <v>2.46</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.55</v>
+        <v>1.91</v>
       </c>
       <c r="AH28" t="n">
-        <v>3.85</v>
+        <v>4.33</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.19</v>
+        <v>1.53</v>
       </c>
       <c r="M30" t="n">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="N30" t="n">
-        <v>12.25</v>
+        <v>4.75</v>
       </c>
       <c r="O30" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="P30" t="n">
-        <v>2.61</v>
+        <v>2.38</v>
       </c>
       <c r="Q30" t="n">
-        <v>9.1</v>
+        <v>5.5</v>
       </c>
       <c r="R30" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="S30" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="T30" t="n">
-        <v>2.19</v>
+        <v>2.63</v>
       </c>
       <c r="U30" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="V30" t="n">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="W30" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AI30" t="n">
         <v>1.14</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>1.25</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.53</v>
+        <v>3.12</v>
       </c>
       <c r="M31" t="n">
-        <v>3.9</v>
+        <v>2.91</v>
       </c>
       <c r="N31" t="n">
-        <v>4.75</v>
+        <v>2.19</v>
       </c>
       <c r="O31" t="n">
-        <v>2.1</v>
+        <v>4.05</v>
       </c>
       <c r="P31" t="n">
-        <v>2.38</v>
+        <v>1.98</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.5</v>
+        <v>2.84</v>
       </c>
       <c r="R31" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U31" t="n">
         <v>1.33</v>
       </c>
-      <c r="S31" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.44</v>
-      </c>
       <c r="V31" t="n">
-        <v>6.5</v>
+        <v>7.4</v>
       </c>
       <c r="W31" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X31" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y31" t="n">
-        <v>9.5</v>
+        <v>7.3</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.8</v>
+        <v>2.84</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.05</v>
+        <v>1.55</v>
       </c>
       <c r="AD31" t="n">
-        <v>3</v>
+        <v>3.52</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH31" t="n">
-        <v>5.5</v>
+        <v>6.85</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,76 +4634,76 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.12</v>
+        <v>1.19</v>
       </c>
       <c r="M32" t="n">
-        <v>2.91</v>
+        <v>6</v>
       </c>
       <c r="N32" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T32" t="n">
         <v>2.19</v>
       </c>
-      <c r="O32" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="P32" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T32" t="n">
-        <v>3.04</v>
-      </c>
       <c r="U32" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="V32" t="n">
-        <v>7.4</v>
+        <v>4.6</v>
       </c>
       <c r="W32" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="X32" t="n">
         <v>1.03</v>
       </c>
       <c r="Y32" t="n">
-        <v>7.3</v>
+        <v>19</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.84</v>
+        <v>5</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.4</v>
+        <v>1.42</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.55</v>
+        <v>2.49</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.52</v>
+        <v>2.1</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.22</v>
+        <v>1.66</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="AH32" t="n">
-        <v>6.85</v>
+        <v>3.28</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="M34" t="n">
-        <v>4.31</v>
+        <v>4.2</v>
       </c>
       <c r="N34" t="n">
-        <v>5.1</v>
+        <v>3.75</v>
       </c>
       <c r="O34" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="P34" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="Q34" t="n">
-        <v>5</v>
+        <v>3.95</v>
       </c>
       <c r="R34" t="n">
         <v>1.2</v>
       </c>
       <c r="S34" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="T34" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="U34" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="V34" t="n">
-        <v>4.7</v>
+        <v>4.05</v>
       </c>
       <c r="W34" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="X34" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AA34" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.47</v>
+        <v>2.9</v>
       </c>
       <c r="AD34" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AH34" t="n">
         <v>3.2</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="M35" t="n">
-        <v>4.2</v>
+        <v>4.31</v>
       </c>
       <c r="N35" t="n">
-        <v>3.75</v>
+        <v>5.1</v>
       </c>
       <c r="O35" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="P35" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="R35" t="n">
         <v>1.2</v>
       </c>
       <c r="S35" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="T35" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="U35" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V35" t="n">
-        <v>4.05</v>
+        <v>4.7</v>
       </c>
       <c r="W35" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="X35" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y35" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AA35" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.9</v>
+        <v>2.47</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AH35" t="n">
         <v>3.2</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5426,37 +5426,37 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.54</v>
+        <v>2.47</v>
       </c>
       <c r="M38" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="N38" t="n">
-        <v>2.86</v>
+        <v>3.15</v>
       </c>
       <c r="O38" t="n">
-        <v>3.39</v>
+        <v>3.14</v>
       </c>
       <c r="P38" t="n">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.67</v>
+        <v>3.8</v>
       </c>
       <c r="R38" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="S38" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="T38" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="U38" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="V38" t="n">
-        <v>12</v>
+        <v>9.1</v>
       </c>
       <c r="W38" t="n">
         <v>1.03</v>
@@ -5465,28 +5465,28 @@
         <v>1.08</v>
       </c>
       <c r="Y38" t="n">
-        <v>5.5</v>
+        <v>6.25</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.35</v>
+        <v>2.53</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AD38" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AG38" t="n">
         <v>1.7</v>
@@ -5495,7 +5495,7 @@
         <v>13</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,76 +5954,76 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.29</v>
+        <v>2.66</v>
       </c>
       <c r="M42" t="n">
-        <v>2.94</v>
+        <v>3.63</v>
       </c>
       <c r="N42" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O42" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V42" t="n">
+        <v>7</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG42" t="n">
         <v>2.1</v>
       </c>
-      <c r="O42" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="P42" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S42" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T42" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V42" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X42" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AH42" t="n">
-        <v>9</v>
+        <v>5.85</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,76 +6086,76 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="M43" t="n">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="N43" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="O43" t="n">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="P43" t="n">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="R43" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="S43" t="n">
-        <v>3.75</v>
+        <v>2.35</v>
       </c>
       <c r="T43" t="n">
-        <v>2.23</v>
+        <v>3.42</v>
       </c>
       <c r="U43" t="n">
-        <v>1.55</v>
+        <v>1.28</v>
       </c>
       <c r="V43" t="n">
-        <v>3.8</v>
+        <v>7.8</v>
       </c>
       <c r="W43" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.15</v>
+        <v>1.52</v>
       </c>
       <c r="AA43" t="n">
-        <v>4.3</v>
+        <v>2.53</v>
       </c>
       <c r="AB43" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AC43" t="n">
         <v>1.5</v>
       </c>
-      <c r="AC43" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AD43" t="n">
-        <v>2.22</v>
+        <v>4.75</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.44</v>
+        <v>2.09</v>
       </c>
       <c r="AG43" t="n">
-        <v>2.64</v>
+        <v>1.68</v>
       </c>
       <c r="AH43" t="n">
-        <v>3.58</v>
+        <v>9.5</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,76 +6218,76 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="M44" t="n">
-        <v>3.63</v>
+        <v>3.85</v>
       </c>
       <c r="N44" t="n">
-        <v>2.47</v>
+        <v>2.23</v>
       </c>
       <c r="O44" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="P44" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="R44" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="T44" t="n">
-        <v>2.75</v>
+        <v>2.23</v>
       </c>
       <c r="U44" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="V44" t="n">
-        <v>7</v>
+        <v>3.8</v>
       </c>
       <c r="W44" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="X44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AA44" t="n">
-        <v>3.36</v>
+        <v>4.3</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.94</v>
+        <v>1.5</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.88</v>
+        <v>2.4</v>
       </c>
       <c r="AD44" t="n">
-        <v>3.08</v>
+        <v>2.22</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AG44" t="n">
-        <v>2.1</v>
+        <v>2.64</v>
       </c>
       <c r="AH44" t="n">
-        <v>5.85</v>
+        <v>3.58</v>
       </c>
       <c r="AI44" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
@@ -6614,73 +6614,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="M47" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N47" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O47" t="n">
         <v>2.83</v>
       </c>
-      <c r="N47" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="O47" t="n">
-        <v>3.04</v>
-      </c>
       <c r="P47" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.49</v>
+        <v>4.33</v>
       </c>
       <c r="R47" t="n">
         <v>1.5</v>
       </c>
       <c r="S47" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="T47" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U47" t="n">
         <v>1.22</v>
       </c>
       <c r="V47" t="n">
-        <v>8.5</v>
+        <v>13</v>
       </c>
       <c r="W47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X47" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Y47" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AB47" t="n">
-        <v>2.37</v>
+        <v>2.7</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AD47" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF47" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AH47" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AI47" t="n">
         <v>1.03</v>

--- a/jogos_2025-08-11.xlsx
+++ b/jogos_2025-08-11.xlsx
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,25 +1704,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="n">
         <v>1</v>
       </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1730,85 +1730,85 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.72</v>
+        <v>2.2</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>5</v>
+        <v>3.35</v>
       </c>
       <c r="O10" t="n">
-        <v>2.42</v>
+        <v>3.07</v>
       </c>
       <c r="P10" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.34</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>2.31</v>
+        <v>2.6</v>
       </c>
       <c r="T10" t="n">
-        <v>3.66</v>
+        <v>3.1</v>
       </c>
       <c r="U10" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>9.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="W10" t="n">
         <v>1.02</v>
       </c>
       <c r="X10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AI10" t="n">
         <v>1.06</v>
       </c>
-      <c r="Y10" t="n">
-        <v>5.79</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>5.04</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+5', '90']</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>['41']</t>
+          <t>['23', '27', '50']</t>
         </is>
       </c>
       <c r="AL10" s="3" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,111 +1836,111 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G11" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T11" t="n">
         <v>2</v>
       </c>
-      <c r="H11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="M11" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="O11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.3</v>
-      </c>
       <c r="U11" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="V11" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="X11" t="n">
         <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>9.300000000000001</v>
+        <v>12</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.6</v>
+        <v>7.28</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.71</v>
+        <v>1.42</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>4.7</v>
+        <v>3.2</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>['-1', '-1']</t>
+          <t>['70', '72', '86', '89', '90+3']</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>['-1', '-1']</t>
+          <t>['65']</t>
         </is>
       </c>
       <c r="AL11" s="3" t="n">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,102 +1968,102 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>3.35</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
-        <v>3.07</v>
+        <v>2.42</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>6.34</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="S12" t="n">
-        <v>2.6</v>
+        <v>2.31</v>
       </c>
       <c r="T12" t="n">
-        <v>3.1</v>
+        <v>3.66</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="V12" t="n">
-        <v>8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W12" t="n">
         <v>1.02</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>7.5</v>
+        <v>5.79</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.37</v>
+        <v>1.56</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.88</v>
+        <v>2.33</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.1</v>
+        <v>2.61</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.99</v>
+        <v>5.04</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.85</v>
+        <v>2.36</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AH12" t="n">
-        <v>7.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['41']</t>
         </is>
       </c>
       <c r="AL12" s="3" t="n">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,16 +2100,16 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>1</v>
@@ -2126,85 +2126,85 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="N13" t="n">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="O13" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="P13" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T13" t="n">
         <v>3</v>
       </c>
-      <c r="R13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
       <c r="U13" t="n">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="V13" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y13" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.11</v>
+        <v>1.35</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.28</v>
+        <v>2.74</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.2</v>
+        <v>3.98</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.42</v>
+        <v>1.91</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.24</v>
+        <v>1.06</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>['70', '72', '86', '89', '90+3']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>['65']</t>
+          <t>['-1']</t>
         </is>
       </c>
       <c r="AL13" s="3" t="n">
@@ -2241,20 +2241,20 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -2331,12 +2331,12 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['18', '45+2', '84']</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['83']</t>
         </is>
       </c>
       <c r="AL14" s="3" t="n">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,19 +2364,19 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -2386,89 +2386,89 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.49</v>
+        <v>3.02</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>2.85</v>
+        <v>2.05</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="S15" t="n">
-        <v>2.62</v>
+        <v>3.14</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="V15" t="n">
-        <v>7.5</v>
+        <v>4.8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X15" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.74</v>
+        <v>4.6</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.98</v>
+        <v>2.63</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.17</v>
+        <v>1.48</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="AH15" t="n">
-        <v>9</v>
+        <v>4.7</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['-1', '-1']</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['-1', '-1']</t>
         </is>
       </c>
       <c r="AL15" s="3" t="n">
@@ -2486,121 +2486,121 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="M16" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>3.23</v>
+        <v>2.91</v>
       </c>
       <c r="O16" t="n">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="P16" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="R16" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T16" t="n">
-        <v>2.63</v>
+        <v>2.41</v>
       </c>
       <c r="U16" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V16" t="n">
-        <v>7</v>
+        <v>5.35</v>
       </c>
       <c r="W16" t="n">
         <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.25</v>
+        <v>2.57</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH16" t="n">
-        <v>6.25</v>
+        <v>4.45</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['74']</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['16', '27', '35', '72']</t>
         </is>
       </c>
       <c r="AL16" s="3" t="n">
@@ -2640,7 +2640,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['61']</t>
         </is>
       </c>
       <c r="AL17" s="3" t="n">
@@ -2750,121 +2750,121 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.6</v>
+        <v>1.39</v>
       </c>
       <c r="M18" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="N18" t="n">
-        <v>1.93</v>
+        <v>5.7</v>
       </c>
       <c r="O18" t="n">
-        <v>4.7</v>
+        <v>1.83</v>
       </c>
       <c r="P18" t="n">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.56</v>
+        <v>6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>2.6</v>
+        <v>3.75</v>
       </c>
       <c r="T18" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="U18" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="V18" t="n">
-        <v>8.5</v>
+        <v>5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="X18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>7.5</v>
+        <v>11</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.88</v>
+        <v>5.25</v>
       </c>
       <c r="AB18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG18" t="n">
         <v>2.1</v>
       </c>
-      <c r="AC18" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AH18" t="n">
-        <v>8</v>
+        <v>3.9</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45', '77']</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['62', '72']</t>
         </is>
       </c>
       <c r="AL18" s="3" t="n">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,111 +2892,111 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.29</v>
+        <v>3.15</v>
       </c>
       <c r="M19" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="N19" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="O19" t="n">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="P19" t="n">
-        <v>2.19</v>
+        <v>1.85</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.35</v>
+        <v>3.12</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3</v>
+        <v>1.61</v>
       </c>
       <c r="S19" t="n">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="T19" t="n">
-        <v>2.4</v>
+        <v>3.85</v>
       </c>
       <c r="U19" t="n">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="V19" t="n">
-        <v>5.3</v>
+        <v>11.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="Y19" t="n">
-        <v>9.199999999999999</v>
+        <v>6.11</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.2</v>
+        <v>1.58</v>
       </c>
       <c r="AA19" t="n">
-        <v>4.1</v>
+        <v>2.33</v>
       </c>
       <c r="AB19" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG19" t="n">
         <v>1.62</v>
       </c>
-      <c r="AC19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AH19" t="n">
-        <v>4.33</v>
+        <v>13</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['77']</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['9', '64']</t>
         </is>
       </c>
       <c r="AL19" s="3" t="n">
@@ -3014,121 +3014,121 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.39</v>
+        <v>3.6</v>
       </c>
       <c r="M20" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>5.7</v>
+        <v>1.93</v>
       </c>
       <c r="O20" t="n">
-        <v>1.83</v>
+        <v>4.7</v>
       </c>
       <c r="P20" t="n">
-        <v>2.63</v>
+        <v>2.05</v>
       </c>
       <c r="Q20" t="n">
-        <v>6</v>
+        <v>2.56</v>
       </c>
       <c r="R20" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="S20" t="n">
-        <v>3.75</v>
+        <v>2.6</v>
       </c>
       <c r="T20" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="U20" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="V20" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>11</v>
+        <v>7.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="AA20" t="n">
-        <v>5.25</v>
+        <v>2.88</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.58</v>
+        <v>2.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.18</v>
+        <v>1.66</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.15</v>
+        <v>3.95</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.62</v>
+        <v>1.18</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.9</v>
+        <v>8</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['17', '27']</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['48', '58']</t>
         </is>
       </c>
       <c r="AL20" s="3" t="n">
@@ -3146,112 +3146,112 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="N21" t="n">
-        <v>2.91</v>
+        <v>3.23</v>
       </c>
       <c r="O21" t="n">
-        <v>2.85</v>
+        <v>2.6</v>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>2.41</v>
+        <v>2.63</v>
       </c>
       <c r="U21" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V21" t="n">
-        <v>5.35</v>
+        <v>7</v>
       </c>
       <c r="W21" t="n">
         <v>1.1</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AA21" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.57</v>
+        <v>3.25</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH21" t="n">
-        <v>4.45</v>
+        <v>6.25</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['12']</t>
         </is>
       </c>
       <c r="AL21" s="3" t="n">
@@ -3297,20 +3297,20 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -3387,12 +3387,12 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['5', '43', '45+1']</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7', '24']</t>
         </is>
       </c>
       <c r="AL22" s="3" t="n">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,111 +3420,111 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.15</v>
+        <v>2.29</v>
       </c>
       <c r="M23" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="N23" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="O23" t="n">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="P23" t="n">
-        <v>1.85</v>
+        <v>2.19</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.12</v>
+        <v>3.35</v>
       </c>
       <c r="R23" t="n">
-        <v>1.61</v>
+        <v>1.3</v>
       </c>
       <c r="S23" t="n">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="T23" t="n">
-        <v>3.85</v>
+        <v>2.4</v>
       </c>
       <c r="U23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z23" t="n">
         <v>1.2</v>
       </c>
-      <c r="V23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>6.11</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.58</v>
-      </c>
       <c r="AA23" t="n">
-        <v>2.33</v>
+        <v>4.1</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.67</v>
+        <v>1.62</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.37</v>
+        <v>2.15</v>
       </c>
       <c r="AD23" t="n">
-        <v>5.45</v>
+        <v>2.65</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.08</v>
+        <v>1.5</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="AH23" t="n">
-        <v>13</v>
+        <v>4.33</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['3', '45+1', '79']</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['38', '41', '53']</t>
         </is>
       </c>
       <c r="AL23" s="3" t="n">
@@ -3561,20 +3561,20 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['36']</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['75']</t>
         </is>
       </c>
       <c r="AL24" s="3" t="n">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,111 +3684,111 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L25" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="M25" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="N25" t="n">
         <v>2</v>
       </c>
-      <c r="M25" t="n">
-        <v>3</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3.3</v>
-      </c>
       <c r="O25" t="n">
-        <v>2.69</v>
+        <v>3.5</v>
       </c>
       <c r="P25" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>2.57</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="S25" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V25" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AG25" t="n">
         <v>2.6</v>
       </c>
-      <c r="T25" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V25" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AE25" t="n">
+      <c r="AH25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AI25" t="n">
         <v>1.18</v>
       </c>
-      <c r="AF25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['19', '26']</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['14', '28', '72']</t>
         </is>
       </c>
       <c r="AL25" s="3" t="n">
@@ -3825,20 +3825,20 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['17', '49', '89']</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['78']</t>
         </is>
       </c>
       <c r="AL26" s="3" t="n">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,111 +3948,111 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.15</v>
+        <v>1.4</v>
       </c>
       <c r="M27" t="n">
-        <v>4.01</v>
+        <v>4.2</v>
       </c>
       <c r="N27" t="n">
-        <v>2</v>
+        <v>5.75</v>
       </c>
       <c r="O27" t="n">
-        <v>3.5</v>
+        <v>1.91</v>
       </c>
       <c r="P27" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.57</v>
+        <v>6</v>
       </c>
       <c r="R27" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="S27" t="n">
-        <v>3.85</v>
+        <v>3.22</v>
       </c>
       <c r="T27" t="n">
         <v>2.25</v>
       </c>
       <c r="U27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V27" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AB27" t="n">
         <v>1.62</v>
       </c>
-      <c r="V27" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>5.73</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AC27" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.46</v>
+        <v>1.83</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="AH27" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['15', '20', '62', '79']</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['33', '45', '73']</t>
         </is>
       </c>
       <c r="AL27" s="3" t="n">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,106 +4080,106 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L28" t="n">
+        <v>2</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O28" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>4</v>
+      </c>
+      <c r="R28" t="n">
         <v>1.4</v>
       </c>
-      <c r="M28" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N28" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>6</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.28</v>
-      </c>
       <c r="S28" t="n">
-        <v>3.22</v>
+        <v>2.6</v>
       </c>
       <c r="T28" t="n">
-        <v>2.25</v>
+        <v>3.15</v>
       </c>
       <c r="U28" t="n">
-        <v>1.55</v>
+        <v>1.32</v>
       </c>
       <c r="V28" t="n">
-        <v>5.8</v>
+        <v>8.1</v>
       </c>
       <c r="W28" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="X28" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y28" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.62</v>
+        <v>2.16</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.15</v>
+        <v>1.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.46</v>
+        <v>3.7</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.43</v>
+        <v>1.18</v>
       </c>
       <c r="AF28" t="n">
         <v>1.83</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="AH28" t="n">
-        <v>4.33</v>
+        <v>8.5</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['15']</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -4485,20 +4485,20 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -4575,12 +4575,12 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['33']</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['60']</t>
         </is>
       </c>
       <c r="AL31" s="3" t="n">
@@ -4617,20 +4617,20 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L32" t="n">
@@ -4707,12 +4707,12 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['18', '79']</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['55', '67']</t>
         </is>
       </c>
       <c r="AL32" s="3" t="n">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,76 +5954,76 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.66</v>
+        <v>3.75</v>
       </c>
       <c r="M42" t="n">
-        <v>3.63</v>
+        <v>3</v>
       </c>
       <c r="N42" t="n">
-        <v>2.47</v>
+        <v>2.1</v>
       </c>
       <c r="O42" t="n">
-        <v>3.25</v>
+        <v>4.25</v>
       </c>
       <c r="P42" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.2</v>
+        <v>2.69</v>
       </c>
       <c r="R42" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>2.35</v>
       </c>
       <c r="T42" t="n">
-        <v>2.75</v>
+        <v>3.42</v>
       </c>
       <c r="U42" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="V42" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y42" t="n">
         <v>7</v>
       </c>
-      <c r="W42" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X42" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="Z42" t="n">
-        <v>1.24</v>
+        <v>1.52</v>
       </c>
       <c r="AA42" t="n">
-        <v>3.36</v>
+        <v>2.53</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.94</v>
+        <v>2.53</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.88</v>
+        <v>1.5</v>
       </c>
       <c r="AD42" t="n">
-        <v>3.08</v>
+        <v>4.75</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.67</v>
+        <v>2.09</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="AH42" t="n">
-        <v>5.85</v>
+        <v>9.5</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,76 +6086,76 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.75</v>
+        <v>2.66</v>
       </c>
       <c r="M43" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="N43" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O43" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S43" t="n">
         <v>3</v>
       </c>
-      <c r="N43" t="n">
+      <c r="T43" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V43" t="n">
+        <v>7</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG43" t="n">
         <v>2.1</v>
       </c>
-      <c r="O43" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="P43" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S43" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="T43" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V43" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1</v>
-      </c>
-      <c r="X43" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AH43" t="n">
-        <v>9.5</v>
+        <v>5.85</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>

--- a/jogos_2025-08-11.xlsx
+++ b/jogos_2025-08-11.xlsx
@@ -1694,35 +1694,35 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1730,85 +1730,85 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.2</v>
+        <v>3.02</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>3.35</v>
+        <v>2.05</v>
       </c>
       <c r="O10" t="n">
-        <v>3.07</v>
+        <v>3.4</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="S10" t="n">
-        <v>2.6</v>
+        <v>3.14</v>
       </c>
       <c r="T10" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="U10" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="V10" t="n">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="W10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X10" t="n">
         <v>1.02</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y10" t="n">
-        <v>7.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.37</v>
+        <v>1.16</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.88</v>
+        <v>4.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.66</v>
+        <v>2.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.99</v>
+        <v>2.63</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.18</v>
+        <v>1.48</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.85</v>
+        <v>2.45</v>
       </c>
       <c r="AH10" t="n">
-        <v>7.8</v>
+        <v>4.7</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>['45+5', '90']</t>
+          <t>['-1', '-1']</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>['23', '27', '50']</t>
+          <t>['-1', '-1']</t>
         </is>
       </c>
       <c r="AL10" s="3" t="n">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,25 +1968,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1994,85 +1994,85 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="O12" t="n">
-        <v>2.42</v>
+        <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.34</v>
+        <v>4</v>
       </c>
       <c r="R12" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="T12" t="n">
-        <v>3.66</v>
+        <v>3.5</v>
       </c>
       <c r="U12" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="V12" t="n">
-        <v>9.300000000000001</v>
+        <v>11</v>
       </c>
       <c r="W12" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.79</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.61</v>
+        <v>2.2</v>
       </c>
       <c r="AC12" t="n">
         <v>1.68</v>
       </c>
       <c r="AD12" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.36</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AH12" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['18', '45+2', '84']</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>['41']</t>
+          <t>['83']</t>
         </is>
       </c>
       <c r="AL12" s="3" t="n">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,42 +2232,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="n">
         <v>3</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>1</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>2</v>
       </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="M14" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>4.33</v>
+        <v>3.35</v>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="P14" t="n">
         <v>2</v>
@@ -2276,67 +2276,67 @@
         <v>4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="T14" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="U14" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>['18', '45+2', '84']</t>
+          <t>['45+5', '90']</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>['83']</t>
+          <t>['23', '27', '50']</t>
         </is>
       </c>
       <c r="AL14" s="3" t="n">
@@ -2354,35 +2354,35 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2390,85 +2390,85 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.02</v>
+        <v>1.72</v>
       </c>
       <c r="M15" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>2.05</v>
+        <v>5</v>
       </c>
       <c r="O15" t="n">
-        <v>3.4</v>
+        <v>2.42</v>
       </c>
       <c r="P15" t="n">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.6</v>
+        <v>6.34</v>
       </c>
       <c r="R15" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="S15" t="n">
-        <v>3.14</v>
+        <v>2.31</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3</v>
+        <v>3.66</v>
       </c>
       <c r="U15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V15" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.53</v>
       </c>
-      <c r="V15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y15" t="n">
+      <c r="AH15" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="Z15" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>4.7</v>
-      </c>
       <c r="AI15" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>['-1', '-1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>['-1', '-1']</t>
+          <t>['41']</t>
         </is>
       </c>
       <c r="AL15" s="3" t="n">
@@ -2618,33 +2618,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="n">
         <v>1</v>
       </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
@@ -2654,85 +2654,85 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.6</v>
+        <v>1.39</v>
       </c>
       <c r="M17" t="n">
-        <v>3.64</v>
+        <v>4.5</v>
       </c>
       <c r="N17" t="n">
-        <v>2.46</v>
+        <v>5.7</v>
       </c>
       <c r="O17" t="n">
-        <v>3.25</v>
+        <v>1.83</v>
       </c>
       <c r="P17" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>6</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V17" t="n">
+        <v>5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AD17" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="Z17" t="n">
+      <c r="AE17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AI17" t="n">
         <v>1.25</v>
       </c>
-      <c r="AA17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45', '77']</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>['61']</t>
+          <t>['62', '72']</t>
         </is>
       </c>
       <c r="AL17" s="3" t="n">
@@ -2750,121 +2750,121 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" t="n">
         <v>2</v>
       </c>
-      <c r="H18" t="n">
+      <c r="J18" t="n">
         <v>2</v>
       </c>
-      <c r="I18" t="n">
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X18" t="n">
         <v>1</v>
       </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N18" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>6</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U18" t="n">
+      <c r="Y18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB18" t="n">
         <v>1.62</v>
       </c>
-      <c r="V18" t="n">
-        <v>5</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.58</v>
-      </c>
       <c r="AC18" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.15</v>
+        <v>2.65</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>['45', '77']</t>
+          <t>['3', '45+1', '79']</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>['62', '72']</t>
+          <t>['38', '41', '53']</t>
         </is>
       </c>
       <c r="AL18" s="3" t="n">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,25 +2892,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H19" t="n">
         <v>2</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2918,85 +2918,85 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.15</v>
+        <v>2.75</v>
       </c>
       <c r="M19" t="n">
-        <v>3.04</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P19" t="n">
         <v>2.2</v>
       </c>
-      <c r="O19" t="n">
-        <v>4</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.85</v>
-      </c>
       <c r="Q19" t="n">
-        <v>3.12</v>
+        <v>2.9</v>
       </c>
       <c r="R19" t="n">
-        <v>1.61</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="T19" t="n">
-        <v>3.85</v>
+        <v>2.4</v>
       </c>
       <c r="U19" t="n">
-        <v>1.2</v>
+        <v>1.55</v>
       </c>
       <c r="V19" t="n">
-        <v>11.5</v>
+        <v>5.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="X19" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>6.11</v>
+        <v>13</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.58</v>
+        <v>1.17</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.33</v>
+        <v>4.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.67</v>
+        <v>1.67</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.37</v>
+        <v>2.15</v>
       </c>
       <c r="AD19" t="n">
-        <v>5.45</v>
+        <v>2.6</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.08</v>
+        <v>1.48</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="AH19" t="n">
-        <v>13</v>
+        <v>4.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>['77']</t>
+          <t>['5', '43', '45+1']</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>['9', '64']</t>
+          <t>['7', '24']</t>
         </is>
       </c>
       <c r="AL19" s="3" t="n">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,25 +3288,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3314,19 +3314,19 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="M22" t="n">
-        <v>3.75</v>
+        <v>3.64</v>
       </c>
       <c r="N22" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="O22" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P22" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q22" t="n">
         <v>2.9</v>
@@ -3335,64 +3335,64 @@
         <v>1.3</v>
       </c>
       <c r="S22" t="n">
+        <v>3</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V22" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA22" t="n">
         <v>3.5</v>
       </c>
-      <c r="T22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V22" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AB22" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AH22" t="n">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>['5', '43', '45+1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>['7', '24']</t>
+          <t>['61']</t>
         </is>
       </c>
       <c r="AL22" s="3" t="n">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,25 +3420,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3446,85 +3446,85 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.29</v>
+        <v>3.15</v>
       </c>
       <c r="M23" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="N23" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="O23" t="n">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="P23" t="n">
-        <v>2.19</v>
+        <v>1.85</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.35</v>
+        <v>3.12</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3</v>
+        <v>1.61</v>
       </c>
       <c r="S23" t="n">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="T23" t="n">
-        <v>2.4</v>
+        <v>3.85</v>
       </c>
       <c r="U23" t="n">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="V23" t="n">
-        <v>5.3</v>
+        <v>11.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="Y23" t="n">
-        <v>9.199999999999999</v>
+        <v>6.11</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.2</v>
+        <v>1.58</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.1</v>
+        <v>2.33</v>
       </c>
       <c r="AB23" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG23" t="n">
         <v>1.62</v>
       </c>
-      <c r="AC23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AH23" t="n">
-        <v>4.33</v>
+        <v>13</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>['3', '45+1', '79']</t>
+          <t>['77']</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>['38', '41', '53']</t>
+          <t>['9', '64']</t>
         </is>
       </c>
       <c r="AL23" s="3" t="n">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,16 +3684,16 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H25" t="n">
         <v>3</v>
@@ -3710,85 +3710,85 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.15</v>
+        <v>1.4</v>
       </c>
       <c r="M25" t="n">
-        <v>4.01</v>
+        <v>4.2</v>
       </c>
       <c r="N25" t="n">
-        <v>2</v>
+        <v>5.75</v>
       </c>
       <c r="O25" t="n">
-        <v>3.5</v>
+        <v>1.91</v>
       </c>
       <c r="P25" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.57</v>
+        <v>6</v>
       </c>
       <c r="R25" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="S25" t="n">
-        <v>3.85</v>
+        <v>3.22</v>
       </c>
       <c r="T25" t="n">
         <v>2.25</v>
       </c>
       <c r="U25" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V25" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AB25" t="n">
         <v>1.62</v>
       </c>
-      <c r="V25" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>5.73</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AC25" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.46</v>
+        <v>1.83</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="AH25" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>['19', '26']</t>
+          <t>['15', '20', '62', '79']</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>['14', '28', '72']</t>
+          <t>['33', '45', '73']</t>
         </is>
       </c>
       <c r="AL25" s="3" t="n">
@@ -3816,25 +3816,25 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" t="n">
         <v>3</v>
       </c>
-      <c r="H26" t="n">
-        <v>1</v>
-      </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3842,28 +3842,28 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.62</v>
+        <v>3.15</v>
       </c>
       <c r="M26" t="n">
-        <v>3.55</v>
+        <v>4.01</v>
       </c>
       <c r="N26" t="n">
-        <v>2.34</v>
+        <v>2</v>
       </c>
       <c r="O26" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="P26" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="R26" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="S26" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="T26" t="n">
         <v>2.25</v>
@@ -3872,55 +3872,55 @@
         <v>1.62</v>
       </c>
       <c r="V26" t="n">
-        <v>4.6</v>
+        <v>5.15</v>
       </c>
       <c r="W26" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z26" t="n">
         <v>1.15</v>
       </c>
-      <c r="X26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AA26" t="n">
-        <v>5.1</v>
+        <v>5.73</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AH26" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>['17', '49', '89']</t>
+          <t>['19', '26']</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>['78']</t>
+          <t>['14', '28', '72']</t>
         </is>
       </c>
       <c r="AL26" s="3" t="n">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,111 +3948,111 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>2</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q27" t="n">
         <v>4</v>
       </c>
-      <c r="H27" t="n">
-        <v>3</v>
-      </c>
-      <c r="I27" t="n">
-        <v>2</v>
-      </c>
-      <c r="J27" t="n">
-        <v>2</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
+      <c r="R27" t="n">
         <v>1.4</v>
       </c>
-      <c r="M27" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N27" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>6</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.28</v>
-      </c>
       <c r="S27" t="n">
-        <v>3.22</v>
+        <v>2.6</v>
       </c>
       <c r="T27" t="n">
-        <v>2.25</v>
+        <v>3.15</v>
       </c>
       <c r="U27" t="n">
-        <v>1.55</v>
+        <v>1.32</v>
       </c>
       <c r="V27" t="n">
-        <v>5.8</v>
+        <v>8.1</v>
       </c>
       <c r="W27" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="X27" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y27" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.62</v>
+        <v>2.16</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.15</v>
+        <v>1.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.46</v>
+        <v>3.7</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.43</v>
+        <v>1.18</v>
       </c>
       <c r="AF27" t="n">
         <v>1.83</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="AH27" t="n">
-        <v>4.33</v>
+        <v>8.5</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>['15', '20', '62', '79']</t>
+          <t>['15']</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>['33', '45', '73']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AL27" s="3" t="n">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,19 +4080,19 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G28" t="n">
+        <v>3</v>
+      </c>
+      <c r="H28" t="n">
         <v>1</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>1</v>
@@ -4106,85 +4106,85 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="M28" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="N28" t="n">
-        <v>3.3</v>
+        <v>2.34</v>
       </c>
       <c r="O28" t="n">
-        <v>2.69</v>
+        <v>3.1</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="S28" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="T28" t="n">
-        <v>3.15</v>
+        <v>2.25</v>
       </c>
       <c r="U28" t="n">
-        <v>1.32</v>
+        <v>1.62</v>
       </c>
       <c r="V28" t="n">
-        <v>8.1</v>
+        <v>4.6</v>
       </c>
       <c r="W28" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="X28" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.35</v>
+        <v>1.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.16</v>
+        <v>1.47</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.7</v>
+        <v>2.35</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.77</v>
+        <v>2.55</v>
       </c>
       <c r="AH28" t="n">
-        <v>8.5</v>
+        <v>3.85</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>['15']</t>
+          <t>['17', '49', '89']</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['78']</t>
         </is>
       </c>
       <c r="AL28" s="3" t="n">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L29" t="n">
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L30" t="n">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['49']</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,19 +4476,19 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I31" t="n">
         <v>1</v>
@@ -4502,85 +4502,85 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.12</v>
+        <v>1.19</v>
       </c>
       <c r="M31" t="n">
-        <v>2.91</v>
+        <v>6</v>
       </c>
       <c r="N31" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T31" t="n">
         <v>2.19</v>
       </c>
-      <c r="O31" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3.04</v>
-      </c>
       <c r="U31" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="V31" t="n">
-        <v>7.4</v>
+        <v>4.6</v>
       </c>
       <c r="W31" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="X31" t="n">
         <v>1.03</v>
       </c>
       <c r="Y31" t="n">
-        <v>7.3</v>
+        <v>19</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.84</v>
+        <v>5</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.4</v>
+        <v>1.42</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.55</v>
+        <v>2.49</v>
       </c>
       <c r="AD31" t="n">
-        <v>3.52</v>
+        <v>2.1</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.22</v>
+        <v>1.66</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="AH31" t="n">
-        <v>6.85</v>
+        <v>3.28</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>['33']</t>
+          <t>['18', '79']</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>['60']</t>
+          <t>['55', '67']</t>
         </is>
       </c>
       <c r="AL31" s="3" t="n">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,19 +4608,19 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
         <v>1</v>
@@ -4634,85 +4634,85 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.19</v>
+        <v>3.12</v>
       </c>
       <c r="M32" t="n">
-        <v>6</v>
+        <v>2.91</v>
       </c>
       <c r="N32" t="n">
-        <v>12.25</v>
+        <v>2.19</v>
       </c>
       <c r="O32" t="n">
-        <v>1.6</v>
+        <v>4.05</v>
       </c>
       <c r="P32" t="n">
-        <v>2.61</v>
+        <v>1.98</v>
       </c>
       <c r="Q32" t="n">
-        <v>9.1</v>
+        <v>2.84</v>
       </c>
       <c r="R32" t="n">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="S32" t="n">
-        <v>3.34</v>
+        <v>2.53</v>
       </c>
       <c r="T32" t="n">
-        <v>2.19</v>
+        <v>3.04</v>
       </c>
       <c r="U32" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="V32" t="n">
-        <v>4.6</v>
+        <v>7.4</v>
       </c>
       <c r="W32" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="X32" t="n">
         <v>1.03</v>
       </c>
       <c r="Y32" t="n">
-        <v>19</v>
+        <v>7.3</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.1</v>
+        <v>1.33</v>
       </c>
       <c r="AA32" t="n">
-        <v>5</v>
+        <v>2.84</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.42</v>
+        <v>2.4</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.49</v>
+        <v>1.55</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.1</v>
+        <v>3.52</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.66</v>
+        <v>1.22</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AH32" t="n">
-        <v>3.28</v>
+        <v>6.85</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>['18', '79']</t>
+          <t>['33']</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>['55', '67']</t>
+          <t>['60']</t>
         </is>
       </c>
       <c r="AL32" s="3" t="n">
@@ -4749,20 +4749,20 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L33" t="n">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['14', '90+3']</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['32', '80']</t>
         </is>
       </c>
       <c r="AL33" s="3" t="n">
@@ -4881,20 +4881,20 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L34" t="n">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['55', '65']</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['11']</t>
         </is>
       </c>
       <c r="AL34" s="3" t="n">
@@ -5013,20 +5013,20 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L35" t="n">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['42', '59', '69']</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['5', '21']</t>
         </is>
       </c>
       <c r="AL35" s="3" t="n">
@@ -5426,19 +5426,19 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="M38" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="N38" t="n">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="O38" t="n">
-        <v>3.14</v>
+        <v>3.24</v>
       </c>
       <c r="P38" t="n">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="Q38" t="n">
         <v>3.8</v>
@@ -5447,19 +5447,19 @@
         <v>1.52</v>
       </c>
       <c r="S38" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="T38" t="n">
         <v>3.6</v>
       </c>
       <c r="U38" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="V38" t="n">
         <v>9.1</v>
       </c>
       <c r="W38" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X38" t="n">
         <v>1.08</v>
@@ -5480,16 +5480,16 @@
         <v>1.44</v>
       </c>
       <c r="AD38" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="AE38" t="n">
         <v>1.15</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AH38" t="n">
         <v>13</v>
@@ -5558,58 +5558,58 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="M39" t="n">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="N39" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="O39" t="n">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="P39" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="R39" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="S39" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="T39" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="U39" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="V39" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="W39" t="n">
         <v>1.02</v>
       </c>
       <c r="X39" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="Y39" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB39" t="n">
-        <v>3.23</v>
+        <v>3.47</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AD39" t="n">
         <v>6.25</v>
@@ -5618,16 +5618,16 @@
         <v>1.11</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AH39" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,76 +5954,76 @@
         </is>
       </c>
       <c r="L42" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M42" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="N42" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="O42" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S42" t="n">
         <v>3.75</v>
       </c>
-      <c r="M42" t="n">
-        <v>3</v>
-      </c>
-      <c r="N42" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O42" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="P42" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="R42" t="n">
+      <c r="T42" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V42" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AB42" t="n">
         <v>1.5</v>
       </c>
-      <c r="S42" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="T42" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V42" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1</v>
-      </c>
-      <c r="X42" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>2.53</v>
-      </c>
       <c r="AC42" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="AD42" t="n">
-        <v>4.75</v>
+        <v>2.22</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.17</v>
+        <v>1.6</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.09</v>
+        <v>1.44</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.68</v>
+        <v>2.64</v>
       </c>
       <c r="AH42" t="n">
-        <v>9.5</v>
+        <v>3.58</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,76 +6086,76 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.66</v>
+        <v>3.9</v>
       </c>
       <c r="M43" t="n">
-        <v>3.63</v>
+        <v>3.2</v>
       </c>
       <c r="N43" t="n">
-        <v>2.47</v>
+        <v>2.02</v>
       </c>
       <c r="O43" t="n">
-        <v>3.25</v>
+        <v>4.37</v>
       </c>
       <c r="P43" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.2</v>
+        <v>2.68</v>
       </c>
       <c r="R43" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>2.34</v>
       </c>
       <c r="T43" t="n">
-        <v>2.75</v>
+        <v>3.48</v>
       </c>
       <c r="U43" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="V43" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="W43" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X43" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="Y43" t="n">
-        <v>9.199999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.36</v>
+        <v>2.56</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.94</v>
+        <v>2.58</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.88</v>
+        <v>1.5</v>
       </c>
       <c r="AD43" t="n">
-        <v>3.08</v>
+        <v>5</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.67</v>
+        <v>2.22</v>
       </c>
       <c r="AG43" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AH43" t="n">
-        <v>5.85</v>
+        <v>9.5</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,76 +6218,76 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="M44" t="n">
-        <v>3.85</v>
+        <v>3.63</v>
       </c>
       <c r="N44" t="n">
-        <v>2.23</v>
+        <v>2.47</v>
       </c>
       <c r="O44" t="n">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="P44" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="R44" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="S44" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="T44" t="n">
-        <v>2.23</v>
+        <v>2.75</v>
       </c>
       <c r="U44" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="V44" t="n">
-        <v>3.8</v>
+        <v>7</v>
       </c>
       <c r="W44" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AA44" t="n">
-        <v>4.3</v>
+        <v>3.36</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.5</v>
+        <v>1.94</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.4</v>
+        <v>1.88</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.22</v>
+        <v>3.08</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AG44" t="n">
-        <v>2.64</v>
+        <v>2.1</v>
       </c>
       <c r="AH44" t="n">
-        <v>3.58</v>
+        <v>5.85</v>
       </c>
       <c r="AI44" t="n">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
@@ -6482,61 +6482,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="M46" t="n">
         <v>2.84</v>
       </c>
       <c r="N46" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="O46" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="P46" t="n">
         <v>1.75</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="R46" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="S46" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="T46" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="U46" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="V46" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W46" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X46" t="n">
         <v>1.11</v>
       </c>
       <c r="Y46" t="n">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="Z46" t="n">
         <v>1.74</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AB46" t="n">
         <v>3</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AD46" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AE46" t="n">
         <v>1.11</v>
@@ -6548,10 +6548,10 @@
         <v>1.45</v>
       </c>
       <c r="AH46" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AI46" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
@@ -6617,25 +6617,25 @@
         <v>2.25</v>
       </c>
       <c r="M47" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="N47" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="O47" t="n">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
       <c r="P47" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.33</v>
+        <v>4.55</v>
       </c>
       <c r="R47" t="n">
         <v>1.5</v>
       </c>
       <c r="S47" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="T47" t="n">
         <v>3.75</v>
@@ -6644,10 +6644,10 @@
         <v>1.22</v>
       </c>
       <c r="V47" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="W47" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X47" t="n">
         <v>1.1</v>
@@ -6656,16 +6656,16 @@
         <v>6</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB47" t="n">
         <v>2.7</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AD47" t="n">
         <v>6</v>
@@ -6674,10 +6674,10 @@
         <v>1.11</v>
       </c>
       <c r="AF47" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AH47" t="n">
         <v>11</v>

--- a/jogos_2025-08-11.xlsx
+++ b/jogos_2025-08-11.xlsx
@@ -683,13 +683,13 @@
         <v>3.5</v>
       </c>
       <c r="O2" t="n">
-        <v>2.8</v>
+        <v>1.57</v>
       </c>
       <c r="P2" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.65</v>
+        <v>2.25</v>
       </c>
       <c r="R2" t="n">
         <v>1.17</v>
@@ -815,13 +815,13 @@
         <v>5.1</v>
       </c>
       <c r="O3" t="n">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="P3" t="n">
-        <v>2.35</v>
+        <v>11.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.46</v>
+        <v>2.88</v>
       </c>
       <c r="R3" t="n">
         <v>1.35</v>
@@ -947,13 +947,13 @@
         <v>2.96</v>
       </c>
       <c r="O4" t="n">
-        <v>3.2</v>
+        <v>1.98</v>
       </c>
       <c r="P4" t="n">
-        <v>1.95</v>
+        <v>6.55</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.6</v>
+        <v>2.18</v>
       </c>
       <c r="R4" t="n">
         <v>1.53</v>
@@ -1079,13 +1079,13 @@
         <v>4.4</v>
       </c>
       <c r="O5" t="n">
-        <v>2.15</v>
+        <v>1.5</v>
       </c>
       <c r="P5" t="n">
-        <v>2.15</v>
+        <v>9.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.25</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
         <v>1.36</v>
@@ -1211,13 +1211,13 @@
         <v>2.38</v>
       </c>
       <c r="O6" t="n">
-        <v>3.12</v>
+        <v>1.95</v>
       </c>
       <c r="P6" t="n">
-        <v>1.94</v>
+        <v>9</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="R6" t="n">
         <v>1.42</v>
@@ -1298,26 +1298,26 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kudrivka</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
@@ -1334,85 +1334,85 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.69</v>
+        <v>3.35</v>
       </c>
       <c r="M7" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P7" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA7" t="n">
         <v>3.7</v>
       </c>
-      <c r="N7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V7" t="n">
-        <v>8</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
       <c r="AB7" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AC7" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1.65</v>
       </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.13</v>
-      </c>
       <c r="AG7" t="n">
-        <v>1.71</v>
+        <v>2.08</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>['22', '56']</t>
+          <t>['18']</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>['50']</t>
+          <t>['84']</t>
         </is>
       </c>
       <c r="AL7" s="3" t="n">
@@ -1430,26 +1430,26 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Kudrivka</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
@@ -1466,85 +1466,85 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.35</v>
+        <v>1.69</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="N8" t="n">
-        <v>1.92</v>
+        <v>4.8</v>
       </c>
       <c r="O8" t="n">
-        <v>3.9</v>
+        <v>1.62</v>
       </c>
       <c r="P8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="R8" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="S8" t="n">
-        <v>2.94</v>
+        <v>2.6</v>
       </c>
       <c r="T8" t="n">
-        <v>2.55</v>
+        <v>3.15</v>
       </c>
       <c r="U8" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.65</v>
+        <v>2.13</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.08</v>
+        <v>1.71</v>
       </c>
       <c r="AH8" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>['18']</t>
+          <t>['22', '56']</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>['84']</t>
+          <t>['50']</t>
         </is>
       </c>
       <c r="AL8" s="3" t="n">
@@ -1607,13 +1607,13 @@
         <v>8</v>
       </c>
       <c r="O9" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="P9" t="n">
-        <v>2.35</v>
+        <v>11.75</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.2</v>
+        <v>3.5</v>
       </c>
       <c r="R9" t="n">
         <v>1.33</v>
@@ -1694,121 +1694,121 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>2</v>
       </c>
       <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
         <v>2</v>
       </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.02</v>
+        <v>2.2</v>
       </c>
       <c r="M10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N10" t="n">
         <v>3.35</v>
       </c>
-      <c r="N10" t="n">
-        <v>2.05</v>
-      </c>
       <c r="O10" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="P10" t="n">
-        <v>2.38</v>
+        <v>7</v>
       </c>
       <c r="Q10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S10" t="n">
         <v>2.6</v>
       </c>
-      <c r="R10" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.14</v>
-      </c>
       <c r="T10" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="U10" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="W10" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.300000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.16</v>
+        <v>1.37</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.6</v>
+        <v>2.88</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.25</v>
+        <v>1.66</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.63</v>
+        <v>3.99</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.48</v>
+        <v>1.18</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.45</v>
+        <v>1.85</v>
       </c>
       <c r="AH10" t="n">
-        <v>4.7</v>
+        <v>7.8</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>['-1', '-1']</t>
+          <t>['45+5', '90']</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>['-1', '-1']</t>
+          <t>['23', '27', '50']</t>
         </is>
       </c>
       <c r="AL10" s="3" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,16 +1836,16 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
@@ -1862,85 +1862,85 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="N11" t="n">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="O11" t="n">
-        <v>2.85</v>
+        <v>1.91</v>
       </c>
       <c r="P11" t="n">
-        <v>2.4</v>
+        <v>7.4</v>
       </c>
       <c r="Q11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T11" t="n">
         <v>3</v>
       </c>
-      <c r="R11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2</v>
-      </c>
       <c r="U11" t="n">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="V11" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y11" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.11</v>
+        <v>1.35</v>
       </c>
       <c r="AA11" t="n">
-        <v>7.28</v>
+        <v>2.74</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.2</v>
+        <v>3.98</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.42</v>
+        <v>1.91</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.24</v>
+        <v>1.06</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>['70', '72', '86', '89', '90+3']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>['65']</t>
+          <t>['-1']</t>
         </is>
       </c>
       <c r="AL11" s="3" t="n">
@@ -1958,121 +1958,121 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
       </c>
       <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P12" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T12" t="n">
         <v>2</v>
       </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="M12" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="N12" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="O12" t="n">
+      <c r="U12" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V12" t="n">
+        <v>4</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC12" t="n">
         <v>3</v>
       </c>
-      <c r="P12" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>4</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="AD12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AG12" t="n">
         <v>2.5</v>
       </c>
-      <c r="T12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V12" t="n">
-        <v>11</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>['18', '45+2', '84']</t>
+          <t>['70', '72', '86', '89', '90+3']</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>['83']</t>
+          <t>['65']</t>
         </is>
       </c>
       <c r="AL12" s="3" t="n">
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2118,7 +2118,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.49</v>
+        <v>1.72</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>2.85</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>3</v>
+        <v>1.63</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.5</v>
+        <v>2.66</v>
       </c>
       <c r="R13" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="S13" t="n">
-        <v>2.62</v>
+        <v>2.31</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>3.66</v>
       </c>
       <c r="U13" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="V13" t="n">
-        <v>7.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>8</v>
+        <v>5.79</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.74</v>
+        <v>2.33</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.1</v>
+        <v>2.61</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.98</v>
+        <v>5.04</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.91</v>
+        <v>2.36</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AH13" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>['-1']</t>
+          <t>['41']</t>
         </is>
       </c>
       <c r="AL13" s="3" t="n">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,111 +2232,111 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
         <v>2</v>
       </c>
-      <c r="H14" t="n">
-        <v>3</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1</v>
-      </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="N14" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V14" t="n">
+        <v>11</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
         <v>2</v>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="M14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O14" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>4</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V14" t="n">
-        <v>8</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AG14" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AH14" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>['45+5', '90']</t>
+          <t>['18', '45+2', '84']</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>['23', '27', '50']</t>
+          <t>['83']</t>
         </is>
       </c>
       <c r="AL14" s="3" t="n">
@@ -2354,35 +2354,35 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2390,85 +2390,85 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.72</v>
+        <v>3.02</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>5</v>
+        <v>2.05</v>
       </c>
       <c r="O15" t="n">
-        <v>2.42</v>
+        <v>2.13</v>
       </c>
       <c r="P15" t="n">
-        <v>1.91</v>
+        <v>13.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.34</v>
+        <v>1.75</v>
       </c>
       <c r="R15" t="n">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="S15" t="n">
-        <v>2.31</v>
+        <v>3.14</v>
       </c>
       <c r="T15" t="n">
-        <v>3.66</v>
+        <v>2.3</v>
       </c>
       <c r="U15" t="n">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="V15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y15" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="W15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>5.79</v>
-      </c>
       <c r="Z15" t="n">
-        <v>1.56</v>
+        <v>1.16</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.33</v>
+        <v>4.6</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.61</v>
+        <v>1.55</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.68</v>
+        <v>2.25</v>
       </c>
       <c r="AD15" t="n">
-        <v>5.04</v>
+        <v>2.63</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.11</v>
+        <v>1.48</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.36</v>
+        <v>1.71</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="AH15" t="n">
-        <v>9.300000000000001</v>
+        <v>4.7</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['-1', '-1']</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>['41']</t>
+          <t>['-1', '-1']</t>
         </is>
       </c>
       <c r="AL15" s="3" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,111 +2496,111 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
         <v>1</v>
       </c>
-      <c r="H16" t="n">
-        <v>4</v>
-      </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2</v>
+      </c>
+      <c r="P16" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S16" t="n">
         <v>3</v>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L16" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="M16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R16" t="n">
+      <c r="T16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V16" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE16" t="n">
         <v>1.33</v>
       </c>
-      <c r="S16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V16" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AF16" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AH16" t="n">
-        <v>4.45</v>
+        <v>5.25</v>
       </c>
       <c r="AI16" t="n">
         <v>1.13</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>['74']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>['16', '27', '35', '72']</t>
+          <t>['61']</t>
         </is>
       </c>
       <c r="AL16" s="3" t="n">
@@ -2618,35 +2618,35 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
         <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2654,85 +2654,85 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.39</v>
+        <v>2.75</v>
       </c>
       <c r="M17" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="N17" t="n">
-        <v>5.7</v>
+        <v>2.44</v>
       </c>
       <c r="O17" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.63</v>
+        <v>10</v>
       </c>
       <c r="Q17" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S17" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="U17" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="V17" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z17" t="n">
         <v>1.17</v>
       </c>
       <c r="AA17" t="n">
-        <v>5.25</v>
+        <v>4.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>['45', '77']</t>
+          <t>['5', '43', '45+1']</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>['62', '72']</t>
+          <t>['7', '24']</t>
         </is>
       </c>
       <c r="AL17" s="3" t="n">
@@ -2795,13 +2795,13 @@
         <v>2.8</v>
       </c>
       <c r="O18" t="n">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="P18" t="n">
-        <v>2.19</v>
+        <v>10</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.35</v>
+        <v>2.3</v>
       </c>
       <c r="R18" t="n">
         <v>1.3</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,25 +2892,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
         <v>2</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2918,85 +2918,85 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.75</v>
+        <v>3.15</v>
       </c>
       <c r="M19" t="n">
-        <v>3.75</v>
+        <v>3.04</v>
       </c>
       <c r="N19" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="O19" t="n">
-        <v>3.2</v>
+        <v>2.53</v>
       </c>
       <c r="P19" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF19" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y19" t="n">
+      <c r="AG19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH19" t="n">
         <v>13</v>
       </c>
-      <c r="Z19" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AI19" t="n">
-        <v>1.16</v>
+        <v>1.02</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>['5', '43', '45+1']</t>
+          <t>['77']</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>['7', '24']</t>
+          <t>['9', '64']</t>
         </is>
       </c>
       <c r="AL19" s="3" t="n">
@@ -3059,13 +3059,13 @@
         <v>1.93</v>
       </c>
       <c r="O20" t="n">
-        <v>4.7</v>
+        <v>2.5</v>
       </c>
       <c r="P20" t="n">
-        <v>2.05</v>
+        <v>8.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.56</v>
+        <v>1.67</v>
       </c>
       <c r="R20" t="n">
         <v>1.44</v>
@@ -3191,13 +3191,13 @@
         <v>3.23</v>
       </c>
       <c r="O21" t="n">
-        <v>2.6</v>
+        <v>1.73</v>
       </c>
       <c r="P21" t="n">
-        <v>2.25</v>
+        <v>9</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="R21" t="n">
         <v>1.36</v>
@@ -3278,33 +3278,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="n">
         <v>1</v>
       </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
@@ -3314,85 +3314,85 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.6</v>
+        <v>1.39</v>
       </c>
       <c r="M22" t="n">
-        <v>3.64</v>
+        <v>4.5</v>
       </c>
       <c r="N22" t="n">
-        <v>2.46</v>
+        <v>5.7</v>
       </c>
       <c r="O22" t="n">
-        <v>3.25</v>
+        <v>1.4</v>
       </c>
       <c r="P22" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V22" t="n">
+        <v>5</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AD22" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q22" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V22" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="Z22" t="n">
+      <c r="AE22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AI22" t="n">
         <v>1.25</v>
       </c>
-      <c r="AA22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45', '77']</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>['61']</t>
+          <t>['62', '72']</t>
         </is>
       </c>
       <c r="AL22" s="3" t="n">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,111 +3420,111 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="n">
+        <v>4</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="P23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V23" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC23" t="n">
         <v>2</v>
       </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="M23" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O23" t="n">
-        <v>4</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>6.11</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AD23" t="n">
-        <v>5.45</v>
+        <v>2.57</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.08</v>
+        <v>1.41</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AH23" t="n">
-        <v>13</v>
+        <v>4.45</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>['77']</t>
+          <t>['74']</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>['9', '64']</t>
+          <t>['16', '27', '35', '72']</t>
         </is>
       </c>
       <c r="AL23" s="3" t="n">
@@ -3587,13 +3587,13 @@
         <v>4.2</v>
       </c>
       <c r="O24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P24" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="Q24" t="n">
         <v>2.5</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>4.5</v>
       </c>
       <c r="R24" t="n">
         <v>1.4</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,111 +3684,111 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>2</v>
+      </c>
+      <c r="M25" t="n">
         <v>3</v>
       </c>
-      <c r="I25" t="n">
-        <v>2</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
+      <c r="N25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="P25" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="R25" t="n">
         <v>1.4</v>
       </c>
-      <c r="M25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N25" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>6</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.28</v>
-      </c>
       <c r="S25" t="n">
-        <v>3.22</v>
+        <v>2.6</v>
       </c>
       <c r="T25" t="n">
-        <v>2.25</v>
+        <v>3.15</v>
       </c>
       <c r="U25" t="n">
-        <v>1.55</v>
+        <v>1.32</v>
       </c>
       <c r="V25" t="n">
-        <v>5.8</v>
+        <v>8.1</v>
       </c>
       <c r="W25" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="X25" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y25" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.62</v>
+        <v>2.16</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.15</v>
+        <v>1.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.46</v>
+        <v>3.7</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.43</v>
+        <v>1.18</v>
       </c>
       <c r="AF25" t="n">
         <v>1.83</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="AH25" t="n">
-        <v>4.33</v>
+        <v>8.5</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>['15', '20', '62', '79']</t>
+          <t>['15']</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>['33', '45', '73']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AL25" s="3" t="n">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,16 +3816,16 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H26" t="n">
         <v>3</v>
@@ -3842,85 +3842,85 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.15</v>
+        <v>1.4</v>
       </c>
       <c r="M26" t="n">
-        <v>4.01</v>
+        <v>4.2</v>
       </c>
       <c r="N26" t="n">
-        <v>2</v>
+        <v>5.75</v>
       </c>
       <c r="O26" t="n">
-        <v>3.5</v>
+        <v>1.44</v>
       </c>
       <c r="P26" t="n">
-        <v>2.3</v>
+        <v>11</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.57</v>
+        <v>3</v>
       </c>
       <c r="R26" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="S26" t="n">
-        <v>3.85</v>
+        <v>3.22</v>
       </c>
       <c r="T26" t="n">
         <v>2.25</v>
       </c>
       <c r="U26" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V26" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AB26" t="n">
         <v>1.62</v>
       </c>
-      <c r="V26" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>5.73</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AC26" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.46</v>
+        <v>1.83</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="AH26" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>['19', '26']</t>
+          <t>['15', '20', '62', '79']</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>['14', '28', '72']</t>
+          <t>['33', '45', '73']</t>
         </is>
       </c>
       <c r="AL26" s="3" t="n">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,25 +3948,25 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3974,85 +3974,85 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="M27" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="N27" t="n">
         <v>2</v>
       </c>
-      <c r="M27" t="n">
-        <v>3</v>
-      </c>
-      <c r="N27" t="n">
-        <v>3.3</v>
-      </c>
       <c r="O27" t="n">
-        <v>2.69</v>
+        <v>2.1</v>
       </c>
       <c r="P27" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>1.73</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="S27" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V27" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AG27" t="n">
         <v>2.6</v>
       </c>
-      <c r="T27" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V27" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AE27" t="n">
+      <c r="AH27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AI27" t="n">
         <v>1.18</v>
       </c>
-      <c r="AF27" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>['15']</t>
+          <t>['19', '26']</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['14', '28', '72']</t>
         </is>
       </c>
       <c r="AL27" s="3" t="n">
@@ -4115,13 +4115,13 @@
         <v>2.34</v>
       </c>
       <c r="O28" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="P28" t="n">
-        <v>2.5</v>
+        <v>15</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.4</v>
+        <v>1.73</v>
       </c>
       <c r="R28" t="n">
         <v>1.25</v>
@@ -4247,13 +4247,13 @@
         <v>3.7</v>
       </c>
       <c r="O29" t="n">
-        <v>2.95</v>
+        <v>1.73</v>
       </c>
       <c r="P29" t="n">
-        <v>1.93</v>
+        <v>7.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.27</v>
+        <v>2.63</v>
       </c>
       <c r="R29" t="n">
         <v>1.5</v>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,22 +4344,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G30" t="n">
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -4370,85 +4370,85 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.53</v>
+        <v>3.12</v>
       </c>
       <c r="M30" t="n">
-        <v>3.9</v>
+        <v>2.91</v>
       </c>
       <c r="N30" t="n">
-        <v>4.75</v>
+        <v>2.19</v>
       </c>
       <c r="O30" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="P30" t="n">
-        <v>2.38</v>
+        <v>7.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.5</v>
+        <v>1.83</v>
       </c>
       <c r="R30" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U30" t="n">
         <v>1.33</v>
       </c>
-      <c r="S30" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.44</v>
-      </c>
       <c r="V30" t="n">
-        <v>6.5</v>
+        <v>7.4</v>
       </c>
       <c r="W30" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X30" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y30" t="n">
-        <v>9.5</v>
+        <v>7.3</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.8</v>
+        <v>2.84</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.05</v>
+        <v>1.55</v>
       </c>
       <c r="AD30" t="n">
-        <v>3</v>
+        <v>3.52</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH30" t="n">
-        <v>5.5</v>
+        <v>6.85</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>['49']</t>
+          <t>['33']</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['60']</t>
         </is>
       </c>
       <c r="AL30" s="3" t="n">
@@ -4511,13 +4511,13 @@
         <v>12.25</v>
       </c>
       <c r="O31" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="P31" t="n">
-        <v>2.61</v>
+        <v>15.25</v>
       </c>
       <c r="Q31" t="n">
-        <v>9.1</v>
+        <v>4.65</v>
       </c>
       <c r="R31" t="n">
         <v>1.26</v>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,22 +4608,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G32" t="n">
         <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -4634,85 +4634,85 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.12</v>
+        <v>1.53</v>
       </c>
       <c r="M32" t="n">
-        <v>2.91</v>
+        <v>3.9</v>
       </c>
       <c r="N32" t="n">
-        <v>2.19</v>
+        <v>4.75</v>
       </c>
       <c r="O32" t="n">
-        <v>4.05</v>
+        <v>1.5</v>
       </c>
       <c r="P32" t="n">
-        <v>1.98</v>
+        <v>10.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="R32" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="S32" t="n">
-        <v>2.53</v>
+        <v>3.25</v>
       </c>
       <c r="T32" t="n">
-        <v>3.04</v>
+        <v>2.63</v>
       </c>
       <c r="U32" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="V32" t="n">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="W32" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X32" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y32" t="n">
-        <v>7.3</v>
+        <v>9.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.84</v>
+        <v>3.8</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.4</v>
+        <v>1.75</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.55</v>
+        <v>2.05</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.52</v>
+        <v>3</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH32" t="n">
-        <v>6.85</v>
+        <v>5.5</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>['33']</t>
+          <t>['49']</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>['60']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AL32" s="3" t="n">
@@ -4775,13 +4775,13 @@
         <v>1.76</v>
       </c>
       <c r="O33" t="n">
-        <v>5</v>
+        <v>2.75</v>
       </c>
       <c r="P33" t="n">
-        <v>2.1</v>
+        <v>8</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.38</v>
+        <v>1.57</v>
       </c>
       <c r="R33" t="n">
         <v>1.44</v>
@@ -4907,13 +4907,13 @@
         <v>3.75</v>
       </c>
       <c r="O34" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="P34" t="n">
-        <v>2.44</v>
+        <v>24</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.95</v>
+        <v>2.2</v>
       </c>
       <c r="R34" t="n">
         <v>1.2</v>
@@ -5039,13 +5039,13 @@
         <v>5.1</v>
       </c>
       <c r="O35" t="n">
-        <v>2.02</v>
+        <v>1.41</v>
       </c>
       <c r="P35" t="n">
-        <v>2.5</v>
+        <v>20.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>5</v>
+        <v>2.89</v>
       </c>
       <c r="R35" t="n">
         <v>1.2</v>
@@ -5145,20 +5145,20 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L36" t="n">
@@ -5171,13 +5171,13 @@
         <v>5.5</v>
       </c>
       <c r="O36" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="P36" t="n">
-        <v>2.3</v>
+        <v>10</v>
       </c>
       <c r="Q36" t="n">
-        <v>5.5</v>
+        <v>2.75</v>
       </c>
       <c r="R36" t="n">
         <v>1.33</v>
@@ -5235,7 +5235,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['12', '32', '79']</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -5303,13 +5303,13 @@
         <v>4.2</v>
       </c>
       <c r="O37" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P37" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q37" t="n">
         <v>2.6</v>
-      </c>
-      <c r="P37" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>4.75</v>
       </c>
       <c r="R37" t="n">
         <v>1.44</v>
@@ -5435,13 +5435,13 @@
         <v>2.98</v>
       </c>
       <c r="O38" t="n">
-        <v>3.24</v>
+        <v>1.91</v>
       </c>
       <c r="P38" t="n">
-        <v>2.05</v>
+        <v>6.25</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="R38" t="n">
         <v>1.52</v>
@@ -5567,13 +5567,13 @@
         <v>3</v>
       </c>
       <c r="O39" t="n">
-        <v>3.36</v>
+        <v>2.05</v>
       </c>
       <c r="P39" t="n">
-        <v>1.71</v>
+        <v>5.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="R39" t="n">
         <v>1.73</v>
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="L40" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="M40" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="O40" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P40" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Q40" t="n">
         <v>2.2</v>
       </c>
-      <c r="M40" t="n">
-        <v>3</v>
-      </c>
-      <c r="N40" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="O40" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P40" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>3.7</v>
-      </c>
       <c r="R40" t="n">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="S40" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="T40" t="n">
-        <v>3.17</v>
+        <v>3.8</v>
       </c>
       <c r="U40" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="V40" t="n">
-        <v>8.25</v>
+        <v>10</v>
       </c>
       <c r="W40" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X40" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Y40" t="n">
-        <v>7.1</v>
+        <v>6.4</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.93</v>
+        <v>2.35</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.15</v>
+        <v>2.65</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.62</v>
+        <v>1.42</v>
       </c>
       <c r="AD40" t="n">
-        <v>3.95</v>
+        <v>4.75</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.97</v>
+        <v>2.16</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="AH40" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,76 +5822,76 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.5</v>
+        <v>2.16</v>
       </c>
       <c r="M41" t="n">
-        <v>2.75</v>
+        <v>3.03</v>
       </c>
       <c r="N41" t="n">
-        <v>2.7</v>
+        <v>3.27</v>
       </c>
       <c r="O41" t="n">
-        <v>3.54</v>
+        <v>1.73</v>
       </c>
       <c r="P41" t="n">
-        <v>1.82</v>
+        <v>7.5</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.38</v>
+        <v>2.4</v>
       </c>
       <c r="R41" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="S41" t="n">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="T41" t="n">
-        <v>3.78</v>
+        <v>3.1</v>
       </c>
       <c r="U41" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="V41" t="n">
-        <v>10</v>
+        <v>8.25</v>
       </c>
       <c r="W41" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AI41" t="n">
         <v>1.03</v>
-      </c>
-      <c r="X41" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>1.02</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
@@ -5957,19 +5957,19 @@
         <v>2.8</v>
       </c>
       <c r="M42" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="N42" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="O42" t="n">
-        <v>4.1</v>
+        <v>2.25</v>
       </c>
       <c r="P42" t="n">
-        <v>2.3</v>
+        <v>13.5</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.65</v>
+        <v>1.57</v>
       </c>
       <c r="R42" t="n">
         <v>1.25</v>
@@ -5978,10 +5978,10 @@
         <v>3.75</v>
       </c>
       <c r="T42" t="n">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="U42" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="V42" t="n">
         <v>3.8</v>
@@ -5996,34 +5996,34 @@
         <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AA42" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="AH42" t="n">
         <v>3.58</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
@@ -6086,22 +6086,22 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.9</v>
+        <v>3.29</v>
       </c>
       <c r="M43" t="n">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="N43" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="O43" t="n">
-        <v>4.37</v>
+        <v>2.4</v>
       </c>
       <c r="P43" t="n">
-        <v>2.05</v>
+        <v>6.5</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.68</v>
+        <v>1.8</v>
       </c>
       <c r="R43" t="n">
         <v>1.5</v>
@@ -6128,16 +6128,16 @@
         <v>6.5</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.58</v>
+        <v>2.35</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AD43" t="n">
         <v>5</v>
@@ -6227,13 +6227,13 @@
         <v>2.47</v>
       </c>
       <c r="O44" t="n">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="P44" t="n">
-        <v>2.2</v>
+        <v>12</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.2</v>
+        <v>1.95</v>
       </c>
       <c r="R44" t="n">
         <v>1.36</v>
@@ -6353,37 +6353,37 @@
         <v>1.73</v>
       </c>
       <c r="M45" t="n">
-        <v>3.99</v>
+        <v>3.75</v>
       </c>
       <c r="N45" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="O45" t="n">
-        <v>2.55</v>
+        <v>1.53</v>
       </c>
       <c r="P45" t="n">
-        <v>2.15</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="R45" t="n">
         <v>1.33</v>
       </c>
       <c r="S45" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="T45" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="U45" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="V45" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="W45" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
@@ -6392,25 +6392,25 @@
         <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AA45" t="n">
-        <v>3.9</v>
+        <v>3.98</v>
       </c>
       <c r="AB45" t="n">
         <v>1.77</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD45" t="n">
         <v>2.95</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AG45" t="n">
         <v>2</v>
@@ -6419,7 +6419,7 @@
         <v>5.4</v>
       </c>
       <c r="AI45" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
@@ -6482,22 +6482,22 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="M46" t="n">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="N46" t="n">
-        <v>3.45</v>
+        <v>3.84</v>
       </c>
       <c r="O46" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="P46" t="n">
-        <v>1.75</v>
+        <v>5.25</v>
       </c>
       <c r="Q46" t="n">
-        <v>5.2</v>
+        <v>2.5</v>
       </c>
       <c r="R46" t="n">
         <v>1.65</v>
@@ -6524,16 +6524,16 @@
         <v>4.9</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="AB46" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AD46" t="n">
         <v>5.8</v>
@@ -6614,22 +6614,22 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="M47" t="n">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="N47" t="n">
-        <v>3.65</v>
+        <v>3.16</v>
       </c>
       <c r="O47" t="n">
-        <v>2.77</v>
+        <v>1.91</v>
       </c>
       <c r="P47" t="n">
-        <v>1.82</v>
+        <v>6.25</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.55</v>
+        <v>2.3</v>
       </c>
       <c r="R47" t="n">
         <v>1.5</v>
@@ -6656,16 +6656,16 @@
         <v>6</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AB47" t="n">
-        <v>2.7</v>
+        <v>2.37</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AD47" t="n">
         <v>6</v>

--- a/jogos_2025-08-11.xlsx
+++ b/jogos_2025-08-11.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL47"/>
+  <dimension ref="A1:AK48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,85 +543,80 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over25</t>
+          <t>FT_Odd_Over05</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under25</t>
+          <t>Odd_Over15</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>FT_Odd_Over05</t>
+          <t>Odd_Under15</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>FT_Odd_Under05</t>
+          <t>Odd_Over25</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over15</t>
+          <t>Odd_Under25</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under15</t>
+          <t>Odd_Over35</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over25</t>
+          <t>Odd_Under35</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under25</t>
+          <t>Odd_BTTS_Yes</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over35</t>
+          <t>Odd_BTTS_No</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under35</t>
+          <t>homeGoals</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Odd_BTTS_Yes</t>
+          <t>awayGoals</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Odd_BTTS_No</t>
+          <t>Odd_H_D</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over45</t>
+          <t>Odd_A_D</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under45</t>
+          <t>Odd_marcar_prim_H</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>homeGoals</t>
+          <t>Odd_marcar_prim_A</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>awayGoals</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -683,13 +678,13 @@
         <v>3.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.57</v>
+        <v>2.8</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.25</v>
+        <v>2.65</v>
       </c>
       <c r="R2" t="n">
         <v>1.17</v>
@@ -704,58 +699,55 @@
         <v>1.83</v>
       </c>
       <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X2" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z2" t="n">
         <v>3.3</v>
       </c>
-      <c r="W2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AA2" t="n">
-        <v>6.5</v>
+        <v>1.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.3</v>
+        <v>1.27</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.27</v>
+        <v>3.2</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>['23', '36', '64', '89']</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>['9', '16']</t>
+        </is>
       </c>
       <c r="AG2" t="n">
-        <v>3.2</v>
+        <v>1.52</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.35</v>
+        <v>1.45</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>['23', '36', '64', '89']</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>['9', '16']</t>
-        </is>
-      </c>
-      <c r="AL2" s="3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK2" s="3" t="n">
         <v>45880</v>
       </c>
     </row>
@@ -815,13 +807,13 @@
         <v>5.1</v>
       </c>
       <c r="O3" t="n">
-        <v>1.44</v>
+        <v>2.05</v>
       </c>
       <c r="P3" t="n">
-        <v>11.25</v>
+        <v>2.35</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.88</v>
+        <v>4.46</v>
       </c>
       <c r="R3" t="n">
         <v>1.35</v>
@@ -836,58 +828,55 @@
         <v>1.5</v>
       </c>
       <c r="V3" t="n">
-        <v>6.2</v>
+        <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>3.85</v>
       </c>
       <c r="Y3" t="n">
-        <v>12</v>
+        <v>1.7</v>
       </c>
       <c r="Z3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>['15', '62', '68', '80']</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>['90+6']</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
         <v>1.25</v>
       </c>
-      <c r="AA3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD3" t="n">
+      <c r="AH3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>2.88</v>
       </c>
-      <c r="AE3" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>['15', '62', '68', '80']</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>['90+6']</t>
-        </is>
-      </c>
-      <c r="AL3" s="3" t="n">
+      <c r="AK3" s="3" t="n">
         <v>45880.22916666666</v>
       </c>
     </row>
@@ -902,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,22 +901,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Renofa Yamaguchi</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -938,88 +927,85 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.35</v>
+        <v>1.59</v>
       </c>
       <c r="M4" t="n">
-        <v>2.8</v>
+        <v>3.82</v>
       </c>
       <c r="N4" t="n">
-        <v>2.96</v>
+        <v>4.4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="P4" t="n">
-        <v>6.55</v>
+        <v>2.15</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.18</v>
+        <v>5.25</v>
       </c>
       <c r="R4" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="T4" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X4" t="n">
         <v>3.6</v>
       </c>
-      <c r="U4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V4" t="n">
-        <v>11</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y4" t="n">
-        <v>6.55</v>
+        <v>1.76</v>
       </c>
       <c r="Z4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>['13', '54', '81']</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>['2']</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI4" t="n">
         <v>1.5</v>
       </c>
-      <c r="AA4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>['40']</t>
-        </is>
-      </c>
-      <c r="AL4" s="3" t="n">
+      <c r="AJ4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK4" s="3" t="n">
         <v>45880.29166666666</v>
       </c>
     </row>
@@ -1034,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,22 +1030,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Renofa Yamaguchi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -1070,88 +1056,85 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.59</v>
+        <v>2.35</v>
       </c>
       <c r="M5" t="n">
-        <v>3.82</v>
+        <v>2.8</v>
       </c>
       <c r="N5" t="n">
-        <v>4.4</v>
+        <v>2.96</v>
       </c>
       <c r="O5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W5" t="n">
         <v>1.5</v>
       </c>
-      <c r="P5" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3</v>
-      </c>
-      <c r="R5" t="n">
+      <c r="X5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>['40']</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
         <v>1.36</v>
       </c>
-      <c r="S5" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AH5" t="n">
-        <v>5.75</v>
+        <v>1.53</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>['13', '54', '81']</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>['2']</t>
-        </is>
-      </c>
-      <c r="AL5" s="3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AK5" s="3" t="n">
         <v>45880.29166666666</v>
       </c>
     </row>
@@ -1211,13 +1194,13 @@
         <v>2.38</v>
       </c>
       <c r="O6" t="n">
-        <v>1.95</v>
+        <v>3.12</v>
       </c>
       <c r="P6" t="n">
-        <v>9</v>
+        <v>1.94</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="R6" t="n">
         <v>1.42</v>
@@ -1232,58 +1215,55 @@
         <v>1.27</v>
       </c>
       <c r="V6" t="n">
-        <v>8.4</v>
+        <v>1.06</v>
       </c>
       <c r="W6" t="n">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="X6" t="n">
-        <v>1.06</v>
+        <v>2.7</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.5</v>
+        <v>2.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.7</v>
+        <v>3.98</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.15</v>
+        <v>1.17</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.57</v>
+        <v>1.87</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>['28']</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.82</v>
+        <v>1.37</v>
       </c>
       <c r="AH6" t="n">
-        <v>8.1</v>
+        <v>1.3</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>['28']</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL6" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK6" s="3" t="n">
         <v>45880.45833333334</v>
       </c>
     </row>
@@ -1298,26 +1278,26 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Kudrivka</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
@@ -1334,88 +1314,85 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.35</v>
+        <v>1.69</v>
       </c>
       <c r="M7" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="N7" t="n">
-        <v>1.92</v>
+        <v>4.8</v>
       </c>
       <c r="O7" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="P7" t="n">
-        <v>9</v>
+        <v>2.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.67</v>
+        <v>5.47</v>
       </c>
       <c r="R7" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="S7" t="n">
-        <v>2.94</v>
+        <v>2.6</v>
       </c>
       <c r="T7" t="n">
-        <v>2.55</v>
+        <v>3.15</v>
       </c>
       <c r="U7" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="V7" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>11</v>
+        <v>2.05</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.22</v>
+        <v>1.65</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.83</v>
+        <v>2.13</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>['22', '56']</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>['50']</t>
+        </is>
       </c>
       <c r="AG7" t="n">
-        <v>2.08</v>
+        <v>1.18</v>
       </c>
       <c r="AH7" t="n">
-        <v>5.1</v>
+        <v>2.14</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>['18']</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>['84']</t>
-        </is>
-      </c>
-      <c r="AL7" s="3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AK7" s="3" t="n">
         <v>45880.5</v>
       </c>
     </row>
@@ -1430,26 +1407,26 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kudrivka</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
@@ -1466,88 +1443,85 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.69</v>
+        <v>3.35</v>
       </c>
       <c r="M8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X8" t="n">
         <v>3.7</v>
       </c>
-      <c r="N8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V8" t="n">
-        <v>8</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.05</v>
+        <v>1.37</v>
       </c>
       <c r="AC8" t="n">
         <v>1.65</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>['18']</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>['84']</t>
+        </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.71</v>
+        <v>1.2</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>['22', '56']</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>['50']</t>
-        </is>
-      </c>
-      <c r="AL8" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK8" s="3" t="n">
         <v>45880.5</v>
       </c>
     </row>
@@ -1607,13 +1581,13 @@
         <v>8</v>
       </c>
       <c r="O9" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="P9" t="n">
-        <v>11.75</v>
+        <v>2.35</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.5</v>
+        <v>6.2</v>
       </c>
       <c r="R9" t="n">
         <v>1.33</v>
@@ -1628,58 +1602,55 @@
         <v>1.4</v>
       </c>
       <c r="V9" t="n">
-        <v>7.7</v>
+        <v>1.05</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>3.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.5</v>
+        <v>1.85</v>
       </c>
       <c r="Z9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.25</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AC9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>['47', '53', '57', '87', '90']</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>3.5</v>
       </c>
-      <c r="AB9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>['47', '53', '57', '87', '90']</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL9" s="3" t="n">
+      <c r="AK9" s="3" t="n">
         <v>45880.52083333334</v>
       </c>
     </row>
@@ -1739,13 +1710,13 @@
         <v>3.35</v>
       </c>
       <c r="O10" t="n">
-        <v>2.1</v>
+        <v>3.07</v>
       </c>
       <c r="P10" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.91</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
         <v>1.4</v>
@@ -1760,58 +1731,55 @@
         <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="W10" t="n">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>2.88</v>
       </c>
       <c r="Y10" t="n">
-        <v>7.5</v>
+        <v>2.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.37</v>
+        <v>1.66</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.88</v>
+        <v>3.99</v>
       </c>
       <c r="AB10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>['45+5', '90']</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>['23', '27', '50']</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI10" t="n">
         <v>2.1</v>
       </c>
-      <c r="AC10" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>['45+5', '90']</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>['23', '27', '50']</t>
-        </is>
-      </c>
-      <c r="AL10" s="3" t="n">
+      <c r="AJ10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK10" s="3" t="n">
         <v>45880.54166666666</v>
       </c>
     </row>
@@ -1826,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,16 +1804,16 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
@@ -1862,88 +1830,85 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.49</v>
+        <v>2.44</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="N11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O11" t="n">
         <v>2.85</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X11" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>['70', '72', '86', '89', '90+3']</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>['65']</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>1.91</v>
       </c>
-      <c r="P11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V11" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>9</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>['-1']</t>
-        </is>
-      </c>
-      <c r="AL11" s="3" t="n">
+      <c r="AK11" s="3" t="n">
         <v>45880.54166666666</v>
       </c>
     </row>
@@ -1958,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,16 +1933,16 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
@@ -1994,88 +1959,85 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
       <c r="M12" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="N12" t="n">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="O12" t="n">
-        <v>1.83</v>
+        <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>17.75</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC12" t="n">
         <v>1.91</v>
       </c>
-      <c r="R12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V12" t="n">
-        <v>4</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>7.28</v>
-      </c>
-      <c r="AB12" t="n">
+      <c r="AD12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>['-1']</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
         <v>1.4</v>
       </c>
-      <c r="AC12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AH12" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>['70', '72', '86', '89', '90+3']</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>['65']</t>
-        </is>
-      </c>
-      <c r="AL12" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK12" s="3" t="n">
         <v>45880.54166666666</v>
       </c>
     </row>
@@ -2135,13 +2097,13 @@
         <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.63</v>
+        <v>2.42</v>
       </c>
       <c r="P13" t="n">
-        <v>8.699999999999999</v>
+        <v>1.91</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.66</v>
+        <v>6.34</v>
       </c>
       <c r="R13" t="n">
         <v>1.57</v>
@@ -2156,58 +2118,55 @@
         <v>1.22</v>
       </c>
       <c r="V13" t="n">
-        <v>9.300000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>1.56</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>2.33</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.79</v>
+        <v>2.61</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.33</v>
+        <v>5.04</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.61</v>
+        <v>1.11</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.68</v>
+        <v>2.36</v>
       </c>
       <c r="AD13" t="n">
-        <v>5.04</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.36</v>
+        <v>1.53</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>['41']</t>
+        </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.53</v>
+        <v>1.16</v>
       </c>
       <c r="AH13" t="n">
-        <v>9.300000000000001</v>
+        <v>2.07</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>['41']</t>
-        </is>
-      </c>
-      <c r="AL13" s="3" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AK13" s="3" t="n">
         <v>45880.54166666666</v>
       </c>
     </row>
@@ -2222,32 +2181,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2258,88 +2217,85 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>['-1', '-1']</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>['-1', '-1']</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>1.75</v>
       </c>
-      <c r="M14" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="N14" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V14" t="n">
-        <v>11</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>['18', '45+2', '84']</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>['83']</t>
-        </is>
-      </c>
-      <c r="AL14" s="3" t="n">
+      <c r="AK14" s="3" t="n">
         <v>45880.54166666666</v>
       </c>
     </row>
@@ -2354,33 +2310,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
         <v>2</v>
       </c>
-      <c r="H15" t="n">
-        <v>2</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
@@ -2390,88 +2346,85 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.02</v>
+        <v>2.78</v>
       </c>
       <c r="M15" t="n">
-        <v>3.35</v>
+        <v>2.77</v>
       </c>
       <c r="N15" t="n">
-        <v>2.05</v>
+        <v>2.68</v>
       </c>
       <c r="O15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC15" t="n">
         <v>2.13</v>
       </c>
-      <c r="P15" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AD15" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>['18', '45+2', '84']</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>['83']</t>
+        </is>
       </c>
       <c r="AG15" t="n">
-        <v>2.45</v>
+        <v>1.4</v>
       </c>
       <c r="AH15" t="n">
-        <v>4.7</v>
+        <v>1.36</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>['-1', '-1']</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>['-1', '-1']</t>
-        </is>
-      </c>
-      <c r="AL15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="3" t="n">
         <v>45880.54166666666</v>
       </c>
     </row>
@@ -2486,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,25 +2449,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2522,88 +2475,85 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.6</v>
+        <v>2.01</v>
       </c>
       <c r="M16" t="n">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>2.46</v>
+        <v>2.91</v>
       </c>
       <c r="O16" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z16" t="n">
         <v>2</v>
       </c>
-      <c r="P16" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AA16" t="n">
-        <v>3.5</v>
+        <v>2.57</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.8</v>
+        <v>1.41</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>['74']</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>['16', '27', '35', '72']</t>
+        </is>
       </c>
       <c r="AG16" t="n">
-        <v>2.17</v>
+        <v>1.4</v>
       </c>
       <c r="AH16" t="n">
-        <v>5.25</v>
+        <v>1.6</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>['61']</t>
-        </is>
-      </c>
-      <c r="AL16" s="3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK16" s="3" t="n">
         <v>45880.58333333334</v>
       </c>
     </row>
@@ -2618,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,22 +2578,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>3</v>
       </c>
       <c r="H17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" t="n">
         <v>2</v>
-      </c>
-      <c r="I17" t="n">
-        <v>3</v>
       </c>
       <c r="J17" t="n">
         <v>2</v>
@@ -2654,88 +2604,85 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O17" t="n">
         <v>2.75</v>
       </c>
-      <c r="M17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2</v>
-      </c>
       <c r="P17" t="n">
-        <v>10</v>
+        <v>2.19</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.8</v>
+        <v>3.35</v>
       </c>
       <c r="R17" t="n">
         <v>1.3</v>
       </c>
       <c r="S17" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="T17" t="n">
         <v>2.4</v>
       </c>
       <c r="U17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC17" t="n">
         <v>1.55</v>
       </c>
-      <c r="V17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AD17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.57</v>
+        <v>2.4</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>['3', '45+1', '79']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>['38', '41', '53']</t>
+        </is>
       </c>
       <c r="AG17" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="AH17" t="n">
-        <v>4.5</v>
+        <v>1.55</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>['5', '43', '45+1']</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>['7', '24']</t>
-        </is>
-      </c>
-      <c r="AL17" s="3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK17" s="3" t="n">
         <v>45880.58333333334</v>
       </c>
     </row>
@@ -2750,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,25 +2707,25 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
         <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2786,88 +2733,85 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.29</v>
+        <v>3.6</v>
       </c>
       <c r="M18" t="n">
         <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>2.8</v>
+        <v>1.93</v>
       </c>
       <c r="O18" t="n">
-        <v>1.75</v>
+        <v>4.7</v>
       </c>
       <c r="P18" t="n">
-        <v>10</v>
+        <v>2.05</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="T18" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="U18" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
-        <v>5.3</v>
+        <v>1.05</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>2.88</v>
       </c>
       <c r="Y18" t="n">
-        <v>9.199999999999999</v>
+        <v>2.1</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.2</v>
+        <v>1.66</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.62</v>
+        <v>1.18</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>['17', '27']</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>['48', '58']</t>
+        </is>
       </c>
       <c r="AG18" t="n">
-        <v>2.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.33</v>
+        <v>1.25</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>['3', '45+1', '79']</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>['38', '41', '53']</t>
-        </is>
-      </c>
-      <c r="AL18" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK18" s="3" t="n">
         <v>45880.58333333334</v>
       </c>
     </row>
@@ -2882,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,114 +2836,111 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O19" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q19" t="n">
         <v>2</v>
       </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L19" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="M19" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="P19" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC19" t="n">
         <v>1.8</v>
       </c>
-      <c r="R19" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>6.11</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AD19" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.2</v>
+        <v>2</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>['19']</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>['90']</t>
+        </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.62</v>
+        <v>2.11</v>
       </c>
       <c r="AH19" t="n">
-        <v>13</v>
+        <v>1.13</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>['77']</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>['9', '64']</t>
-        </is>
-      </c>
-      <c r="AL19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" s="3" t="n">
         <v>45880.58333333334</v>
       </c>
     </row>
@@ -3014,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3039,7 +2980,7 @@
         <v>2</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -3050,88 +2991,85 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.6</v>
+        <v>1.39</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="N20" t="n">
-        <v>1.93</v>
+        <v>5.7</v>
       </c>
       <c r="O20" t="n">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="P20" t="n">
-        <v>8.5</v>
+        <v>2.63</v>
       </c>
       <c r="Q20" t="n">
+        <v>6</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X20" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC20" t="n">
         <v>1.67</v>
       </c>
-      <c r="R20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V20" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AA20" t="n">
+      <c r="AD20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>['45', '77']</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>['62', '72']</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AJ20" t="n">
         <v>2.88</v>
       </c>
-      <c r="AB20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>['17', '27']</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>['48', '58']</t>
-        </is>
-      </c>
-      <c r="AL20" s="3" t="n">
+      <c r="AK20" s="3" t="n">
         <v>45880.58333333334</v>
       </c>
     </row>
@@ -3191,13 +3129,13 @@
         <v>3.23</v>
       </c>
       <c r="O21" t="n">
-        <v>1.73</v>
+        <v>2.6</v>
       </c>
       <c r="P21" t="n">
-        <v>9</v>
+        <v>2.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
         <v>1.36</v>
@@ -3212,58 +3150,55 @@
         <v>1.44</v>
       </c>
       <c r="V21" t="n">
-        <v>7</v>
+        <v>1.06</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="X21" t="n">
-        <v>1.06</v>
+        <v>3.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>9</v>
+        <v>1.8</v>
       </c>
       <c r="Z21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>['12']</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
         <v>1.3</v>
       </c>
-      <c r="AA21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AF21" t="n">
+      <c r="AH21" t="n">
         <v>1.7</v>
       </c>
-      <c r="AG21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>6.25</v>
-      </c>
       <c r="AI21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>['12']</t>
-        </is>
-      </c>
-      <c r="AL21" s="3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK21" s="3" t="n">
         <v>45880.58333333334</v>
       </c>
     </row>
@@ -3278,35 +3213,35 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
         <v>2</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3314,88 +3249,85 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.39</v>
+        <v>3.15</v>
       </c>
       <c r="M22" t="n">
-        <v>4.5</v>
+        <v>3.04</v>
       </c>
       <c r="N22" t="n">
-        <v>5.7</v>
+        <v>2.2</v>
       </c>
       <c r="O22" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="P22" t="n">
-        <v>12</v>
+        <v>1.85</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.88</v>
+        <v>3.12</v>
       </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>1.61</v>
       </c>
       <c r="S22" t="n">
-        <v>3.75</v>
+        <v>2.25</v>
       </c>
       <c r="T22" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC22" t="n">
         <v>2.2</v>
       </c>
-      <c r="U22" t="n">
+      <c r="AD22" t="n">
         <v>1.62</v>
       </c>
-      <c r="V22" t="n">
-        <v>5</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.67</v>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>['77']</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>['9', '64']</t>
+        </is>
       </c>
       <c r="AG22" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>3.9</v>
+        <v>1.26</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>['45', '77']</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>['62', '72']</t>
-        </is>
-      </c>
-      <c r="AL22" s="3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK22" s="3" t="n">
         <v>45880.58333333334</v>
       </c>
     </row>
@@ -3410,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,25 +3352,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3446,88 +3378,85 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.01</v>
+        <v>2.75</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="N23" t="n">
-        <v>2.91</v>
+        <v>2.44</v>
       </c>
       <c r="O23" t="n">
-        <v>1.73</v>
+        <v>3.2</v>
       </c>
       <c r="P23" t="n">
-        <v>12.5</v>
+        <v>2.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="R23" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S23" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="T23" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="U23" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="V23" t="n">
-        <v>5.35</v>
+        <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="Y23" t="n">
-        <v>10</v>
+        <v>1.67</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.17</v>
+        <v>2.15</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AC23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>['5', '43', '45+1']</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>['7', '24']</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI23" t="n">
         <v>2</v>
       </c>
-      <c r="AD23" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>['74']</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>['16', '27', '35', '72']</t>
-        </is>
-      </c>
-      <c r="AL23" s="3" t="n">
+      <c r="AJ23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK23" s="3" t="n">
         <v>45880.58333333334</v>
       </c>
     </row>
@@ -3537,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,22 +3481,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3578,89 +3507,86 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.85</v>
+        <v>2.6</v>
       </c>
       <c r="M24" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X24" t="n">
         <v>3.5</v>
       </c>
-      <c r="N24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="P24" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V24" t="n">
-        <v>8</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y24" t="n">
-        <v>8.5</v>
+        <v>1.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.35</v>
+        <v>1.95</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.05</v>
+        <v>1.33</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.95</v>
+        <v>2.17</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>['61']</t>
+        </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.8</v>
+        <v>1.28</v>
       </c>
       <c r="AH24" t="n">
-        <v>7.5</v>
+        <v>1.48</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>['36']</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>['75']</t>
-        </is>
-      </c>
-      <c r="AL24" s="3" t="n">
-        <v>45880.61458333334</v>
+        <v>2</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK24" s="3" t="n">
+        <v>45880.58333333334</v>
       </c>
     </row>
     <row r="25">
@@ -3669,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,19 +3610,19 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
         <v>1</v>
@@ -3710,89 +3636,86 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="O25" t="n">
-        <v>1.73</v>
+        <v>2.5</v>
       </c>
       <c r="P25" t="n">
-        <v>7.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.49</v>
+        <v>4.5</v>
       </c>
       <c r="R25" t="n">
         <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="T25" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="U25" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="V25" t="n">
-        <v>8.1</v>
+        <v>1.06</v>
       </c>
       <c r="W25" t="n">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="X25" t="n">
-        <v>1.06</v>
+        <v>3.1</v>
       </c>
       <c r="Y25" t="n">
-        <v>7.8</v>
+        <v>2.05</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.35</v>
+        <v>1.75</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.16</v>
+        <v>1.25</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>['36']</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>['75']</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH25" t="n">
         <v>1.83</v>
       </c>
-      <c r="AG25" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>8.5</v>
-      </c>
       <c r="AI25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>['15']</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL25" s="3" t="n">
-        <v>45880.625</v>
+        <v>1.67</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK25" s="3" t="n">
+        <v>45880.61458333334</v>
       </c>
     </row>
     <row r="26">
@@ -3851,13 +3774,13 @@
         <v>5.75</v>
       </c>
       <c r="O26" t="n">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="P26" t="n">
-        <v>11</v>
+        <v>2.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R26" t="n">
         <v>1.28</v>
@@ -3872,58 +3795,55 @@
         <v>1.55</v>
       </c>
       <c r="V26" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="W26" t="n">
-        <v>1.13</v>
+        <v>1.37</v>
       </c>
       <c r="X26" t="n">
-        <v>1.03</v>
+        <v>2.91</v>
       </c>
       <c r="Y26" t="n">
-        <v>9.199999999999999</v>
+        <v>1.62</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.37</v>
+        <v>2.15</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.91</v>
+        <v>2.46</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>['15', '20', '62', '79']</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>['33', '45', '73']</t>
+        </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.91</v>
+        <v>1.12</v>
       </c>
       <c r="AH26" t="n">
-        <v>4.33</v>
+        <v>2.31</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>['15', '20', '62', '79']</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>['33', '45', '73']</t>
-        </is>
-      </c>
-      <c r="AL26" s="3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK26" s="3" t="n">
         <v>45880.625</v>
       </c>
     </row>
@@ -3948,25 +3868,25 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3974,28 +3894,28 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.15</v>
+        <v>2.62</v>
       </c>
       <c r="M27" t="n">
-        <v>4.01</v>
+        <v>3.55</v>
       </c>
       <c r="N27" t="n">
-        <v>2</v>
+        <v>2.34</v>
       </c>
       <c r="O27" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="P27" t="n">
-        <v>11</v>
+        <v>2.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.73</v>
+        <v>2.4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="S27" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="T27" t="n">
         <v>2.25</v>
@@ -4004,58 +3924,55 @@
         <v>1.62</v>
       </c>
       <c r="V27" t="n">
-        <v>5.15</v>
+        <v>1.03</v>
       </c>
       <c r="W27" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="X27" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="Y27" t="n">
-        <v>10</v>
+        <v>1.47</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.15</v>
+        <v>2.4</v>
       </c>
       <c r="AA27" t="n">
-        <v>5.73</v>
+        <v>2.35</v>
       </c>
       <c r="AB27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC27" t="n">
         <v>1.5</v>
       </c>
-      <c r="AC27" t="n">
-        <v>2.45</v>
-      </c>
       <c r="AD27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.46</v>
+        <v>2.55</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>['17', '49', '89']</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>['78']</t>
+        </is>
       </c>
       <c r="AG27" t="n">
-        <v>2.6</v>
+        <v>1.62</v>
       </c>
       <c r="AH27" t="n">
-        <v>3.5</v>
+        <v>1.35</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>['19', '26']</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>['14', '28', '72']</t>
-        </is>
-      </c>
-      <c r="AL27" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK27" s="3" t="n">
         <v>45880.625</v>
       </c>
     </row>
@@ -4080,25 +3997,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G28" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" t="n">
         <v>3</v>
       </c>
-      <c r="H28" t="n">
-        <v>1</v>
-      </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4106,28 +4023,28 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.62</v>
+        <v>3.15</v>
       </c>
       <c r="M28" t="n">
-        <v>3.55</v>
+        <v>4.01</v>
       </c>
       <c r="N28" t="n">
-        <v>2.34</v>
+        <v>2</v>
       </c>
       <c r="O28" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="P28" t="n">
-        <v>15</v>
+        <v>2.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.73</v>
+        <v>2.57</v>
       </c>
       <c r="R28" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="S28" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="T28" t="n">
         <v>2.25</v>
@@ -4136,58 +4053,55 @@
         <v>1.62</v>
       </c>
       <c r="V28" t="n">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="W28" t="n">
         <v>1.15</v>
       </c>
       <c r="X28" t="n">
-        <v>1.03</v>
+        <v>5.73</v>
       </c>
       <c r="Y28" t="n">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.1</v>
+        <v>2.45</v>
       </c>
       <c r="AA28" t="n">
-        <v>5.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.4</v>
+        <v>1.46</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>['19', '26']</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>['14', '28', '72']</t>
+        </is>
       </c>
       <c r="AG28" t="n">
-        <v>2.55</v>
+        <v>1.29</v>
       </c>
       <c r="AH28" t="n">
-        <v>3.85</v>
+        <v>1.33</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>['17', '49', '89']</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>['78']</t>
-        </is>
-      </c>
-      <c r="AL28" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK28" s="3" t="n">
         <v>45880.625</v>
       </c>
     </row>
@@ -4197,12 +4111,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,22 +4126,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -4238,89 +4152,86 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="M29" t="n">
         <v>3</v>
       </c>
       <c r="N29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA29" t="n">
         <v>3.7</v>
       </c>
-      <c r="O29" t="n">
+      <c r="AB29" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>['15']</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI29" t="n">
         <v>1.73</v>
       </c>
-      <c r="P29" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V29" t="n">
-        <v>9</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL29" s="3" t="n">
-        <v>45880.63541666666</v>
+      <c r="AJ29" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AK29" s="3" t="n">
+        <v>45880.625</v>
       </c>
     </row>
     <row r="30">
@@ -4329,12 +4240,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,22 +4255,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -4370,89 +4281,86 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.12</v>
+        <v>2.05</v>
       </c>
       <c r="M30" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>2.19</v>
+        <v>3.7</v>
       </c>
       <c r="O30" t="n">
-        <v>2.38</v>
+        <v>2.95</v>
       </c>
       <c r="P30" t="n">
-        <v>7.3</v>
+        <v>1.93</v>
       </c>
       <c r="Q30" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH30" t="n">
         <v>1.83</v>
       </c>
-      <c r="R30" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T30" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V30" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>6.85</v>
-      </c>
       <c r="AI30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>['33']</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>['60']</t>
-        </is>
-      </c>
-      <c r="AL30" s="3" t="n">
-        <v>45880.64583333334</v>
+        <v>1.73</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AK30" s="3" t="n">
+        <v>45880.63541666666</v>
       </c>
     </row>
     <row r="31">
@@ -4466,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,22 +4384,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -4502,88 +4410,85 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>12.25</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>15.25</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>2.07</v>
+        <v>0</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>['49']</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>['18', '79']</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>['55', '67']</t>
-        </is>
-      </c>
-      <c r="AL31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="3" t="n">
         <v>45880.64583333334</v>
       </c>
     </row>
@@ -4598,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,22 +4513,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G32" t="n">
         <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -4634,88 +4539,85 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.53</v>
+        <v>3.12</v>
       </c>
       <c r="M32" t="n">
-        <v>3.9</v>
+        <v>2.91</v>
       </c>
       <c r="N32" t="n">
-        <v>4.75</v>
+        <v>2.19</v>
       </c>
       <c r="O32" t="n">
-        <v>1.5</v>
+        <v>4.05</v>
       </c>
       <c r="P32" t="n">
-        <v>10.5</v>
+        <v>1.98</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="R32" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U32" t="n">
         <v>1.33</v>
       </c>
-      <c r="S32" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.44</v>
-      </c>
       <c r="V32" t="n">
-        <v>6.5</v>
+        <v>1.03</v>
       </c>
       <c r="W32" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="X32" t="n">
-        <v>1.05</v>
+        <v>2.84</v>
       </c>
       <c r="Y32" t="n">
-        <v>9.5</v>
+        <v>2.4</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.8</v>
+        <v>3.52</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.75</v>
+        <v>1.22</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AD32" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF32" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>['33']</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>['60']</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ32" t="n">
         <v>1.83</v>
       </c>
-      <c r="AG32" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>['49']</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL32" s="3" t="n">
+      <c r="AK32" s="3" t="n">
         <v>45880.64583333334</v>
       </c>
     </row>
@@ -4725,12 +4627,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4758,7 +4660,7 @@
         <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4766,89 +4668,86 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>4</v>
+        <v>1.19</v>
       </c>
       <c r="M33" t="n">
-        <v>3.31</v>
+        <v>6</v>
       </c>
       <c r="N33" t="n">
-        <v>1.76</v>
+        <v>12.25</v>
       </c>
       <c r="O33" t="n">
-        <v>2.75</v>
+        <v>1.6</v>
       </c>
       <c r="P33" t="n">
-        <v>8</v>
+        <v>2.61</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.57</v>
+        <v>9.1</v>
       </c>
       <c r="R33" t="n">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="S33" t="n">
-        <v>2.63</v>
+        <v>3.34</v>
       </c>
       <c r="T33" t="n">
-        <v>3</v>
+        <v>2.19</v>
       </c>
       <c r="U33" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="V33" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="W33" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X33" t="n">
-        <v>1.02</v>
+        <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>7.8</v>
+        <v>1.42</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.35</v>
+        <v>2.49</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.12</v>
+        <v>2.1</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.94</v>
+        <v>1.66</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.76</v>
+        <v>2.07</v>
       </c>
       <c r="AD33" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>2</v>
+        <v>1.64</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>['18', '79']</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>['55', '67']</t>
+        </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="AH33" t="n">
-        <v>6.75</v>
+        <v>4.05</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>['14', '90+3']</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>['32', '80']</t>
-        </is>
-      </c>
-      <c r="AL33" s="3" t="n">
-        <v>45880.65625</v>
+        <v>1.2</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AK33" s="3" t="n">
+        <v>45880.64583333334</v>
       </c>
     </row>
     <row r="34">
@@ -4857,37 +4756,37 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G34" t="n">
         <v>2</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>1</v>
@@ -4898,89 +4797,86 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.8</v>
+        <v>5</v>
       </c>
       <c r="M34" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="N34" t="n">
-        <v>3.75</v>
+        <v>1.69</v>
       </c>
       <c r="O34" t="n">
-        <v>1.67</v>
+        <v>5.5</v>
       </c>
       <c r="P34" t="n">
-        <v>24</v>
+        <v>2.25</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="R34" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="S34" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="T34" t="n">
-        <v>2.08</v>
+        <v>3</v>
       </c>
       <c r="U34" t="n">
-        <v>1.75</v>
+        <v>1.42</v>
       </c>
       <c r="V34" t="n">
-        <v>4.05</v>
+        <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="X34" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="Y34" t="n">
-        <v>20</v>
+        <v>2.1</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.13</v>
+        <v>1.85</v>
       </c>
       <c r="AA34" t="n">
-        <v>5.5</v>
+        <v>3.1</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.9</v>
+        <v>1.77</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.42</v>
+        <v>1.86</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>['14', '90+3']</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>['32', '80']</t>
+        </is>
       </c>
       <c r="AG34" t="n">
-        <v>2.4</v>
+        <v>1.25</v>
       </c>
       <c r="AH34" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>['55', '65']</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>['11']</t>
-        </is>
-      </c>
-      <c r="AL34" s="3" t="n">
-        <v>45880.67708333334</v>
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="3" t="n">
+        <v>45880.65625</v>
       </c>
     </row>
     <row r="35">
@@ -5004,25 +4900,25 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -5030,88 +4926,85 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="M35" t="n">
-        <v>4.31</v>
+        <v>4.2</v>
       </c>
       <c r="N35" t="n">
-        <v>5.1</v>
+        <v>3.75</v>
       </c>
       <c r="O35" t="n">
-        <v>1.41</v>
+        <v>2.25</v>
       </c>
       <c r="P35" t="n">
-        <v>20.5</v>
+        <v>2.44</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.89</v>
+        <v>3.95</v>
       </c>
       <c r="R35" t="n">
         <v>1.2</v>
       </c>
       <c r="S35" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="T35" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="U35" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="V35" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="W35" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="X35" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="Y35" t="n">
-        <v>16</v>
+        <v>1.36</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.15</v>
+        <v>2.9</v>
       </c>
       <c r="AA35" t="n">
-        <v>5.3</v>
+        <v>1.85</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.47</v>
+        <v>1.42</v>
       </c>
       <c r="AD35" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>['55', '65']</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>['11']</t>
+        </is>
       </c>
       <c r="AG35" t="n">
-        <v>2.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH35" t="n">
-        <v>3.2</v>
+        <v>2.03</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>['42', '59', '69']</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>['5', '21']</t>
-        </is>
-      </c>
-      <c r="AL35" s="3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK35" s="3" t="n">
         <v>45880.67708333334</v>
       </c>
     </row>
@@ -5121,130 +5014,127 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G36" t="n">
         <v>3</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="n">
         <v>2</v>
       </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="M36" t="n">
-        <v>3.85</v>
+        <v>4.31</v>
       </c>
       <c r="N36" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="O36" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>5</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X36" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Y36" t="n">
         <v>1.5</v>
       </c>
-      <c r="P36" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S36" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T36" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V36" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>9.5</v>
-      </c>
       <c r="Z36" t="n">
-        <v>1.28</v>
+        <v>2.47</v>
       </c>
       <c r="AA36" t="n">
-        <v>3.65</v>
+        <v>2</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.97</v>
+        <v>1.5</v>
       </c>
       <c r="AD36" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1.8</v>
+        <v>2.33</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>['42', '59', '69']</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>['5', '21']</t>
+        </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.95</v>
+        <v>1.15</v>
       </c>
       <c r="AH36" t="n">
-        <v>5.75</v>
+        <v>2.3</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>['12', '32', '79']</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL36" s="3" t="n">
-        <v>45880.69791666666</v>
+        <v>1.41</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AK36" s="3" t="n">
+        <v>45880.67708333334</v>
       </c>
     </row>
     <row r="37">
@@ -5253,130 +5143,127 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="M37" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="N37" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="O37" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="P37" t="n">
-        <v>7</v>
+        <v>2.3</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="R37" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U37" t="n">
         <v>1.44</v>
       </c>
-      <c r="S37" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T37" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.33</v>
-      </c>
       <c r="V37" t="n">
-        <v>9</v>
+        <v>1.05</v>
       </c>
       <c r="W37" t="n">
-        <v>1.07</v>
+        <v>1.28</v>
       </c>
       <c r="X37" t="n">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="Y37" t="n">
-        <v>7</v>
+        <v>1.83</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.36</v>
+        <v>1.97</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.2</v>
+        <v>1.38</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>2</v>
+        <v>1.95</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>['12', '32', '79']</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.73</v>
+        <v>1.15</v>
       </c>
       <c r="AH37" t="n">
-        <v>7.2</v>
+        <v>2.3</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL37" s="3" t="n">
-        <v>45880.75</v>
+        <v>1.5</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AK37" s="3" t="n">
+        <v>45880.69791666666</v>
       </c>
     </row>
     <row r="38">
@@ -5385,12 +5272,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,19 +5287,19 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -5422,93 +5309,90 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="M38" t="n">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="N38" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O38" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X38" t="n">
         <v>2.98</v>
       </c>
-      <c r="O38" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P38" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T38" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V38" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y38" t="n">
-        <v>6.25</v>
+        <v>2.2</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.4</v>
+        <v>3.92</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.53</v>
+        <v>1.23</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="AD38" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>['76']</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>['56']</t>
+        </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.71</v>
+        <v>1.19</v>
       </c>
       <c r="AH38" t="n">
-        <v>13</v>
+        <v>1.79</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL38" s="3" t="n">
-        <v>45880.79166666666</v>
+        <v>1.67</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AK38" s="3" t="n">
+        <v>45880.75</v>
       </c>
     </row>
     <row r="39">
@@ -5517,12 +5401,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,19 +5416,19 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -5554,93 +5438,90 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="M39" t="n">
-        <v>2.62</v>
+        <v>2.92</v>
       </c>
       <c r="N39" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O39" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="P39" t="n">
         <v>2.05</v>
       </c>
-      <c r="P39" t="n">
-        <v>5.5</v>
-      </c>
       <c r="Q39" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X39" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>['-1', '-1', '-1', '-1']</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>['-1', '-1']</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ39" t="n">
         <v>2.3</v>
       </c>
-      <c r="R39" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="T39" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V39" t="n">
-        <v>12</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL39" s="3" t="n">
-        <v>45880.79861111111</v>
+      <c r="AK39" s="3" t="n">
+        <v>45880.79166666666</v>
       </c>
     </row>
     <row r="40">
@@ -5649,12 +5530,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,115 +5545,112 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.65</v>
+        <v>2.18</v>
       </c>
       <c r="M40" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="N40" t="n">
-        <v>2.79</v>
+        <v>3</v>
       </c>
       <c r="O40" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X40" t="n">
         <v>2.05</v>
       </c>
-      <c r="P40" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="S40" t="n">
+      <c r="Y40" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC40" t="n">
         <v>2.35</v>
       </c>
-      <c r="T40" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U40" t="n">
+      <c r="AD40" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>['36']</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
         <v>1.25</v>
       </c>
-      <c r="V40" t="n">
-        <v>10</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Z40" t="n">
+      <c r="AH40" t="n">
         <v>1.53</v>
       </c>
-      <c r="AA40" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>10</v>
-      </c>
       <c r="AI40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL40" s="3" t="n">
-        <v>45880.8125</v>
+        <v>2.05</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK40" s="3" t="n">
+        <v>45880.79861111111</v>
       </c>
     </row>
     <row r="41">
@@ -5796,114 +5674,111 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L41" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="M41" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="N41" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="O41" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X41" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC41" t="n">
         <v>2.16</v>
       </c>
-      <c r="M41" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="N41" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="O41" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="P41" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S41" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T41" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V41" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X41" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC41" t="n">
+      <c r="AD41" t="n">
         <v>1.58</v>
       </c>
-      <c r="AD41" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>1.95</v>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>['8']</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.87</v>
+        <v>1.44</v>
       </c>
       <c r="AH41" t="n">
-        <v>7.5</v>
+        <v>1.44</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL41" s="3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK41" s="3" t="n">
         <v>45880.8125</v>
       </c>
     </row>
@@ -5913,12 +5788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,115 +5803,112 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.8</v>
+        <v>2.16</v>
       </c>
       <c r="M42" t="n">
-        <v>3.65</v>
+        <v>3.03</v>
       </c>
       <c r="N42" t="n">
-        <v>2.21</v>
+        <v>3.27</v>
       </c>
       <c r="O42" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X42" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y42" t="n">
         <v>2.25</v>
       </c>
-      <c r="P42" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S42" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V42" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>0</v>
-      </c>
       <c r="Z42" t="n">
-        <v>1.14</v>
+        <v>1.58</v>
       </c>
       <c r="AA42" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.49</v>
+        <v>1.17</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>1.42</v>
+        <v>1.87</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>['17']</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>['45+5']</t>
+        </is>
       </c>
       <c r="AG42" t="n">
-        <v>2.54</v>
+        <v>1.3</v>
       </c>
       <c r="AH42" t="n">
-        <v>3.58</v>
+        <v>1.52</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL42" s="3" t="n">
-        <v>45880.83333333334</v>
+        <v>1.73</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK42" s="3" t="n">
+        <v>45880.8125</v>
       </c>
     </row>
     <row r="43">
@@ -6050,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,114 +5932,111 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.29</v>
+        <v>2.66</v>
       </c>
       <c r="M43" t="n">
-        <v>2.94</v>
+        <v>3.63</v>
       </c>
       <c r="N43" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O43" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X43" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD43" t="n">
         <v>2.1</v>
       </c>
-      <c r="O43" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P43" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R43" t="n">
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>['16', '62', '79', '86']</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG43" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH43" t="n">
         <v>1.5</v>
       </c>
-      <c r="S43" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="T43" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V43" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X43" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>9.5</v>
-      </c>
       <c r="AI43" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL43" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK43" s="3" t="n">
         <v>45880.83333333334</v>
       </c>
     </row>
@@ -6182,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6192,114 +6061,111 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="M44" t="n">
-        <v>3.63</v>
+        <v>3.65</v>
       </c>
       <c r="N44" t="n">
-        <v>2.47</v>
+        <v>2.21</v>
       </c>
       <c r="O44" t="n">
-        <v>2</v>
+        <v>4.1</v>
       </c>
       <c r="P44" t="n">
-        <v>12</v>
+        <v>2.32</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.95</v>
+        <v>2.62</v>
       </c>
       <c r="R44" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="T44" t="n">
-        <v>2.75</v>
+        <v>2.13</v>
       </c>
       <c r="U44" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="V44" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X44" t="n">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="Y44" t="n">
-        <v>9.199999999999999</v>
+        <v>1.49</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.24</v>
+        <v>2.5</v>
       </c>
       <c r="AA44" t="n">
-        <v>3.36</v>
+        <v>2.15</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.94</v>
+        <v>1.65</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.88</v>
+        <v>1.42</v>
       </c>
       <c r="AD44" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>1.67</v>
+        <v>2.54</v>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>['12', '45']</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG44" t="n">
-        <v>2.1</v>
+        <v>1.25</v>
       </c>
       <c r="AH44" t="n">
-        <v>5.85</v>
+        <v>1.35</v>
       </c>
       <c r="AI44" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL44" s="3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AK44" s="3" t="n">
         <v>45880.83333333334</v>
       </c>
     </row>
@@ -6309,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6324,115 +6190,112 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.73</v>
+        <v>3.29</v>
       </c>
       <c r="M45" t="n">
-        <v>3.75</v>
+        <v>2.94</v>
       </c>
       <c r="N45" t="n">
-        <v>3.95</v>
+        <v>2.1</v>
       </c>
       <c r="O45" t="n">
-        <v>1.53</v>
+        <v>4.37</v>
       </c>
       <c r="P45" t="n">
-        <v>9.300000000000001</v>
+        <v>2.05</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="R45" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="S45" t="n">
-        <v>3.1</v>
+        <v>2.34</v>
       </c>
       <c r="T45" t="n">
-        <v>2.45</v>
+        <v>3.48</v>
       </c>
       <c r="U45" t="n">
-        <v>1.51</v>
+        <v>1.25</v>
       </c>
       <c r="V45" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X45" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AA45" t="n">
         <v>5</v>
       </c>
-      <c r="W45" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z45" t="n">
+      <c r="AB45" t="n">
         <v>1.17</v>
       </c>
-      <c r="AA45" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AC45" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>['27', '81']</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>['90']</t>
+        </is>
       </c>
       <c r="AG45" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="AH45" t="n">
-        <v>5.4</v>
+        <v>1.25</v>
       </c>
       <c r="AI45" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL45" s="3" t="n">
-        <v>45880.85416666666</v>
+        <v>2.4</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK45" s="3" t="n">
+        <v>45880.83333333334</v>
       </c>
     </row>
     <row r="46">
@@ -6441,12 +6304,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6456,115 +6319,112 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.02</v>
+        <v>1.73</v>
       </c>
       <c r="M46" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="N46" t="n">
-        <v>3.84</v>
+        <v>3.95</v>
       </c>
       <c r="O46" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="P46" t="n">
-        <v>5.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q46" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X46" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>['29', '51', '62', '77']</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>['36', '68', '86']</t>
+        </is>
+      </c>
+      <c r="AG46" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ46" t="n">
         <v>2.5</v>
       </c>
-      <c r="R46" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="S46" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="T46" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V46" t="n">
-        <v>15</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1</v>
-      </c>
-      <c r="X46" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>11</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL46" s="3" t="n">
-        <v>45880.88194444445</v>
+      <c r="AK46" s="3" t="n">
+        <v>45880.85416666666</v>
       </c>
     </row>
     <row r="47">
@@ -6573,129 +6433,255 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Racing Córdoba</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Quilmes</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>2</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>2</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="M47" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="N47" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="O47" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S47" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X47" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>['2', '21']</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG47" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK47" s="3" t="n">
+        <v>45880.88194444445</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>45880</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>Paysandu</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Vila Nova</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L47" t="n">
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
         <v>2.22</v>
       </c>
-      <c r="M47" t="n">
+      <c r="M48" t="n">
         <v>2.83</v>
       </c>
-      <c r="N47" t="n">
+      <c r="N48" t="n">
         <v>3.16</v>
       </c>
-      <c r="O47" t="n">
+      <c r="O48" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="P48" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S48" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X48" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>['71']</t>
+        </is>
+      </c>
+      <c r="AG48" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI48" t="n">
         <v>1.91</v>
       </c>
-      <c r="P47" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="Q47" t="n">
+      <c r="AJ48" t="n">
         <v>2.3</v>
       </c>
-      <c r="R47" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S47" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="T47" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V47" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1</v>
-      </c>
-      <c r="X47" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>11</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL47" s="3" t="n">
+      <c r="AK48" s="3" t="n">
         <v>45880.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-08-11.xlsx
+++ b/jogos_2025-08-11.xlsx
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,19 +1804,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.44</v>
+        <v>3.02</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="O11" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="P11" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="R11" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="T11" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="U11" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="V11" t="n">
         <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="X11" t="n">
-        <v>7.28</v>
+        <v>4.6</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="Z11" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.42</v>
+        <v>1.71</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['70', '72', '86', '89', '90+3']</t>
+          <t>['-1', '-1']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['65']</t>
+          <t>['-1', '-1']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.6</v>
+        <v>1.26</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.83</v>
+        <v>2.13</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45880.54166666666</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.49</v>
+        <v>1.72</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>2.85</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>2.42</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.5</v>
+        <v>6.34</v>
       </c>
       <c r="R12" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="S12" t="n">
-        <v>2.62</v>
+        <v>2.31</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>3.66</v>
       </c>
       <c r="U12" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="V12" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W12" t="n">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
       <c r="X12" t="n">
-        <v>2.74</v>
+        <v>2.33</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.1</v>
+        <v>2.61</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.98</v>
+        <v>5.04</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.91</v>
+        <v>2.36</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2022,20 +2022,20 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['-1']</t>
+          <t>['41']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.4</v>
+        <v>1.16</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.5</v>
+        <v>2.07</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.91</v>
+        <v>1.63</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.25</v>
+        <v>2.66</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45880.54166666666</v>
@@ -2052,26 +2052,26 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H13" t="n">
         <v>1</v>
@@ -2080,7 +2080,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.72</v>
+        <v>2.44</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="O13" t="n">
-        <v>2.42</v>
+        <v>2.85</v>
       </c>
       <c r="P13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X13" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>['70', '72', '86', '89', '90+3']</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>['65']</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ13" t="n">
         <v>1.91</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>6.34</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>5.04</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>['41']</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>2.66</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45880.54166666666</v>
@@ -2181,33 +2181,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
         <v>2</v>
       </c>
-      <c r="H14" t="n">
-        <v>2</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.02</v>
+        <v>2.78</v>
       </c>
       <c r="M14" t="n">
-        <v>3.35</v>
+        <v>2.77</v>
       </c>
       <c r="N14" t="n">
-        <v>2.05</v>
+        <v>2.68</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P14" t="n">
-        <v>2.38</v>
+        <v>1.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.6</v>
+        <v>3.48</v>
       </c>
       <c r="R14" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="S14" t="n">
-        <v>3.14</v>
+        <v>2.25</v>
       </c>
       <c r="T14" t="n">
-        <v>2.3</v>
+        <v>3.45</v>
       </c>
       <c r="U14" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="V14" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="W14" t="n">
-        <v>1.16</v>
+        <v>1.49</v>
       </c>
       <c r="X14" t="n">
-        <v>4.6</v>
+        <v>2.52</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.55</v>
+        <v>2.74</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.25</v>
+        <v>1.48</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.63</v>
+        <v>4.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.48</v>
+        <v>1.17</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.71</v>
+        <v>2.13</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.45</v>
+        <v>1.68</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['-1', '-1']</t>
+          <t>['18', '45+2', '84']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>['-1', '-1']</t>
+          <t>['83']</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45880.54166666666</v>
@@ -2310,119 +2310,119 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O15" t="n">
         <v>3</v>
       </c>
-      <c r="H15" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" t="n">
+      <c r="P15" t="n">
         <v>2</v>
       </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="M15" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="O15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.9</v>
-      </c>
       <c r="Q15" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="T15" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="W15" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="X15" t="n">
-        <v>2.52</v>
+        <v>2.74</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.74</v>
+        <v>2.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.9</v>
+        <v>3.98</v>
       </c>
       <c r="AB15" t="n">
         <v>1.17</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['18', '45+2', '84']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['83']</t>
+          <t>['-1']</t>
         </is>
       </c>
       <c r="AG15" t="n">
         <v>1.4</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45880.54166666666</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,109 +2449,109 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S16" t="n">
         <v>3</v>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L16" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="M16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R16" t="n">
+      <c r="T16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB16" t="n">
         <v>1.33</v>
       </c>
-      <c r="S16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z16" t="n">
+      <c r="AC16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>['61']</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI16" t="n">
         <v>2</v>
       </c>
-      <c r="AA16" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>['74']</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>['16', '27', '35', '72']</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AJ16" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45880.58333333334</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,109 +2578,109 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O17" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q17" t="n">
         <v>2</v>
       </c>
-      <c r="J17" t="n">
+      <c r="R17" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z17" t="n">
         <v>2</v>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="M17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AA17" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['3', '45+1', '79']</t>
+          <t>['19']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>['38', '41', '53']</t>
+          <t>['90']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.4</v>
+        <v>2.11</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.55</v>
+        <v>1.13</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45880.58333333334</v>
@@ -2707,109 +2707,109 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z18" t="n">
         <v>2</v>
       </c>
-      <c r="H18" t="n">
-        <v>2</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="M18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="O18" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y18" t="n">
+      <c r="AA18" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD18" t="n">
         <v>2.1</v>
       </c>
-      <c r="Z18" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['17', '27']</t>
+          <t>['74']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>['48', '58']</t>
+          <t>['16', '27', '35', '72']</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.5</v>
+        <v>1.73</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45880.58333333334</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,22 +2836,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4.35</v>
+        <v>3.6</v>
       </c>
       <c r="M19" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="O19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>['17', '27']</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>['48', '58']</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ19" t="n">
         <v>1.67</v>
-      </c>
-      <c r="O19" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X19" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>['19']</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>['90']</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45880.58333333334</v>
@@ -2955,35 +2955,35 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
         <v>2</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.39</v>
+        <v>2.75</v>
       </c>
       <c r="M20" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="N20" t="n">
-        <v>5.7</v>
+        <v>2.44</v>
       </c>
       <c r="O20" t="n">
-        <v>1.83</v>
+        <v>3.2</v>
       </c>
       <c r="P20" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>6</v>
+        <v>2.9</v>
       </c>
       <c r="R20" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S20" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="T20" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="U20" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="V20" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W20" t="n">
         <v>1.17</v>
       </c>
       <c r="X20" t="n">
-        <v>5.25</v>
+        <v>4.2</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>['45', '77']</t>
+          <t>['5', '43', '45+1']</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>['62', '72']</t>
+          <t>['7', '24']</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.09</v>
+        <v>1.27</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.75</v>
+        <v>1.44</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.88</v>
+        <v>1.8</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45880.58333333334</v>
@@ -3342,35 +3342,35 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
         <v>2</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.75</v>
+        <v>1.39</v>
       </c>
       <c r="M23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N23" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>6</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S23" t="n">
         <v>3.75</v>
       </c>
-      <c r="N23" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="O23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P23" t="n">
+      <c r="T23" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q23" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.4</v>
-      </c>
       <c r="U23" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="V23" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W23" t="n">
         <v>1.17</v>
       </c>
       <c r="X23" t="n">
-        <v>4.2</v>
+        <v>5.25</v>
       </c>
       <c r="Y23" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC23" t="n">
         <v>1.67</v>
       </c>
-      <c r="Z23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AD23" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['5', '43', '45+1']</t>
+          <t>['45', '77']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['7', '24']</t>
+          <t>['62', '72']</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.27</v>
+        <v>1.09</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.44</v>
+        <v>2.75</v>
       </c>
       <c r="AI23" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.8</v>
+        <v>2.88</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45880.58333333334</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,25 +3481,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.6</v>
+        <v>2.29</v>
       </c>
       <c r="M24" t="n">
-        <v>3.64</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="O24" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="P24" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
       <c r="R24" t="n">
         <v>1.3</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="T24" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="U24" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="V24" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="W24" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X24" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.17</v>
+        <v>2.4</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['3', '45+1', '79']</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>['61']</t>
+          <t>['38', '41', '53']</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AI24" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45880.58333333334</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,109 +3739,109 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>2</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q26" t="n">
         <v>4</v>
       </c>
-      <c r="H26" t="n">
-        <v>3</v>
-      </c>
-      <c r="I26" t="n">
-        <v>2</v>
-      </c>
-      <c r="J26" t="n">
-        <v>2</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L26" t="n">
+      <c r="R26" t="n">
         <v>1.4</v>
       </c>
-      <c r="M26" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N26" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>6</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.28</v>
-      </c>
       <c r="S26" t="n">
-        <v>3.22</v>
+        <v>2.6</v>
       </c>
       <c r="T26" t="n">
-        <v>2.25</v>
+        <v>3.15</v>
       </c>
       <c r="U26" t="n">
-        <v>1.55</v>
+        <v>1.32</v>
       </c>
       <c r="V26" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W26" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="X26" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.62</v>
+        <v>2.16</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.15</v>
+        <v>1.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.46</v>
+        <v>3.7</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.43</v>
+        <v>1.18</v>
       </c>
       <c r="AC26" t="n">
         <v>1.83</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['15', '20', '62', '79']</t>
+          <t>['15']</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>['33', '45', '73']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.31</v>
+        <v>1.67</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AJ26" t="n">
-        <v>3</v>
+        <v>2.49</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45880.625</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,16 +3997,16 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H28" t="n">
         <v>3</v>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.15</v>
+        <v>1.4</v>
       </c>
       <c r="M28" t="n">
-        <v>4.01</v>
+        <v>4.2</v>
       </c>
       <c r="N28" t="n">
-        <v>2</v>
+        <v>5.75</v>
       </c>
       <c r="O28" t="n">
-        <v>3.5</v>
+        <v>1.91</v>
       </c>
       <c r="P28" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.57</v>
+        <v>6</v>
       </c>
       <c r="R28" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="S28" t="n">
-        <v>3.85</v>
+        <v>3.22</v>
       </c>
       <c r="T28" t="n">
         <v>2.25</v>
       </c>
       <c r="U28" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="Y28" t="n">
         <v>1.62</v>
       </c>
-      <c r="V28" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X28" t="n">
-        <v>5.73</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.5</v>
-      </c>
       <c r="Z28" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.46</v>
+        <v>1.83</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>['19', '26']</t>
+          <t>['15', '20', '62', '79']</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>['14', '28', '72']</t>
+          <t>['33', '45', '73']</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.33</v>
+        <v>2.31</v>
       </c>
       <c r="AI28" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.73</v>
+        <v>3</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45880.625</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,25 +4126,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="M29" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="N29" t="n">
         <v>2</v>
       </c>
-      <c r="M29" t="n">
-        <v>3</v>
-      </c>
-      <c r="N29" t="n">
-        <v>3.3</v>
-      </c>
       <c r="O29" t="n">
-        <v>2.69</v>
+        <v>3.5</v>
       </c>
       <c r="P29" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>4</v>
+        <v>2.57</v>
       </c>
       <c r="R29" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="S29" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X29" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AD29" t="n">
         <v>2.6</v>
       </c>
-      <c r="T29" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X29" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['15']</t>
+          <t>['19', '26']</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['14', '28', '72']</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AI29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ29" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>2.49</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45880.625</v>
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,16 +4477,16 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45880.64583333334</v>
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.12</v>
+        <v>3.45</v>
       </c>
       <c r="M32" t="n">
-        <v>2.91</v>
+        <v>3.1</v>
       </c>
       <c r="N32" t="n">
-        <v>2.19</v>
+        <v>2.01</v>
       </c>
       <c r="O32" t="n">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="P32" t="n">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="R32" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S32" t="n">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="T32" t="n">
-        <v>3.04</v>
+        <v>3.34</v>
       </c>
       <c r="U32" t="n">
         <v>1.33</v>
       </c>
       <c r="V32" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W32" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="X32" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.52</v>
+        <v>4</v>
       </c>
       <c r="AB32" t="n">
         <v>1.22</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,16 +4606,16 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AI32" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45880.64583333334</v>
@@ -4900,25 +4900,25 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G35" t="n">
+        <v>3</v>
+      </c>
+      <c r="H35" t="n">
         <v>2</v>
       </c>
-      <c r="H35" t="n">
-        <v>1</v>
-      </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="M35" t="n">
-        <v>4.2</v>
+        <v>4.31</v>
       </c>
       <c r="N35" t="n">
-        <v>3.75</v>
+        <v>5.1</v>
       </c>
       <c r="O35" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="P35" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="R35" t="n">
         <v>1.2</v>
       </c>
       <c r="S35" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="T35" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="U35" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V35" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X35" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.9</v>
+        <v>2.47</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>['55', '65']</t>
+          <t>['42', '59', '69']</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>['11']</t>
+          <t>['5', '21']</t>
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AH35" t="n">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="AJ35" t="n">
-        <v>2.2</v>
+        <v>2.89</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45880.67708333334</v>
@@ -5029,25 +5029,25 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5055,83 +5055,83 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="M36" t="n">
-        <v>4.31</v>
+        <v>4.2</v>
       </c>
       <c r="N36" t="n">
-        <v>5.1</v>
+        <v>3.75</v>
       </c>
       <c r="O36" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="P36" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="Q36" t="n">
-        <v>5</v>
+        <v>3.95</v>
       </c>
       <c r="R36" t="n">
         <v>1.2</v>
       </c>
       <c r="S36" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="T36" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="U36" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="V36" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W36" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X36" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.47</v>
+        <v>2.9</v>
       </c>
       <c r="AA36" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>['42', '59', '69']</t>
+          <t>['55', '65']</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>['5', '21']</t>
+          <t>['11']</t>
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="AJ36" t="n">
-        <v>2.89</v>
+        <v>2.2</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45880.67708333334</v>
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,16 +5251,16 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45880.69791666666</v>
